--- a/Data/FlightPlan/FPL_09SEP26.xlsx
+++ b/Data/FlightPlan/FPL_09SEP26.xlsx
@@ -884,267 +884,267 @@
     <t>VN-A648</t>
   </si>
   <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
     <t>VDH</t>
   </si>
   <si>
     <t>10:15</t>
   </si>
   <si>
-    <t>VN-A649</t>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>VN-A655</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>ENH</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>VN-A662</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A671</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
   </si>
   <si>
     <t>11:00</t>
   </si>
   <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>VN-A677</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>VN-A684</t>
+  </si>
+  <si>
+    <t>VN-A685</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A687</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>VN-A689</t>
+  </si>
+  <si>
+    <t>23:20</t>
+  </si>
+  <si>
+    <t>VN-A693</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>VN-A697</t>
+  </si>
+  <si>
+    <t>VN-A698</t>
+  </si>
+  <si>
     <t>15:00</t>
   </si>
   <si>
     <t>20:20</t>
   </si>
   <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>VN-A655</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>ENH</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>VN-A662</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A671</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>VN-A677</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>VN-A684</t>
-  </si>
-  <si>
-    <t>VN-A685</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A687</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>VN-A689</t>
-  </si>
-  <si>
-    <t>23:20</t>
-  </si>
-  <si>
-    <t>VN-A693</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>VN-A697</t>
-  </si>
-  <si>
-    <t>VN-A698</t>
-  </si>
-  <si>
     <t>VN-A811</t>
   </si>
   <si>
@@ -1184,7 +1184,7 @@
     <t>Total Record(s): 351</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 08, 2026 22:05</t>
+    <t xml:space="preserve">Generated on  Sep 08, 2026 23:36</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -8638,7 +8638,7 @@
         <v>13</v>
       </c>
       <c r="B239" s="7">
-        <v>260</v>
+        <v>809</v>
       </c>
       <c t="s" r="C239" s="7">
         <v>14</v>
@@ -8657,10 +8657,10 @@
         <v>291</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>229</v>
+        <v>200</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8671,7 +8671,7 @@
         <v>13</v>
       </c>
       <c r="B240" s="7">
-        <v>261</v>
+        <v>808</v>
       </c>
       <c t="s" r="C240" s="7">
         <v>14</v>
@@ -8690,10 +8690,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>117</v>
+        <v>292</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8704,7 +8704,7 @@
         <v>13</v>
       </c>
       <c r="B241" s="7">
-        <v>807</v>
+        <v>876</v>
       </c>
       <c t="s" r="C241" s="7">
         <v>14</v>
@@ -8720,13 +8720,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8737,7 +8737,7 @@
         <v>13</v>
       </c>
       <c r="B242" s="7">
-        <v>800</v>
+        <v>877</v>
       </c>
       <c t="s" r="C242" s="7">
         <v>14</v>
@@ -8750,65 +8750,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>110</v>
+        <v>57</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>167</v>
+        <v>295</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c r="M242" s="7"/>
     </row>
     <row r="243" ht="14.25" customHeight="1">
-      <c t="s" r="A243" s="6">
-        <v>13</v>
-      </c>
-      <c r="B243" s="7">
-        <v>154</v>
-      </c>
-      <c t="s" r="C243" s="7">
-        <v>14</v>
-      </c>
+      <c r="A243" s="6"/>
+      <c r="B243" s="7"/>
+      <c r="C243" s="7"/>
       <c r="D243" s="7"/>
-      <c t="s" r="E243" s="7">
-        <v>290</v>
-      </c>
-      <c r="F243" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G243" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H243" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="I243" s="7">
-        <v>239</v>
-      </c>
-      <c t="s" r="J243" s="7">
-        <v>58</v>
-      </c>
+      <c r="E243" s="7"/>
+      <c r="F243" s="7"/>
+      <c r="G243" s="8"/>
+      <c r="H243" s="8"/>
+      <c r="I243" s="7"/>
+      <c r="J243" s="7"/>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c r="M243" s="7"/>
     </row>
     <row r="244" ht="14.25" customHeight="1">
-      <c r="A244" s="6"/>
-      <c r="B244" s="7"/>
-      <c r="C244" s="7"/>
+      <c t="s" r="A244" s="6">
+        <v>13</v>
+      </c>
+      <c r="B244" s="7">
+        <v>260</v>
+      </c>
+      <c t="s" r="C244" s="7">
+        <v>14</v>
+      </c>
       <c r="D244" s="7"/>
-      <c r="E244" s="7"/>
-      <c r="F244" s="7"/>
-      <c r="G244" s="8"/>
-      <c r="H244" s="8"/>
-      <c r="I244" s="7"/>
-      <c r="J244" s="7"/>
+      <c t="s" r="E244" s="7">
+        <v>296</v>
+      </c>
+      <c r="F244" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G244" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H244" s="8">
+        <v>297</v>
+      </c>
+      <c t="s" r="I244" s="7">
+        <v>52</v>
+      </c>
+      <c t="s" r="J244" s="7">
+        <v>229</v>
+      </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c r="M244" s="7"/>
@@ -8818,29 +8818,29 @@
         <v>13</v>
       </c>
       <c r="B245" s="7">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c t="s" r="C245" s="7">
         <v>14</v>
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>17</v>
+        <v>297</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -8851,29 +8851,29 @@
         <v>13</v>
       </c>
       <c r="B246" s="7">
-        <v>7078</v>
+        <v>807</v>
       </c>
       <c t="s" r="C246" s="7">
         <v>14</v>
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>207</v>
+        <v>91</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>295</v>
+        <v>44</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -8884,29 +8884,29 @@
         <v>13</v>
       </c>
       <c r="B247" s="7">
-        <v>7079</v>
+        <v>800</v>
       </c>
       <c t="s" r="C247" s="7">
         <v>14</v>
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>225</v>
+        <v>110</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -8917,63 +8917,45 @@
         <v>13</v>
       </c>
       <c r="B248" s="7">
-        <v>273</v>
+        <v>154</v>
       </c>
       <c t="s" r="C248" s="7">
         <v>14</v>
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>102</v>
+        <v>17</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>68</v>
+        <v>239</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c r="M248" s="7"/>
     </row>
     <row r="249" ht="14.25" customHeight="1">
-      <c t="s" r="A249" s="6">
-        <v>13</v>
-      </c>
-      <c r="B249" s="7">
-        <v>1216</v>
-      </c>
-      <c t="s" r="C249" s="7">
-        <v>14</v>
-      </c>
+      <c r="A249" s="6"/>
+      <c r="B249" s="7"/>
+      <c r="C249" s="7"/>
       <c r="D249" s="7"/>
-      <c t="s" r="E249" s="7">
-        <v>293</v>
-      </c>
-      <c r="F249" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G249" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H249" s="8">
-        <v>269</v>
-      </c>
-      <c t="s" r="I249" s="7">
-        <v>296</v>
-      </c>
-      <c t="s" r="J249" s="7">
-        <v>236</v>
-      </c>
+      <c r="E249" s="7"/>
+      <c r="F249" s="7"/>
+      <c r="G249" s="8"/>
+      <c r="H249" s="8"/>
+      <c r="I249" s="7"/>
+      <c r="J249" s="7"/>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c r="M249" s="7"/>
@@ -8983,45 +8965,63 @@
         <v>13</v>
       </c>
       <c r="B250" s="7">
-        <v>1217</v>
+        <v>431</v>
       </c>
       <c t="s" r="C250" s="7">
         <v>14</v>
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F250" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>269</v>
+        <v>27</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>17</v>
+        <v>300</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>158</v>
+        <v>301</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c r="M250" s="7"/>
     </row>
     <row r="251" ht="14.25" customHeight="1">
-      <c r="A251" s="6"/>
-      <c r="B251" s="7"/>
-      <c r="C251" s="7"/>
+      <c t="s" r="A251" s="6">
+        <v>13</v>
+      </c>
+      <c r="B251" s="7">
+        <v>430</v>
+      </c>
+      <c t="s" r="C251" s="7">
+        <v>14</v>
+      </c>
       <c r="D251" s="7"/>
-      <c r="E251" s="7"/>
-      <c r="F251" s="7"/>
-      <c r="G251" s="8"/>
-      <c r="H251" s="8"/>
-      <c r="I251" s="7"/>
-      <c r="J251" s="7"/>
+      <c t="s" r="E251" s="7">
+        <v>299</v>
+      </c>
+      <c r="F251" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G251" s="8">
+        <v>300</v>
+      </c>
+      <c t="s" r="H251" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="I251" s="7">
+        <v>229</v>
+      </c>
+      <c t="s" r="J251" s="7">
+        <v>196</v>
+      </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c r="M251" s="7"/>
@@ -9031,14 +9031,14 @@
         <v>13</v>
       </c>
       <c r="B252" s="7">
-        <v>431</v>
+        <v>403</v>
       </c>
       <c t="s" r="C252" s="7">
         <v>14</v>
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F252" s="7">
         <v>320</v>
@@ -9047,13 +9047,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H252" s="8">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>299</v>
+        <v>250</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9064,29 +9064,29 @@
         <v>13</v>
       </c>
       <c r="B253" s="7">
-        <v>430</v>
+        <v>404</v>
       </c>
       <c t="s" r="C253" s="7">
         <v>14</v>
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F253" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G253" s="8">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c t="s" r="H253" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>229</v>
+        <v>90</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>196</v>
+        <v>303</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9097,14 +9097,14 @@
         <v>13</v>
       </c>
       <c r="B254" s="7">
-        <v>403</v>
+        <v>7712</v>
       </c>
       <c t="s" r="C254" s="7">
         <v>14</v>
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F254" s="7">
         <v>320</v>
@@ -9113,13 +9113,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>181</v>
+        <v>266</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>250</v>
+        <v>305</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9127,114 +9127,114 @@
     </row>
     <row r="255" ht="15" customHeight="1">
       <c t="s" r="A255" s="6">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B255" s="7">
-        <v>404</v>
+        <v>7713</v>
       </c>
       <c t="s" r="C255" s="7">
         <v>14</v>
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F255" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c t="s" r="H255" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c r="M255" s="7"/>
     </row>
     <row r="256" ht="14.25" customHeight="1">
-      <c t="s" r="A256" s="6">
-        <v>13</v>
-      </c>
-      <c r="B256" s="7">
-        <v>7712</v>
-      </c>
-      <c t="s" r="C256" s="7">
-        <v>14</v>
-      </c>
+      <c r="A256" s="6"/>
+      <c r="B256" s="7"/>
+      <c r="C256" s="7"/>
       <c r="D256" s="7"/>
-      <c t="s" r="E256" s="7">
-        <v>297</v>
-      </c>
-      <c r="F256" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G256" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H256" s="8">
-        <v>302</v>
-      </c>
-      <c t="s" r="I256" s="7">
-        <v>266</v>
-      </c>
-      <c t="s" r="J256" s="7">
-        <v>303</v>
-      </c>
+      <c r="E256" s="7"/>
+      <c r="F256" s="7"/>
+      <c r="G256" s="8"/>
+      <c r="H256" s="8"/>
+      <c r="I256" s="7"/>
+      <c r="J256" s="7"/>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c r="M256" s="7"/>
     </row>
     <row r="257" ht="14.25" customHeight="1">
       <c t="s" r="A257" s="6">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B257" s="7">
-        <v>7713</v>
+        <v>123</v>
       </c>
       <c t="s" r="C257" s="7">
         <v>14</v>
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="F257" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>302</v>
+        <v>27</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>38</v>
+        <v>175</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c r="M257" s="7"/>
     </row>
     <row r="258" ht="14.25" customHeight="1">
-      <c r="A258" s="6"/>
-      <c r="B258" s="7"/>
-      <c r="C258" s="7"/>
+      <c t="s" r="A258" s="6">
+        <v>13</v>
+      </c>
+      <c r="B258" s="7">
+        <v>130</v>
+      </c>
+      <c t="s" r="C258" s="7">
+        <v>14</v>
+      </c>
       <c r="D258" s="7"/>
-      <c r="E258" s="7"/>
-      <c r="F258" s="7"/>
-      <c r="G258" s="8"/>
-      <c r="H258" s="8"/>
-      <c r="I258" s="7"/>
-      <c r="J258" s="7"/>
+      <c t="s" r="E258" s="7">
+        <v>307</v>
+      </c>
+      <c r="F258" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G258" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H258" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="I258" s="7">
+        <v>117</v>
+      </c>
+      <c t="s" r="J258" s="7">
+        <v>242</v>
+      </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c r="M258" s="7"/>
@@ -9244,14 +9244,14 @@
         <v>13</v>
       </c>
       <c r="B259" s="7">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c t="s" r="C259" s="7">
         <v>14</v>
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9263,10 +9263,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>299</v>
+        <v>56</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9277,14 +9277,14 @@
         <v>13</v>
       </c>
       <c r="B260" s="7">
-        <v>130</v>
+        <v>308</v>
       </c>
       <c t="s" r="C260" s="7">
         <v>14</v>
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9293,13 +9293,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>117</v>
+        <v>43</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>242</v>
+        <v>78</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9310,63 +9310,45 @@
         <v>13</v>
       </c>
       <c r="B261" s="7">
-        <v>133</v>
+        <v>307</v>
       </c>
       <c t="s" r="C261" s="7">
         <v>14</v>
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c t="s" r="H261" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>100</v>
+        <v>308</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>56</v>
+        <v>309</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c r="M261" s="7"/>
     </row>
     <row r="262" ht="14.25" customHeight="1">
-      <c t="s" r="A262" s="6">
-        <v>13</v>
-      </c>
-      <c r="B262" s="7">
-        <v>308</v>
-      </c>
-      <c t="s" r="C262" s="7">
-        <v>14</v>
-      </c>
+      <c r="A262" s="6"/>
+      <c r="B262" s="7"/>
+      <c r="C262" s="7"/>
       <c r="D262" s="7"/>
-      <c t="s" r="E262" s="7">
-        <v>305</v>
-      </c>
-      <c r="F262" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G262" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H262" s="8">
-        <v>32</v>
-      </c>
-      <c t="s" r="I262" s="7">
-        <v>43</v>
-      </c>
-      <c t="s" r="J262" s="7">
-        <v>78</v>
-      </c>
+      <c r="E262" s="7"/>
+      <c r="F262" s="7"/>
+      <c r="G262" s="8"/>
+      <c r="H262" s="8"/>
+      <c r="I262" s="7"/>
+      <c r="J262" s="7"/>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c r="M262" s="7"/>
@@ -9376,45 +9358,63 @@
         <v>13</v>
       </c>
       <c r="B263" s="7">
-        <v>307</v>
+        <v>122</v>
       </c>
       <c t="s" r="C263" s="7">
         <v>14</v>
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>306</v>
+        <v>61</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>307</v>
+        <v>249</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c r="M263" s="7"/>
     </row>
     <row r="264" ht="14.25" customHeight="1">
-      <c r="A264" s="6"/>
-      <c r="B264" s="7"/>
-      <c r="C264" s="7"/>
+      <c t="s" r="A264" s="6">
+        <v>13</v>
+      </c>
+      <c r="B264" s="7">
+        <v>135</v>
+      </c>
+      <c t="s" r="C264" s="7">
+        <v>14</v>
+      </c>
       <c r="D264" s="7"/>
-      <c r="E264" s="7"/>
-      <c r="F264" s="7"/>
-      <c r="G264" s="8"/>
-      <c r="H264" s="8"/>
-      <c r="I264" s="7"/>
-      <c r="J264" s="7"/>
+      <c t="s" r="E264" s="7">
+        <v>310</v>
+      </c>
+      <c r="F264" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G264" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H264" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I264" s="7">
+        <v>254</v>
+      </c>
+      <c t="s" r="J264" s="7">
+        <v>101</v>
+      </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c r="M264" s="7"/>
@@ -9424,14 +9424,14 @@
         <v>13</v>
       </c>
       <c r="B265" s="7">
-        <v>122</v>
+        <v>842</v>
       </c>
       <c t="s" r="C265" s="7">
         <v>14</v>
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9440,13 +9440,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>27</v>
+        <v>187</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>249</v>
+        <v>47</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9457,63 +9457,45 @@
         <v>13</v>
       </c>
       <c r="B266" s="7">
-        <v>135</v>
+        <v>843</v>
       </c>
       <c t="s" r="C266" s="7">
         <v>14</v>
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>27</v>
+        <v>187</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>254</v>
+        <v>179</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>101</v>
+        <v>311</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c r="M266" s="7"/>
     </row>
     <row r="267" ht="14.25" customHeight="1">
-      <c t="s" r="A267" s="6">
-        <v>13</v>
-      </c>
-      <c r="B267" s="7">
-        <v>842</v>
-      </c>
-      <c t="s" r="C267" s="7">
-        <v>14</v>
-      </c>
+      <c r="A267" s="6"/>
+      <c r="B267" s="7"/>
+      <c r="C267" s="7"/>
       <c r="D267" s="7"/>
-      <c t="s" r="E267" s="7">
-        <v>308</v>
-      </c>
-      <c r="F267" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G267" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H267" s="8">
-        <v>187</v>
-      </c>
-      <c t="s" r="I267" s="7">
-        <v>56</v>
-      </c>
-      <c t="s" r="J267" s="7">
-        <v>47</v>
-      </c>
+      <c r="E267" s="7"/>
+      <c r="F267" s="7"/>
+      <c r="G267" s="8"/>
+      <c r="H267" s="8"/>
+      <c r="I267" s="7"/>
+      <c r="J267" s="7"/>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c r="M267" s="7"/>
@@ -9523,45 +9505,63 @@
         <v>13</v>
       </c>
       <c r="B268" s="7">
-        <v>843</v>
+        <v>447</v>
       </c>
       <c t="s" r="C268" s="7">
         <v>14</v>
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F268" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>187</v>
+        <v>27</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>309</v>
+        <v>242</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c r="M268" s="7"/>
     </row>
     <row r="269" ht="14.25" customHeight="1">
-      <c r="A269" s="6"/>
-      <c r="B269" s="7"/>
-      <c r="C269" s="7"/>
+      <c t="s" r="A269" s="6">
+        <v>13</v>
+      </c>
+      <c r="B269" s="7">
+        <v>440</v>
+      </c>
+      <c t="s" r="C269" s="7">
+        <v>14</v>
+      </c>
       <c r="D269" s="7"/>
-      <c r="E269" s="7"/>
-      <c r="F269" s="7"/>
-      <c r="G269" s="8"/>
-      <c r="H269" s="8"/>
-      <c r="I269" s="7"/>
-      <c r="J269" s="7"/>
+      <c t="s" r="E269" s="7">
+        <v>312</v>
+      </c>
+      <c r="F269" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G269" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="H269" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="I269" s="7">
+        <v>313</v>
+      </c>
+      <c t="s" r="J269" s="7">
+        <v>56</v>
+      </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c r="M269" s="7"/>
@@ -9571,14 +9571,14 @@
         <v>13</v>
       </c>
       <c r="B270" s="7">
-        <v>447</v>
+        <v>903</v>
       </c>
       <c t="s" r="C270" s="7">
         <v>14</v>
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
@@ -9587,13 +9587,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>20</v>
+        <v>261</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>242</v>
+        <v>24</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9604,29 +9604,29 @@
         <v>13</v>
       </c>
       <c r="B271" s="7">
-        <v>440</v>
+        <v>904</v>
       </c>
       <c t="s" r="C271" s="7">
         <v>14</v>
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F271" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>20</v>
+        <v>261</v>
       </c>
       <c t="s" r="H271" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>311</v>
+        <v>239</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>56</v>
+        <v>314</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9634,17 +9634,17 @@
     </row>
     <row r="272" ht="14.25" customHeight="1">
       <c t="s" r="A272" s="6">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B272" s="7">
-        <v>903</v>
+        <v>1980</v>
       </c>
       <c t="s" r="C272" s="7">
         <v>14</v>
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
@@ -9653,95 +9653,95 @@
         <v>27</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>261</v>
+        <v>315</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>110</v>
+        <v>316</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c r="M272" s="7"/>
     </row>
     <row r="273" ht="14.25" customHeight="1">
-      <c t="s" r="A273" s="6">
-        <v>13</v>
-      </c>
-      <c r="B273" s="7">
-        <v>904</v>
-      </c>
-      <c t="s" r="C273" s="7">
-        <v>14</v>
-      </c>
+      <c r="A273" s="6"/>
+      <c r="B273" s="7"/>
+      <c r="C273" s="7"/>
       <c r="D273" s="7"/>
-      <c t="s" r="E273" s="7">
-        <v>310</v>
-      </c>
-      <c r="F273" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G273" s="8">
-        <v>261</v>
-      </c>
-      <c t="s" r="H273" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="I273" s="7">
-        <v>239</v>
-      </c>
-      <c t="s" r="J273" s="7">
-        <v>312</v>
-      </c>
+      <c r="E273" s="7"/>
+      <c r="F273" s="7"/>
+      <c r="G273" s="8"/>
+      <c r="H273" s="8"/>
+      <c r="I273" s="7"/>
+      <c r="J273" s="7"/>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c r="M273" s="7"/>
     </row>
     <row r="274" ht="14.25" customHeight="1">
       <c t="s" r="A274" s="6">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B274" s="7">
-        <v>1980</v>
+        <v>126</v>
       </c>
       <c t="s" r="C274" s="7">
         <v>14</v>
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="F274" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G274" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H274" s="8">
         <v>27</v>
       </c>
-      <c t="s" r="H274" s="8">
-        <v>313</v>
-      </c>
       <c t="s" r="I274" s="7">
-        <v>314</v>
+        <v>85</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>18</v>
+        <v>162</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c r="M274" s="7"/>
     </row>
     <row r="275" ht="15" customHeight="1">
-      <c r="A275" s="6"/>
-      <c r="B275" s="7"/>
-      <c r="C275" s="7"/>
+      <c t="s" r="A275" s="6">
+        <v>13</v>
+      </c>
+      <c r="B275" s="7">
+        <v>1491</v>
+      </c>
+      <c t="s" r="C275" s="7">
+        <v>14</v>
+      </c>
       <c r="D275" s="7"/>
-      <c r="E275" s="7"/>
-      <c r="F275" s="7"/>
-      <c r="G275" s="8"/>
-      <c r="H275" s="8"/>
-      <c r="I275" s="7"/>
-      <c r="J275" s="7"/>
+      <c t="s" r="E275" s="7">
+        <v>317</v>
+      </c>
+      <c r="F275" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G275" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H275" s="8">
+        <v>83</v>
+      </c>
+      <c t="s" r="I275" s="7">
+        <v>318</v>
+      </c>
+      <c t="s" r="J275" s="7">
+        <v>250</v>
+      </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c r="M275" s="7"/>
@@ -9751,29 +9751,29 @@
         <v>13</v>
       </c>
       <c r="B276" s="7">
-        <v>126</v>
+        <v>1492</v>
       </c>
       <c t="s" r="C276" s="7">
         <v>14</v>
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>162</v>
+        <v>218</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9784,14 +9784,14 @@
         <v>13</v>
       </c>
       <c r="B277" s="7">
-        <v>1491</v>
+        <v>511</v>
       </c>
       <c t="s" r="C277" s="7">
         <v>14</v>
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -9800,13 +9800,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>316</v>
+        <v>76</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>250</v>
+        <v>182</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -9817,29 +9817,29 @@
         <v>13</v>
       </c>
       <c r="B278" s="7">
-        <v>1492</v>
+        <v>512</v>
       </c>
       <c t="s" r="C278" s="7">
         <v>14</v>
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>218</v>
+        <v>119</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -9850,14 +9850,14 @@
         <v>13</v>
       </c>
       <c r="B279" s="7">
-        <v>511</v>
+        <v>1127</v>
       </c>
       <c t="s" r="C279" s="7">
         <v>14</v>
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -9866,13 +9866,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>182</v>
+        <v>295</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -9883,63 +9883,45 @@
         <v>13</v>
       </c>
       <c r="B280" s="7">
-        <v>512</v>
+        <v>1128</v>
       </c>
       <c t="s" r="C280" s="7">
         <v>14</v>
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>130</v>
+        <v>319</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>119</v>
+        <v>320</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c r="M280" s="7"/>
     </row>
     <row r="281" ht="14.25" customHeight="1">
-      <c t="s" r="A281" s="6">
-        <v>13</v>
-      </c>
-      <c r="B281" s="7">
-        <v>1127</v>
-      </c>
-      <c t="s" r="C281" s="7">
-        <v>14</v>
-      </c>
+      <c r="A281" s="6"/>
+      <c r="B281" s="7"/>
+      <c r="C281" s="7"/>
       <c r="D281" s="7"/>
-      <c t="s" r="E281" s="7">
-        <v>315</v>
-      </c>
-      <c r="F281" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G281" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H281" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I281" s="7">
-        <v>104</v>
-      </c>
-      <c t="s" r="J281" s="7">
-        <v>317</v>
-      </c>
+      <c r="E281" s="7"/>
+      <c r="F281" s="7"/>
+      <c r="G281" s="8"/>
+      <c r="H281" s="8"/>
+      <c r="I281" s="7"/>
+      <c r="J281" s="7"/>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c r="M281" s="7"/>
@@ -9949,45 +9931,63 @@
         <v>13</v>
       </c>
       <c r="B282" s="7">
-        <v>1128</v>
+        <v>801</v>
       </c>
       <c t="s" r="C282" s="7">
         <v>14</v>
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="F282" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G282" s="8">
         <v>17</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>27</v>
+        <v>261</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>318</v>
+        <v>274</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c r="M282" s="7"/>
     </row>
     <row r="283" ht="14.25" customHeight="1">
-      <c r="A283" s="6"/>
-      <c r="B283" s="7"/>
-      <c r="C283" s="7"/>
+      <c t="s" r="A283" s="6">
+        <v>13</v>
+      </c>
+      <c r="B283" s="7">
+        <v>802</v>
+      </c>
+      <c t="s" r="C283" s="7">
+        <v>14</v>
+      </c>
       <c r="D283" s="7"/>
-      <c r="E283" s="7"/>
-      <c r="F283" s="7"/>
-      <c r="G283" s="8"/>
-      <c r="H283" s="8"/>
-      <c r="I283" s="7"/>
-      <c r="J283" s="7"/>
+      <c t="s" r="E283" s="7">
+        <v>321</v>
+      </c>
+      <c r="F283" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G283" s="8">
+        <v>261</v>
+      </c>
+      <c t="s" r="H283" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I283" s="7">
+        <v>215</v>
+      </c>
+      <c t="s" r="J283" s="7">
+        <v>19</v>
+      </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c r="M283" s="7"/>
@@ -9997,14 +9997,14 @@
         <v>13</v>
       </c>
       <c r="B284" s="7">
-        <v>801</v>
+        <v>3674</v>
       </c>
       <c t="s" r="C284" s="7">
         <v>14</v>
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10013,13 +10013,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>261</v>
+        <v>323</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>274</v>
+        <v>67</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>321</v>
+        <v>179</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10030,63 +10030,45 @@
         <v>13</v>
       </c>
       <c r="B285" s="7">
-        <v>802</v>
+        <v>3675</v>
       </c>
       <c t="s" r="C285" s="7">
         <v>14</v>
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>261</v>
+        <v>323</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>215</v>
+        <v>134</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c r="M285" s="7"/>
     </row>
     <row r="286" ht="14.25" customHeight="1">
-      <c t="s" r="A286" s="6">
-        <v>13</v>
-      </c>
-      <c r="B286" s="7">
-        <v>3674</v>
-      </c>
-      <c t="s" r="C286" s="7">
-        <v>14</v>
-      </c>
+      <c r="A286" s="6"/>
+      <c r="B286" s="7"/>
+      <c r="C286" s="7"/>
       <c r="D286" s="7"/>
-      <c t="s" r="E286" s="7">
-        <v>320</v>
-      </c>
-      <c r="F286" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G286" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H286" s="8">
-        <v>322</v>
-      </c>
-      <c t="s" r="I286" s="7">
-        <v>67</v>
-      </c>
-      <c t="s" r="J286" s="7">
-        <v>179</v>
-      </c>
+      <c r="E286" s="7"/>
+      <c r="F286" s="7"/>
+      <c r="G286" s="8"/>
+      <c r="H286" s="8"/>
+      <c r="I286" s="7"/>
+      <c r="J286" s="7"/>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c r="M286" s="7"/>
@@ -10096,45 +10078,63 @@
         <v>13</v>
       </c>
       <c r="B287" s="7">
-        <v>3675</v>
+        <v>879</v>
       </c>
       <c t="s" r="C287" s="7">
         <v>14</v>
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F287" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>322</v>
+        <v>23</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>59</v>
+        <v>162</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c r="M287" s="7"/>
     </row>
     <row r="288" ht="14.25" customHeight="1">
-      <c r="A288" s="6"/>
-      <c r="B288" s="7"/>
-      <c r="C288" s="7"/>
+      <c t="s" r="A288" s="6">
+        <v>13</v>
+      </c>
+      <c r="B288" s="7">
+        <v>973</v>
+      </c>
+      <c t="s" r="C288" s="7">
+        <v>14</v>
+      </c>
       <c r="D288" s="7"/>
-      <c r="E288" s="7"/>
-      <c r="F288" s="7"/>
-      <c r="G288" s="8"/>
-      <c r="H288" s="8"/>
-      <c r="I288" s="7"/>
-      <c r="J288" s="7"/>
+      <c t="s" r="E288" s="7">
+        <v>324</v>
+      </c>
+      <c r="F288" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G288" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="H288" s="8">
+        <v>106</v>
+      </c>
+      <c t="s" r="I288" s="7">
+        <v>164</v>
+      </c>
+      <c t="s" r="J288" s="7">
+        <v>130</v>
+      </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c r="M288" s="7"/>
@@ -10144,29 +10144,29 @@
         <v>13</v>
       </c>
       <c r="B289" s="7">
-        <v>879</v>
+        <v>814</v>
       </c>
       <c t="s" r="C289" s="7">
         <v>14</v>
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>23</v>
+        <v>106</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>160</v>
+        <v>280</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10177,63 +10177,45 @@
         <v>13</v>
       </c>
       <c r="B290" s="7">
-        <v>973</v>
+        <v>646</v>
       </c>
       <c t="s" r="C290" s="7">
         <v>14</v>
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H290" s="8">
         <v>41</v>
       </c>
-      <c t="s" r="H290" s="8">
-        <v>106</v>
-      </c>
       <c t="s" r="I290" s="7">
-        <v>164</v>
+        <v>277</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>130</v>
+        <v>325</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c r="M290" s="7"/>
     </row>
     <row r="291" ht="14.25" customHeight="1">
-      <c t="s" r="A291" s="6">
-        <v>13</v>
-      </c>
-      <c r="B291" s="7">
-        <v>814</v>
-      </c>
-      <c t="s" r="C291" s="7">
-        <v>14</v>
-      </c>
+      <c r="A291" s="6"/>
+      <c r="B291" s="7"/>
+      <c r="C291" s="7"/>
       <c r="D291" s="7"/>
-      <c t="s" r="E291" s="7">
-        <v>323</v>
-      </c>
-      <c r="F291" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G291" s="8">
-        <v>106</v>
-      </c>
-      <c t="s" r="H291" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I291" s="7">
-        <v>280</v>
-      </c>
-      <c t="s" r="J291" s="7">
-        <v>179</v>
-      </c>
+      <c r="E291" s="7"/>
+      <c r="F291" s="7"/>
+      <c r="G291" s="8"/>
+      <c r="H291" s="8"/>
+      <c r="I291" s="7"/>
+      <c r="J291" s="7"/>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c r="M291" s="7"/>
@@ -10243,45 +10225,63 @@
         <v>13</v>
       </c>
       <c r="B292" s="7">
-        <v>646</v>
+        <v>451</v>
       </c>
       <c t="s" r="C292" s="7">
         <v>14</v>
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F292" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>277</v>
+        <v>231</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>324</v>
+        <v>272</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c r="M292" s="7"/>
     </row>
     <row r="293" ht="14.25" customHeight="1">
-      <c r="A293" s="6"/>
-      <c r="B293" s="7"/>
-      <c r="C293" s="7"/>
+      <c t="s" r="A293" s="6">
+        <v>13</v>
+      </c>
+      <c r="B293" s="7">
+        <v>454</v>
+      </c>
+      <c t="s" r="C293" s="7">
+        <v>14</v>
+      </c>
       <c r="D293" s="7"/>
-      <c r="E293" s="7"/>
-      <c r="F293" s="7"/>
-      <c r="G293" s="8"/>
-      <c r="H293" s="8"/>
-      <c r="I293" s="7"/>
-      <c r="J293" s="7"/>
+      <c t="s" r="E293" s="7">
+        <v>326</v>
+      </c>
+      <c r="F293" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G293" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="H293" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="I293" s="7">
+        <v>67</v>
+      </c>
+      <c t="s" r="J293" s="7">
+        <v>327</v>
+      </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c r="M293" s="7"/>
@@ -10291,14 +10291,14 @@
         <v>13</v>
       </c>
       <c r="B294" s="7">
-        <v>451</v>
+        <v>495</v>
       </c>
       <c t="s" r="C294" s="7">
         <v>14</v>
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10307,13 +10307,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>231</v>
+        <v>183</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10324,63 +10324,45 @@
         <v>13</v>
       </c>
       <c r="B295" s="7">
-        <v>454</v>
+        <v>496</v>
       </c>
       <c t="s" r="C295" s="7">
         <v>14</v>
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>67</v>
+        <v>328</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>326</v>
+        <v>295</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c r="M295" s="7"/>
     </row>
     <row r="296" ht="14.25" customHeight="1">
-      <c t="s" r="A296" s="6">
-        <v>13</v>
-      </c>
-      <c r="B296" s="7">
-        <v>495</v>
-      </c>
-      <c t="s" r="C296" s="7">
-        <v>14</v>
-      </c>
+      <c r="A296" s="6"/>
+      <c r="B296" s="7"/>
+      <c r="C296" s="7"/>
       <c r="D296" s="7"/>
-      <c t="s" r="E296" s="7">
-        <v>325</v>
-      </c>
-      <c r="F296" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G296" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H296" s="8">
-        <v>83</v>
-      </c>
-      <c t="s" r="I296" s="7">
-        <v>183</v>
-      </c>
-      <c t="s" r="J296" s="7">
-        <v>256</v>
-      </c>
+      <c r="E296" s="7"/>
+      <c r="F296" s="7"/>
+      <c r="G296" s="8"/>
+      <c r="H296" s="8"/>
+      <c r="I296" s="7"/>
+      <c r="J296" s="7"/>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c r="M296" s="7"/>
@@ -10390,45 +10372,63 @@
         <v>13</v>
       </c>
       <c r="B297" s="7">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c t="s" r="C297" s="7">
         <v>14</v>
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>327</v>
+        <v>147</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>317</v>
+        <v>30</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c r="M297" s="7"/>
     </row>
     <row r="298" ht="14.25" customHeight="1">
-      <c r="A298" s="6"/>
-      <c r="B298" s="7"/>
-      <c r="C298" s="7"/>
+      <c t="s" r="A298" s="6">
+        <v>13</v>
+      </c>
+      <c r="B298" s="7">
+        <v>510</v>
+      </c>
+      <c t="s" r="C298" s="7">
+        <v>14</v>
+      </c>
       <c r="D298" s="7"/>
-      <c r="E298" s="7"/>
-      <c r="F298" s="7"/>
-      <c r="G298" s="8"/>
-      <c r="H298" s="8"/>
-      <c r="I298" s="7"/>
-      <c r="J298" s="7"/>
+      <c t="s" r="E298" s="7">
+        <v>329</v>
+      </c>
+      <c r="F298" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G298" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="H298" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="I298" s="7">
+        <v>91</v>
+      </c>
+      <c t="s" r="J298" s="7">
+        <v>67</v>
+      </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c r="M298" s="7"/>
@@ -10438,14 +10438,14 @@
         <v>13</v>
       </c>
       <c r="B299" s="7">
-        <v>507</v>
+        <v>439</v>
       </c>
       <c t="s" r="C299" s="7">
         <v>14</v>
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10454,13 +10454,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>41</v>
+        <v>300</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>30</v>
+        <v>167</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10471,29 +10471,29 @@
         <v>13</v>
       </c>
       <c r="B300" s="7">
-        <v>510</v>
+        <v>438</v>
       </c>
       <c t="s" r="C300" s="7">
         <v>14</v>
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>41</v>
+        <v>300</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10504,14 +10504,14 @@
         <v>13</v>
       </c>
       <c r="B301" s="7">
-        <v>439</v>
+        <v>163</v>
       </c>
       <c t="s" r="C301" s="7">
         <v>14</v>
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -10520,47 +10520,29 @@
         <v>27</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>298</v>
+        <v>17</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>78</v>
+        <v>311</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>167</v>
+        <v>114</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
       <c r="M301" s="7"/>
     </row>
     <row r="302" ht="14.25" customHeight="1">
-      <c t="s" r="A302" s="6">
-        <v>13</v>
-      </c>
-      <c r="B302" s="7">
-        <v>438</v>
-      </c>
-      <c t="s" r="C302" s="7">
-        <v>14</v>
-      </c>
+      <c r="A302" s="6"/>
+      <c r="B302" s="7"/>
+      <c r="C302" s="7"/>
       <c r="D302" s="7"/>
-      <c t="s" r="E302" s="7">
-        <v>328</v>
-      </c>
-      <c r="F302" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G302" s="8">
-        <v>298</v>
-      </c>
-      <c t="s" r="H302" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="I302" s="7">
-        <v>24</v>
-      </c>
-      <c t="s" r="J302" s="7">
-        <v>49</v>
-      </c>
+      <c r="E302" s="7"/>
+      <c r="F302" s="7"/>
+      <c r="G302" s="8"/>
+      <c r="H302" s="8"/>
+      <c r="I302" s="7"/>
+      <c r="J302" s="7"/>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
       <c r="M302" s="7"/>
@@ -10570,45 +10552,63 @@
         <v>13</v>
       </c>
       <c r="B303" s="7">
-        <v>163</v>
+        <v>905</v>
       </c>
       <c t="s" r="C303" s="7">
         <v>14</v>
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F303" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G303" s="8">
         <v>27</v>
       </c>
       <c t="s" r="H303" s="8">
-        <v>17</v>
+        <v>217</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>309</v>
+        <v>176</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>114</v>
+        <v>215</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
       <c r="M303" s="7"/>
     </row>
     <row r="304" ht="14.25" customHeight="1">
-      <c r="A304" s="6"/>
-      <c r="B304" s="7"/>
-      <c r="C304" s="7"/>
+      <c t="s" r="A304" s="6">
+        <v>13</v>
+      </c>
+      <c r="B304" s="7">
+        <v>906</v>
+      </c>
+      <c t="s" r="C304" s="7">
+        <v>14</v>
+      </c>
       <c r="D304" s="7"/>
-      <c r="E304" s="7"/>
-      <c r="F304" s="7"/>
-      <c r="G304" s="8"/>
-      <c r="H304" s="8"/>
-      <c r="I304" s="7"/>
-      <c r="J304" s="7"/>
+      <c t="s" r="E304" s="7">
+        <v>330</v>
+      </c>
+      <c r="F304" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G304" s="8">
+        <v>217</v>
+      </c>
+      <c t="s" r="H304" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="I304" s="7">
+        <v>30</v>
+      </c>
+      <c t="s" r="J304" s="7">
+        <v>235</v>
+      </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c r="M304" s="7"/>
@@ -10618,14 +10618,14 @@
         <v>13</v>
       </c>
       <c r="B305" s="7">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c t="s" r="C305" s="7">
         <v>14</v>
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -10634,13 +10634,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>217</v>
+        <v>331</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>176</v>
+        <v>128</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>215</v>
+        <v>332</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10651,29 +10651,29 @@
         <v>13</v>
       </c>
       <c r="B306" s="7">
-        <v>906</v>
+        <v>914</v>
       </c>
       <c t="s" r="C306" s="7">
         <v>14</v>
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>217</v>
+        <v>331</v>
       </c>
       <c t="s" r="H306" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>30</v>
+        <v>168</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>235</v>
+        <v>333</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10684,14 +10684,14 @@
         <v>13</v>
       </c>
       <c r="B307" s="7">
-        <v>913</v>
+        <v>7526</v>
       </c>
       <c t="s" r="C307" s="7">
         <v>14</v>
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -10700,13 +10700,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>128</v>
+        <v>278</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>331</v>
+        <v>25</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10714,114 +10714,114 @@
     </row>
     <row r="308" ht="14.25" customHeight="1">
       <c t="s" r="A308" s="6">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B308" s="7">
-        <v>914</v>
+        <v>7527</v>
       </c>
       <c t="s" r="C308" s="7">
         <v>14</v>
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c t="s" r="H308" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>168</v>
+        <v>335</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c r="M308" s="7"/>
     </row>
     <row r="309" ht="14.25" customHeight="1">
-      <c t="s" r="A309" s="6">
-        <v>13</v>
-      </c>
-      <c r="B309" s="7">
-        <v>7526</v>
-      </c>
-      <c t="s" r="C309" s="7">
-        <v>14</v>
-      </c>
+      <c r="A309" s="6"/>
+      <c r="B309" s="7"/>
+      <c r="C309" s="7"/>
       <c r="D309" s="7"/>
-      <c t="s" r="E309" s="7">
-        <v>329</v>
-      </c>
-      <c r="F309" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G309" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H309" s="8">
-        <v>333</v>
-      </c>
-      <c t="s" r="I309" s="7">
-        <v>278</v>
-      </c>
-      <c t="s" r="J309" s="7">
-        <v>25</v>
-      </c>
+      <c r="E309" s="7"/>
+      <c r="F309" s="7"/>
+      <c r="G309" s="8"/>
+      <c r="H309" s="8"/>
+      <c r="I309" s="7"/>
+      <c r="J309" s="7"/>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c r="M309" s="7"/>
     </row>
     <row r="310" ht="15" customHeight="1">
       <c t="s" r="A310" s="6">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B310" s="7">
-        <v>7527</v>
+        <v>1729</v>
       </c>
       <c t="s" r="C310" s="7">
         <v>14</v>
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="F310" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>333</v>
+        <v>41</v>
       </c>
       <c t="s" r="H310" s="8">
-        <v>27</v>
+        <v>302</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>334</v>
+        <v>43</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>335</v>
+        <v>245</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c r="M310" s="7"/>
     </row>
     <row r="311" ht="14.25" customHeight="1">
-      <c r="A311" s="6"/>
-      <c r="B311" s="7"/>
-      <c r="C311" s="7"/>
+      <c t="s" r="A311" s="6">
+        <v>13</v>
+      </c>
+      <c r="B311" s="7">
+        <v>1728</v>
+      </c>
+      <c t="s" r="C311" s="7">
+        <v>14</v>
+      </c>
       <c r="D311" s="7"/>
-      <c r="E311" s="7"/>
-      <c r="F311" s="7"/>
-      <c r="G311" s="8"/>
-      <c r="H311" s="8"/>
-      <c r="I311" s="7"/>
-      <c r="J311" s="7"/>
+      <c t="s" r="E311" s="7">
+        <v>337</v>
+      </c>
+      <c r="F311" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G311" s="8">
+        <v>302</v>
+      </c>
+      <c t="s" r="H311" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I311" s="7">
+        <v>262</v>
+      </c>
+      <c t="s" r="J311" s="7">
+        <v>130</v>
+      </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c r="M311" s="7"/>
@@ -10831,14 +10831,14 @@
         <v>13</v>
       </c>
       <c r="B312" s="7">
-        <v>1729</v>
+        <v>526</v>
       </c>
       <c t="s" r="C312" s="7">
         <v>14</v>
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -10847,47 +10847,29 @@
         <v>41</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>300</v>
+        <v>27</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>43</v>
+        <v>338</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>245</v>
+        <v>59</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c r="M312" s="7"/>
     </row>
     <row r="313" ht="14.25" customHeight="1">
-      <c t="s" r="A313" s="6">
-        <v>13</v>
-      </c>
-      <c r="B313" s="7">
-        <v>1728</v>
-      </c>
-      <c t="s" r="C313" s="7">
-        <v>14</v>
-      </c>
+      <c r="A313" s="6"/>
+      <c r="B313" s="7"/>
+      <c r="C313" s="7"/>
       <c r="D313" s="7"/>
-      <c t="s" r="E313" s="7">
-        <v>336</v>
-      </c>
-      <c r="F313" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G313" s="8">
-        <v>300</v>
-      </c>
-      <c t="s" r="H313" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I313" s="7">
-        <v>262</v>
-      </c>
-      <c t="s" r="J313" s="7">
-        <v>130</v>
-      </c>
+      <c r="E313" s="7"/>
+      <c r="F313" s="7"/>
+      <c r="G313" s="8"/>
+      <c r="H313" s="8"/>
+      <c r="I313" s="7"/>
+      <c r="J313" s="7"/>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c r="M313" s="7"/>
@@ -10897,45 +10879,63 @@
         <v>13</v>
       </c>
       <c r="B314" s="7">
-        <v>526</v>
+        <v>270</v>
       </c>
       <c t="s" r="C314" s="7">
         <v>14</v>
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F314" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>337</v>
+        <v>175</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c r="M314" s="7"/>
     </row>
     <row r="315" ht="15" customHeight="1">
-      <c r="A315" s="6"/>
-      <c r="B315" s="7"/>
-      <c r="C315" s="7"/>
+      <c t="s" r="A315" s="6">
+        <v>13</v>
+      </c>
+      <c r="B315" s="7">
+        <v>271</v>
+      </c>
+      <c t="s" r="C315" s="7">
+        <v>14</v>
+      </c>
       <c r="D315" s="7"/>
-      <c r="E315" s="7"/>
-      <c r="F315" s="7"/>
-      <c r="G315" s="8"/>
-      <c r="H315" s="8"/>
-      <c r="I315" s="7"/>
-      <c r="J315" s="7"/>
+      <c t="s" r="E315" s="7">
+        <v>339</v>
+      </c>
+      <c r="F315" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G315" s="8">
+        <v>102</v>
+      </c>
+      <c t="s" r="H315" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I315" s="7">
+        <v>86</v>
+      </c>
+      <c t="s" r="J315" s="7">
+        <v>340</v>
+      </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c r="M315" s="7"/>
@@ -10945,14 +10945,14 @@
         <v>13</v>
       </c>
       <c r="B316" s="7">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c t="s" r="C316" s="7">
         <v>14</v>
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -10961,13 +10961,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>175</v>
+        <v>341</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -10978,29 +10978,29 @@
         <v>13</v>
       </c>
       <c r="B317" s="7">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c t="s" r="C317" s="7">
         <v>14</v>
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>86</v>
+        <v>308</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>339</v>
+        <v>255</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11011,29 +11011,29 @@
         <v>13</v>
       </c>
       <c r="B318" s="7">
-        <v>252</v>
+        <v>3908</v>
       </c>
       <c t="s" r="C318" s="7">
         <v>14</v>
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
+        <v>339</v>
+      </c>
+      <c r="F318" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G318" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H318" s="8">
+        <v>334</v>
+      </c>
+      <c t="s" r="I318" s="7">
         <v>338</v>
       </c>
-      <c r="F318" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G318" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H318" s="8">
-        <v>88</v>
-      </c>
-      <c t="s" r="I318" s="7">
-        <v>340</v>
-      </c>
       <c t="s" r="J318" s="7">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11041,114 +11041,114 @@
     </row>
     <row r="319" ht="14.25" customHeight="1">
       <c t="s" r="A319" s="6">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B319" s="7">
-        <v>253</v>
+        <v>3909</v>
       </c>
       <c t="s" r="C319" s="7">
         <v>14</v>
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>88</v>
+        <v>334</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>306</v>
+        <v>343</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>255</v>
+        <v>344</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c r="M319" s="7"/>
     </row>
     <row r="320" ht="15" customHeight="1">
-      <c t="s" r="A320" s="6">
-        <v>13</v>
-      </c>
-      <c r="B320" s="7">
-        <v>3908</v>
-      </c>
-      <c t="s" r="C320" s="7">
-        <v>14</v>
-      </c>
+      <c r="A320" s="6"/>
+      <c r="B320" s="7"/>
+      <c r="C320" s="7"/>
       <c r="D320" s="7"/>
-      <c t="s" r="E320" s="7">
-        <v>338</v>
-      </c>
-      <c r="F320" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G320" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H320" s="8">
-        <v>333</v>
-      </c>
-      <c t="s" r="I320" s="7">
-        <v>337</v>
-      </c>
-      <c t="s" r="J320" s="7">
-        <v>341</v>
-      </c>
+      <c r="E320" s="7"/>
+      <c r="F320" s="7"/>
+      <c r="G320" s="8"/>
+      <c r="H320" s="8"/>
+      <c r="I320" s="7"/>
+      <c r="J320" s="7"/>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c r="M320" s="7"/>
     </row>
     <row r="321" ht="14.25" customHeight="1">
       <c t="s" r="A321" s="6">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B321" s="7">
-        <v>3909</v>
+        <v>382</v>
       </c>
       <c t="s" r="C321" s="7">
         <v>14</v>
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="F321" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>333</v>
+        <v>17</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>17</v>
+        <v>300</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>343</v>
+        <v>55</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c r="M321" s="7"/>
     </row>
     <row r="322" ht="14.25" customHeight="1">
-      <c r="A322" s="6"/>
-      <c r="B322" s="7"/>
-      <c r="C322" s="7"/>
+      <c t="s" r="A322" s="6">
+        <v>13</v>
+      </c>
+      <c r="B322" s="7">
+        <v>383</v>
+      </c>
+      <c t="s" r="C322" s="7">
+        <v>14</v>
+      </c>
       <c r="D322" s="7"/>
-      <c r="E322" s="7"/>
-      <c r="F322" s="7"/>
-      <c r="G322" s="8"/>
-      <c r="H322" s="8"/>
-      <c r="I322" s="7"/>
-      <c r="J322" s="7"/>
+      <c t="s" r="E322" s="7">
+        <v>345</v>
+      </c>
+      <c r="F322" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G322" s="8">
+        <v>300</v>
+      </c>
+      <c t="s" r="H322" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I322" s="7">
+        <v>322</v>
+      </c>
+      <c t="s" r="J322" s="7">
+        <v>147</v>
+      </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c r="M322" s="7"/>
@@ -11158,14 +11158,14 @@
         <v>13</v>
       </c>
       <c r="B323" s="7">
-        <v>382</v>
+        <v>210</v>
       </c>
       <c t="s" r="C323" s="7">
         <v>14</v>
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11174,13 +11174,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>298</v>
+        <v>269</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>345</v>
+        <v>148</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11191,29 +11191,29 @@
         <v>13</v>
       </c>
       <c r="B324" s="7">
-        <v>383</v>
+        <v>211</v>
       </c>
       <c t="s" r="C324" s="7">
         <v>14</v>
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>298</v>
+        <v>269</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>321</v>
+        <v>118</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>147</v>
+        <v>262</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11224,14 +11224,14 @@
         <v>13</v>
       </c>
       <c r="B325" s="7">
-        <v>210</v>
+        <v>805</v>
       </c>
       <c t="s" r="C325" s="7">
         <v>14</v>
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11240,13 +11240,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>56</v>
+        <v>239</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11257,29 +11257,29 @@
         <v>13</v>
       </c>
       <c r="B326" s="7">
-        <v>211</v>
+        <v>806</v>
       </c>
       <c t="s" r="C326" s="7">
         <v>14</v>
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>118</v>
+        <v>266</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>262</v>
+        <v>311</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11290,14 +11290,14 @@
         <v>13</v>
       </c>
       <c r="B327" s="7">
-        <v>805</v>
+        <v>168</v>
       </c>
       <c t="s" r="C327" s="7">
         <v>14</v>
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11306,47 +11306,29 @@
         <v>17</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>261</v>
+        <v>27</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>239</v>
+        <v>347</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
       <c r="M327" s="7"/>
     </row>
     <row r="328" ht="14.25" customHeight="1">
-      <c t="s" r="A328" s="6">
-        <v>13</v>
-      </c>
-      <c r="B328" s="7">
-        <v>806</v>
-      </c>
-      <c t="s" r="C328" s="7">
-        <v>14</v>
-      </c>
+      <c r="A328" s="6"/>
+      <c r="B328" s="7"/>
+      <c r="C328" s="7"/>
       <c r="D328" s="7"/>
-      <c t="s" r="E328" s="7">
-        <v>344</v>
-      </c>
-      <c r="F328" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G328" s="8">
-        <v>261</v>
-      </c>
-      <c t="s" r="H328" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I328" s="7">
-        <v>266</v>
-      </c>
-      <c t="s" r="J328" s="7">
-        <v>309</v>
-      </c>
+      <c r="E328" s="7"/>
+      <c r="F328" s="7"/>
+      <c r="G328" s="8"/>
+      <c r="H328" s="8"/>
+      <c r="I328" s="7"/>
+      <c r="J328" s="7"/>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c r="M328" s="7"/>
@@ -11356,14 +11338,14 @@
         <v>13</v>
       </c>
       <c r="B329" s="7">
-        <v>168</v>
+        <v>1372</v>
       </c>
       <c t="s" r="C329" s="7">
         <v>14</v>
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11372,29 +11354,47 @@
         <v>17</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>27</v>
+        <v>349</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>194</v>
+        <v>350</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>346</v>
+        <v>98</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c r="M329" s="7"/>
     </row>
     <row r="330" ht="15" customHeight="1">
-      <c r="A330" s="6"/>
-      <c r="B330" s="7"/>
-      <c r="C330" s="7"/>
+      <c t="s" r="A330" s="6">
+        <v>13</v>
+      </c>
+      <c r="B330" s="7">
+        <v>1373</v>
+      </c>
+      <c t="s" r="C330" s="7">
+        <v>14</v>
+      </c>
       <c r="D330" s="7"/>
-      <c r="E330" s="7"/>
-      <c r="F330" s="7"/>
-      <c r="G330" s="8"/>
-      <c r="H330" s="8"/>
-      <c r="I330" s="7"/>
-      <c r="J330" s="7"/>
+      <c t="s" r="E330" s="7">
+        <v>348</v>
+      </c>
+      <c r="F330" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G330" s="8">
+        <v>349</v>
+      </c>
+      <c t="s" r="H330" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I330" s="7">
+        <v>124</v>
+      </c>
+      <c t="s" r="J330" s="7">
+        <v>81</v>
+      </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c r="M330" s="7"/>
@@ -11404,14 +11404,14 @@
         <v>13</v>
       </c>
       <c r="B331" s="7">
-        <v>1372</v>
+        <v>372</v>
       </c>
       <c t="s" r="C331" s="7">
         <v>14</v>
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11420,13 +11420,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>349</v>
+        <v>191</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>98</v>
+        <v>230</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11437,29 +11437,29 @@
         <v>13</v>
       </c>
       <c r="B332" s="7">
-        <v>1373</v>
+        <v>373</v>
       </c>
       <c t="s" r="C332" s="7">
         <v>14</v>
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11470,14 +11470,14 @@
         <v>13</v>
       </c>
       <c r="B333" s="7">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c t="s" r="C333" s="7">
         <v>14</v>
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11486,13 +11486,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>348</v>
+        <v>302</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>191</v>
+        <v>67</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>230</v>
+        <v>156</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11503,29 +11503,29 @@
         <v>13</v>
       </c>
       <c r="B334" s="7">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c t="s" r="C334" s="7">
         <v>14</v>
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>348</v>
+        <v>302</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>147</v>
+        <v>225</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11536,14 +11536,14 @@
         <v>13</v>
       </c>
       <c r="B335" s="7">
-        <v>362</v>
+        <v>3948</v>
       </c>
       <c t="s" r="C335" s="7">
         <v>14</v>
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -11552,13 +11552,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>67</v>
+        <v>332</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>156</v>
+        <v>51</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11566,114 +11566,114 @@
     </row>
     <row r="336" ht="14.25" customHeight="1">
       <c t="s" r="A336" s="6">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B336" s="7">
-        <v>363</v>
+        <v>3949</v>
       </c>
       <c t="s" r="C336" s="7">
         <v>14</v>
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>130</v>
+        <v>234</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
       <c r="M336" s="7"/>
     </row>
     <row r="337" ht="14.25" customHeight="1">
-      <c t="s" r="A337" s="6">
-        <v>13</v>
-      </c>
-      <c r="B337" s="7">
-        <v>3948</v>
-      </c>
-      <c t="s" r="C337" s="7">
-        <v>14</v>
-      </c>
+      <c r="A337" s="6"/>
+      <c r="B337" s="7"/>
+      <c r="C337" s="7"/>
       <c r="D337" s="7"/>
-      <c t="s" r="E337" s="7">
-        <v>347</v>
-      </c>
-      <c r="F337" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G337" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H337" s="8">
-        <v>302</v>
-      </c>
-      <c t="s" r="I337" s="7">
-        <v>331</v>
-      </c>
-      <c t="s" r="J337" s="7">
-        <v>51</v>
-      </c>
+      <c r="E337" s="7"/>
+      <c r="F337" s="7"/>
+      <c r="G337" s="8"/>
+      <c r="H337" s="8"/>
+      <c r="I337" s="7"/>
+      <c r="J337" s="7"/>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c r="M337" s="7"/>
     </row>
     <row r="338" ht="14.25" customHeight="1">
       <c t="s" r="A338" s="6">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B338" s="7">
-        <v>3949</v>
+        <v>925</v>
       </c>
       <c t="s" r="C338" s="7">
         <v>14</v>
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F338" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>302</v>
+        <v>23</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>227</v>
+        <v>352</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c r="M338" s="7"/>
     </row>
     <row r="339" ht="14.25" customHeight="1">
-      <c r="A339" s="6"/>
-      <c r="B339" s="7"/>
-      <c r="C339" s="7"/>
+      <c t="s" r="A339" s="6">
+        <v>13</v>
+      </c>
+      <c r="B339" s="7">
+        <v>693</v>
+      </c>
+      <c t="s" r="C339" s="7">
+        <v>14</v>
+      </c>
       <c r="D339" s="7"/>
-      <c r="E339" s="7"/>
-      <c r="F339" s="7"/>
-      <c r="G339" s="8"/>
-      <c r="H339" s="8"/>
-      <c r="I339" s="7"/>
-      <c r="J339" s="7"/>
+      <c t="s" r="E339" s="7">
+        <v>351</v>
+      </c>
+      <c r="F339" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G339" s="8">
+        <v>102</v>
+      </c>
+      <c t="s" r="H339" s="8">
+        <v>302</v>
+      </c>
+      <c t="s" r="I339" s="7">
+        <v>308</v>
+      </c>
+      <c t="s" r="J339" s="7">
+        <v>280</v>
+      </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c r="M339" s="7"/>
@@ -11683,29 +11683,29 @@
         <v>13</v>
       </c>
       <c r="B340" s="7">
-        <v>925</v>
+        <v>692</v>
       </c>
       <c t="s" r="C340" s="7">
         <v>14</v>
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>23</v>
+        <v>302</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>102</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>351</v>
+        <v>94</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>260</v>
+        <v>226</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11716,14 +11716,14 @@
         <v>13</v>
       </c>
       <c r="B341" s="7">
-        <v>693</v>
+        <v>926</v>
       </c>
       <c t="s" r="C341" s="7">
         <v>14</v>
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -11732,47 +11732,29 @@
         <v>102</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>300</v>
+        <v>23</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>306</v>
+        <v>353</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>280</v>
+        <v>132</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c r="M341" s="7"/>
     </row>
     <row r="342" ht="14.25" customHeight="1">
-      <c t="s" r="A342" s="6">
-        <v>13</v>
-      </c>
-      <c r="B342" s="7">
-        <v>692</v>
-      </c>
-      <c t="s" r="C342" s="7">
-        <v>14</v>
-      </c>
+      <c r="A342" s="6"/>
+      <c r="B342" s="7"/>
+      <c r="C342" s="7"/>
       <c r="D342" s="7"/>
-      <c t="s" r="E342" s="7">
-        <v>350</v>
-      </c>
-      <c r="F342" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G342" s="8">
-        <v>300</v>
-      </c>
-      <c t="s" r="H342" s="8">
-        <v>102</v>
-      </c>
-      <c t="s" r="I342" s="7">
-        <v>94</v>
-      </c>
-      <c t="s" r="J342" s="7">
-        <v>226</v>
-      </c>
+      <c r="E342" s="7"/>
+      <c r="F342" s="7"/>
+      <c r="G342" s="8"/>
+      <c r="H342" s="8"/>
+      <c r="I342" s="7"/>
+      <c r="J342" s="7"/>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c r="M342" s="7"/>
@@ -11782,45 +11764,63 @@
         <v>13</v>
       </c>
       <c r="B343" s="7">
-        <v>926</v>
+        <v>401</v>
       </c>
       <c t="s" r="C343" s="7">
         <v>14</v>
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F343" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>102</v>
+        <v>27</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>23</v>
+        <v>302</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>352</v>
+        <v>160</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c r="M343" s="7"/>
     </row>
     <row r="344" ht="14.25" customHeight="1">
-      <c r="A344" s="6"/>
-      <c r="B344" s="7"/>
-      <c r="C344" s="7"/>
+      <c t="s" r="A344" s="6">
+        <v>13</v>
+      </c>
+      <c r="B344" s="7">
+        <v>798</v>
+      </c>
+      <c t="s" r="C344" s="7">
+        <v>14</v>
+      </c>
       <c r="D344" s="7"/>
-      <c r="E344" s="7"/>
-      <c r="F344" s="7"/>
-      <c r="G344" s="8"/>
-      <c r="H344" s="8"/>
-      <c r="I344" s="7"/>
-      <c r="J344" s="7"/>
+      <c t="s" r="E344" s="7">
+        <v>354</v>
+      </c>
+      <c r="F344" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G344" s="8">
+        <v>302</v>
+      </c>
+      <c t="s" r="H344" s="8">
+        <v>269</v>
+      </c>
+      <c t="s" r="I344" s="7">
+        <v>191</v>
+      </c>
+      <c t="s" r="J344" s="7">
+        <v>355</v>
+      </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c r="M344" s="7"/>
@@ -11830,29 +11830,29 @@
         <v>13</v>
       </c>
       <c r="B345" s="7">
-        <v>401</v>
+        <v>799</v>
       </c>
       <c t="s" r="C345" s="7">
         <v>14</v>
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>27</v>
+        <v>269</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>160</v>
+        <v>215</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -11863,29 +11863,29 @@
         <v>13</v>
       </c>
       <c r="B346" s="7">
-        <v>798</v>
+        <v>402</v>
       </c>
       <c t="s" r="C346" s="7">
         <v>14</v>
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c t="s" r="H346" s="8">
-        <v>269</v>
+        <v>27</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>294</v>
+        <v>166</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -11896,29 +11896,29 @@
         <v>13</v>
       </c>
       <c r="B347" s="7">
-        <v>799</v>
+        <v>405</v>
       </c>
       <c t="s" r="C347" s="7">
         <v>14</v>
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G347" s="8">
-        <v>269</v>
+        <v>27</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>215</v>
+        <v>33</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -11929,29 +11929,29 @@
         <v>13</v>
       </c>
       <c r="B348" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c t="s" r="C348" s="7">
         <v>14</v>
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -11962,14 +11962,14 @@
         <v>13</v>
       </c>
       <c r="B349" s="7">
-        <v>405</v>
+        <v>7238</v>
       </c>
       <c t="s" r="C349" s="7">
         <v>14</v>
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -11978,13 +11978,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>33</v>
+        <v>201</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>24</v>
+        <v>347</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -11992,114 +11992,114 @@
     </row>
     <row r="350" ht="15" customHeight="1">
       <c t="s" r="A350" s="6">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B350" s="7">
-        <v>406</v>
+        <v>7239</v>
       </c>
       <c t="s" r="C350" s="7">
         <v>14</v>
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>119</v>
+        <v>356</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>121</v>
+        <v>357</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c r="M350" s="7"/>
     </row>
     <row r="351" ht="14.25" customHeight="1">
-      <c t="s" r="A351" s="6">
-        <v>13</v>
-      </c>
-      <c r="B351" s="7">
-        <v>7238</v>
-      </c>
-      <c t="s" r="C351" s="7">
-        <v>14</v>
-      </c>
+      <c r="A351" s="6"/>
+      <c r="B351" s="7"/>
+      <c r="C351" s="7"/>
       <c r="D351" s="7"/>
-      <c t="s" r="E351" s="7">
-        <v>353</v>
-      </c>
-      <c r="F351" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G351" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H351" s="8">
-        <v>283</v>
-      </c>
-      <c t="s" r="I351" s="7">
-        <v>201</v>
-      </c>
-      <c t="s" r="J351" s="7">
-        <v>346</v>
-      </c>
+      <c r="E351" s="7"/>
+      <c r="F351" s="7"/>
+      <c r="G351" s="8"/>
+      <c r="H351" s="8"/>
+      <c r="I351" s="7"/>
+      <c r="J351" s="7"/>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c r="M351" s="7"/>
     </row>
     <row r="352" ht="14.25" customHeight="1">
       <c t="s" r="A352" s="6">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B352" s="7">
-        <v>7239</v>
+        <v>625</v>
       </c>
       <c t="s" r="C352" s="7">
         <v>14</v>
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F352" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>283</v>
+        <v>41</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>354</v>
+        <v>124</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>355</v>
+        <v>81</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c r="M352" s="7"/>
     </row>
     <row r="353" ht="14.25" customHeight="1">
-      <c r="A353" s="6"/>
-      <c r="B353" s="7"/>
-      <c r="C353" s="7"/>
+      <c t="s" r="A353" s="6">
+        <v>13</v>
+      </c>
+      <c r="B353" s="7">
+        <v>630</v>
+      </c>
+      <c t="s" r="C353" s="7">
+        <v>14</v>
+      </c>
       <c r="D353" s="7"/>
-      <c r="E353" s="7"/>
-      <c r="F353" s="7"/>
-      <c r="G353" s="8"/>
-      <c r="H353" s="8"/>
-      <c r="I353" s="7"/>
-      <c r="J353" s="7"/>
+      <c t="s" r="E353" s="7">
+        <v>358</v>
+      </c>
+      <c r="F353" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G353" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H353" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I353" s="7">
+        <v>87</v>
+      </c>
+      <c t="s" r="J353" s="7">
+        <v>29</v>
+      </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c r="M353" s="7"/>
@@ -12109,14 +12109,14 @@
         <v>13</v>
       </c>
       <c r="B354" s="7">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c t="s" r="C354" s="7">
         <v>14</v>
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -12128,10 +12128,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>124</v>
+        <v>242</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>81</v>
+        <v>250</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12142,14 +12142,14 @@
         <v>13</v>
       </c>
       <c r="B355" s="7">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c t="s" r="C355" s="7">
         <v>14</v>
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -12161,10 +12161,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>29</v>
+        <v>303</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12175,14 +12175,14 @@
         <v>13</v>
       </c>
       <c r="B356" s="7">
-        <v>629</v>
+        <v>878</v>
       </c>
       <c t="s" r="C356" s="7">
         <v>14</v>
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -12191,47 +12191,29 @@
         <v>41</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>242</v>
+        <v>359</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>250</v>
+        <v>173</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c r="M356" s="7"/>
     </row>
     <row r="357" ht="14.25" customHeight="1">
-      <c t="s" r="A357" s="6">
-        <v>13</v>
-      </c>
-      <c r="B357" s="7">
-        <v>636</v>
-      </c>
-      <c t="s" r="C357" s="7">
-        <v>14</v>
-      </c>
+      <c r="A357" s="6"/>
+      <c r="B357" s="7"/>
+      <c r="C357" s="7"/>
       <c r="D357" s="7"/>
-      <c t="s" r="E357" s="7">
-        <v>356</v>
-      </c>
-      <c r="F357" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G357" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H357" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I357" s="7">
-        <v>19</v>
-      </c>
-      <c t="s" r="J357" s="7">
-        <v>301</v>
-      </c>
+      <c r="E357" s="7"/>
+      <c r="F357" s="7"/>
+      <c r="G357" s="8"/>
+      <c r="H357" s="8"/>
+      <c r="I357" s="7"/>
+      <c r="J357" s="7"/>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c r="M357" s="7"/>
@@ -12241,14 +12223,14 @@
         <v>13</v>
       </c>
       <c r="B358" s="7">
-        <v>878</v>
+        <v>621</v>
       </c>
       <c t="s" r="C358" s="7">
         <v>14</v>
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12257,29 +12239,47 @@
         <v>41</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>357</v>
+        <v>267</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c r="M358" s="7"/>
     </row>
     <row r="359" ht="14.25" customHeight="1">
-      <c r="A359" s="6"/>
-      <c r="B359" s="7"/>
-      <c r="C359" s="7"/>
+      <c t="s" r="A359" s="6">
+        <v>13</v>
+      </c>
+      <c r="B359" s="7">
+        <v>632</v>
+      </c>
+      <c t="s" r="C359" s="7">
+        <v>14</v>
+      </c>
       <c r="D359" s="7"/>
-      <c r="E359" s="7"/>
-      <c r="F359" s="7"/>
-      <c r="G359" s="8"/>
-      <c r="H359" s="8"/>
-      <c r="I359" s="7"/>
-      <c r="J359" s="7"/>
+      <c t="s" r="E359" s="7">
+        <v>360</v>
+      </c>
+      <c r="F359" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G359" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H359" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I359" s="7">
+        <v>85</v>
+      </c>
+      <c t="s" r="J359" s="7">
+        <v>146</v>
+      </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c r="M359" s="7"/>
@@ -12289,14 +12289,14 @@
         <v>13</v>
       </c>
       <c r="B360" s="7">
-        <v>621</v>
+        <v>8890</v>
       </c>
       <c t="s" r="C360" s="7">
         <v>14</v>
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12305,13 +12305,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>17</v>
+        <v>264</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>160</v>
+        <v>244</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12322,29 +12322,29 @@
         <v>13</v>
       </c>
       <c r="B361" s="7">
-        <v>632</v>
+        <v>8891</v>
       </c>
       <c t="s" r="C361" s="7">
         <v>14</v>
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>17</v>
+        <v>264</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>85</v>
+        <v>262</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>146</v>
+        <v>361</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12355,14 +12355,14 @@
         <v>13</v>
       </c>
       <c r="B362" s="7">
-        <v>8890</v>
+        <v>8892</v>
       </c>
       <c t="s" r="C362" s="7">
         <v>14</v>
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12374,10 +12374,10 @@
         <v>264</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>250</v>
+        <v>119</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>244</v>
+        <v>333</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12388,14 +12388,14 @@
         <v>13</v>
       </c>
       <c r="B363" s="7">
-        <v>8891</v>
+        <v>8893</v>
       </c>
       <c t="s" r="C363" s="7">
         <v>14</v>
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12407,44 +12407,26 @@
         <v>41</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>262</v>
+        <v>362</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>359</v>
+        <v>212</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c r="M363" s="7"/>
     </row>
     <row r="364" ht="14.25" customHeight="1">
-      <c t="s" r="A364" s="6">
-        <v>13</v>
-      </c>
-      <c r="B364" s="7">
-        <v>8892</v>
-      </c>
-      <c t="s" r="C364" s="7">
-        <v>14</v>
-      </c>
+      <c r="A364" s="6"/>
+      <c r="B364" s="7"/>
+      <c r="C364" s="7"/>
       <c r="D364" s="7"/>
-      <c t="s" r="E364" s="7">
-        <v>358</v>
-      </c>
-      <c r="F364" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G364" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="H364" s="8">
-        <v>264</v>
-      </c>
-      <c t="s" r="I364" s="7">
-        <v>119</v>
-      </c>
-      <c t="s" r="J364" s="7">
-        <v>332</v>
-      </c>
+      <c r="E364" s="7"/>
+      <c r="F364" s="7"/>
+      <c r="G364" s="8"/>
+      <c r="H364" s="8"/>
+      <c r="I364" s="7"/>
+      <c r="J364" s="7"/>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c r="M364" s="7"/>
@@ -12454,45 +12436,63 @@
         <v>13</v>
       </c>
       <c r="B365" s="7">
-        <v>8893</v>
+        <v>563</v>
       </c>
       <c t="s" r="C365" s="7">
         <v>14</v>
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>264</v>
+        <v>27</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>360</v>
+        <v>191</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c r="M365" s="7"/>
     </row>
     <row r="366" ht="14.25" customHeight="1">
-      <c r="A366" s="6"/>
-      <c r="B366" s="7"/>
-      <c r="C366" s="7"/>
+      <c t="s" r="A366" s="6">
+        <v>13</v>
+      </c>
+      <c r="B366" s="7">
+        <v>564</v>
+      </c>
+      <c t="s" r="C366" s="7">
+        <v>14</v>
+      </c>
       <c r="D366" s="7"/>
-      <c r="E366" s="7"/>
-      <c r="F366" s="7"/>
-      <c r="G366" s="8"/>
-      <c r="H366" s="8"/>
-      <c r="I366" s="7"/>
-      <c r="J366" s="7"/>
+      <c t="s" r="E366" s="7">
+        <v>363</v>
+      </c>
+      <c r="F366" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G366" s="8">
+        <v>32</v>
+      </c>
+      <c t="s" r="H366" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="I366" s="7">
+        <v>238</v>
+      </c>
+      <c t="s" r="J366" s="7">
+        <v>101</v>
+      </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c r="M366" s="7"/>
@@ -12502,14 +12502,14 @@
         <v>13</v>
       </c>
       <c r="B367" s="7">
-        <v>563</v>
+        <v>948</v>
       </c>
       <c t="s" r="C367" s="7">
         <v>14</v>
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12518,13 +12518,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>32</v>
+        <v>282</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>191</v>
+        <v>56</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>206</v>
+        <v>150</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12535,29 +12535,29 @@
         <v>13</v>
       </c>
       <c r="B368" s="7">
-        <v>564</v>
+        <v>949</v>
       </c>
       <c t="s" r="C368" s="7">
         <v>14</v>
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>32</v>
+        <v>282</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>238</v>
+        <v>47</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12565,17 +12565,17 @@
     </row>
     <row r="369" ht="14.25" customHeight="1">
       <c t="s" r="A369" s="6">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B369" s="7">
-        <v>948</v>
+        <v>960</v>
       </c>
       <c t="s" r="C369" s="7">
         <v>14</v>
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12584,95 +12584,95 @@
         <v>27</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>282</v>
+        <v>23</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>56</v>
+        <v>188</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c r="M369" s="7"/>
     </row>
     <row r="370" ht="15" customHeight="1">
-      <c t="s" r="A370" s="6">
-        <v>13</v>
-      </c>
-      <c r="B370" s="7">
-        <v>949</v>
-      </c>
-      <c t="s" r="C370" s="7">
-        <v>14</v>
-      </c>
+      <c r="A370" s="6"/>
+      <c r="B370" s="7"/>
+      <c r="C370" s="7"/>
       <c r="D370" s="7"/>
-      <c t="s" r="E370" s="7">
-        <v>361</v>
-      </c>
-      <c r="F370" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G370" s="8">
-        <v>282</v>
-      </c>
-      <c t="s" r="H370" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="I370" s="7">
-        <v>47</v>
-      </c>
-      <c t="s" r="J370" s="7">
-        <v>57</v>
-      </c>
+      <c r="E370" s="7"/>
+      <c r="F370" s="7"/>
+      <c r="G370" s="8"/>
+      <c r="H370" s="8"/>
+      <c r="I370" s="7"/>
+      <c r="J370" s="7"/>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c r="M370" s="7"/>
     </row>
     <row r="371" ht="14.25" customHeight="1">
       <c t="s" r="A371" s="6">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B371" s="7">
-        <v>960</v>
+        <v>813</v>
       </c>
       <c t="s" r="C371" s="7">
         <v>14</v>
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>23</v>
+        <v>106</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>188</v>
+        <v>124</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>115</v>
+        <v>298</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c r="M371" s="7"/>
     </row>
     <row r="372" ht="14.25" customHeight="1">
-      <c r="A372" s="6"/>
-      <c r="B372" s="7"/>
-      <c r="C372" s="7"/>
+      <c t="s" r="A372" s="6">
+        <v>13</v>
+      </c>
+      <c r="B372" s="7">
+        <v>970</v>
+      </c>
+      <c t="s" r="C372" s="7">
+        <v>14</v>
+      </c>
       <c r="D372" s="7"/>
-      <c r="E372" s="7"/>
-      <c r="F372" s="7"/>
-      <c r="G372" s="8"/>
-      <c r="H372" s="8"/>
-      <c r="I372" s="7"/>
-      <c r="J372" s="7"/>
+      <c t="s" r="E372" s="7">
+        <v>364</v>
+      </c>
+      <c r="F372" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G372" s="8">
+        <v>106</v>
+      </c>
+      <c t="s" r="H372" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I372" s="7">
+        <v>275</v>
+      </c>
+      <c t="s" r="J372" s="7">
+        <v>164</v>
+      </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c r="M372" s="7"/>
@@ -12682,29 +12682,29 @@
         <v>13</v>
       </c>
       <c r="B373" s="7">
-        <v>809</v>
+        <v>633</v>
       </c>
       <c t="s" r="C373" s="7">
         <v>14</v>
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>363</v>
+        <v>17</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>146</v>
+        <v>244</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>200</v>
+        <v>308</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12715,29 +12715,29 @@
         <v>13</v>
       </c>
       <c r="B374" s="7">
-        <v>808</v>
+        <v>262</v>
       </c>
       <c t="s" r="C374" s="7">
         <v>14</v>
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>363</v>
+        <v>17</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>17</v>
+        <v>297</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>364</v>
+        <v>35</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>365</v>
+        <v>256</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12748,29 +12748,29 @@
         <v>13</v>
       </c>
       <c r="B375" s="7">
-        <v>876</v>
+        <v>263</v>
       </c>
       <c t="s" r="C375" s="7">
         <v>14</v>
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>17</v>
+        <v>297</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>366</v>
+        <v>17</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>31</v>
+        <v>328</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>69</v>
+        <v>135</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12781,29 +12781,29 @@
         <v>13</v>
       </c>
       <c r="B376" s="7">
-        <v>877</v>
+        <v>858</v>
       </c>
       <c t="s" r="C376" s="7">
         <v>14</v>
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>366</v>
+        <v>17</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>17</v>
+        <v>365</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>57</v>
+        <v>232</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -12811,81 +12811,81 @@
     </row>
     <row r="377" ht="14.25" customHeight="1">
       <c t="s" r="A377" s="6">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B377" s="7">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c t="s" r="C377" s="7">
         <v>14</v>
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>17</v>
+        <v>365</v>
       </c>
       <c t="s" r="H377" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I377" s="7">
+        <v>366</v>
+      </c>
+      <c t="s" r="J377" s="7">
         <v>367</v>
-      </c>
-      <c t="s" r="I377" s="7">
-        <v>232</v>
-      </c>
-      <c t="s" r="J377" s="7">
-        <v>334</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
       <c r="M377" s="7"/>
     </row>
     <row r="378" ht="14.25" customHeight="1">
-      <c t="s" r="A378" s="6">
-        <v>37</v>
-      </c>
-      <c r="B378" s="7">
-        <v>859</v>
-      </c>
-      <c t="s" r="C378" s="7">
-        <v>14</v>
-      </c>
+      <c r="A378" s="6"/>
+      <c r="B378" s="7"/>
+      <c r="C378" s="7"/>
       <c r="D378" s="7"/>
-      <c t="s" r="E378" s="7">
-        <v>362</v>
-      </c>
-      <c r="F378" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G378" s="8">
-        <v>367</v>
-      </c>
-      <c t="s" r="H378" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I378" s="7">
-        <v>368</v>
-      </c>
-      <c t="s" r="J378" s="7">
-        <v>369</v>
-      </c>
+      <c r="E378" s="7"/>
+      <c r="F378" s="7"/>
+      <c r="G378" s="8"/>
+      <c r="H378" s="8"/>
+      <c r="I378" s="7"/>
+      <c r="J378" s="7"/>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c r="M378" s="7"/>
     </row>
     <row r="379" ht="14.25" customHeight="1">
-      <c r="A379" s="6"/>
-      <c r="B379" s="7"/>
-      <c r="C379" s="7"/>
+      <c t="s" r="A379" s="6">
+        <v>13</v>
+      </c>
+      <c r="B379" s="7">
+        <v>121</v>
+      </c>
+      <c t="s" r="C379" s="7">
+        <v>14</v>
+      </c>
       <c r="D379" s="7"/>
-      <c r="E379" s="7"/>
-      <c r="F379" s="7"/>
-      <c r="G379" s="8"/>
-      <c r="H379" s="8"/>
-      <c r="I379" s="7"/>
-      <c r="J379" s="7"/>
+      <c t="s" r="E379" s="7">
+        <v>368</v>
+      </c>
+      <c r="F379" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G379" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H379" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I379" s="7">
+        <v>173</v>
+      </c>
+      <c t="s" r="J379" s="7">
+        <v>229</v>
+      </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c r="M379" s="7"/>
@@ -12895,29 +12895,29 @@
         <v>13</v>
       </c>
       <c r="B380" s="7">
-        <v>121</v>
+        <v>825</v>
       </c>
       <c t="s" r="C380" s="7">
         <v>14</v>
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>17</v>
+        <v>217</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>173</v>
+        <v>18</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -12928,29 +12928,29 @@
         <v>13</v>
       </c>
       <c r="B381" s="7">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c t="s" r="C381" s="7">
         <v>14</v>
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>17</v>
+        <v>217</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>217</v>
+        <v>17</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>243</v>
+        <v>303</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -12961,29 +12961,29 @@
         <v>13</v>
       </c>
       <c r="B382" s="7">
-        <v>826</v>
+        <v>152</v>
       </c>
       <c t="s" r="C382" s="7">
         <v>14</v>
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>217</v>
+        <v>17</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>301</v>
+        <v>49</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -12994,78 +12994,78 @@
         <v>13</v>
       </c>
       <c r="B383" s="7">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c t="s" r="C383" s="7">
         <v>14</v>
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>167</v>
+        <v>369</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>49</v>
+        <v>232</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c r="M383" s="7"/>
     </row>
     <row r="384" ht="14.25" customHeight="1">
-      <c t="s" r="A384" s="6">
-        <v>13</v>
-      </c>
-      <c r="B384" s="7">
-        <v>159</v>
-      </c>
-      <c t="s" r="C384" s="7">
-        <v>14</v>
-      </c>
+      <c r="A384" s="6"/>
+      <c r="B384" s="7"/>
+      <c r="C384" s="7"/>
       <c r="D384" s="7"/>
-      <c t="s" r="E384" s="7">
-        <v>370</v>
-      </c>
-      <c r="F384" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G384" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H384" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I384" s="7">
-        <v>371</v>
-      </c>
-      <c t="s" r="J384" s="7">
-        <v>232</v>
-      </c>
+      <c r="E384" s="7"/>
+      <c r="F384" s="7"/>
+      <c r="G384" s="8"/>
+      <c r="H384" s="8"/>
+      <c r="I384" s="7"/>
+      <c r="J384" s="7"/>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c r="M384" s="7"/>
     </row>
     <row r="385" ht="15" customHeight="1">
-      <c r="A385" s="6"/>
-      <c r="B385" s="7"/>
-      <c r="C385" s="7"/>
+      <c t="s" r="A385" s="6">
+        <v>13</v>
+      </c>
+      <c r="B385" s="7">
+        <v>1382</v>
+      </c>
+      <c t="s" r="C385" s="7">
+        <v>14</v>
+      </c>
       <c r="D385" s="7"/>
-      <c r="E385" s="7"/>
-      <c r="F385" s="7"/>
-      <c r="G385" s="8"/>
-      <c r="H385" s="8"/>
-      <c r="I385" s="7"/>
-      <c r="J385" s="7"/>
+      <c t="s" r="E385" s="7">
+        <v>370</v>
+      </c>
+      <c r="F385" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G385" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H385" s="8">
+        <v>300</v>
+      </c>
+      <c t="s" r="I385" s="7">
+        <v>267</v>
+      </c>
+      <c t="s" r="J385" s="7">
+        <v>73</v>
+      </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c r="M385" s="7"/>
@@ -13075,29 +13075,29 @@
         <v>13</v>
       </c>
       <c r="B386" s="7">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c t="s" r="C386" s="7">
         <v>14</v>
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>17</v>
+        <v>300</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>298</v>
+        <v>17</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>267</v>
+        <v>352</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13108,29 +13108,29 @@
         <v>13</v>
       </c>
       <c r="B387" s="7">
-        <v>1383</v>
+        <v>304</v>
       </c>
       <c t="s" r="C387" s="7">
         <v>14</v>
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G387" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H387" s="8">
+        <v>32</v>
+      </c>
+      <c t="s" r="I387" s="7">
+        <v>146</v>
+      </c>
+      <c t="s" r="J387" s="7">
         <v>298</v>
-      </c>
-      <c t="s" r="H387" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I387" s="7">
-        <v>351</v>
-      </c>
-      <c t="s" r="J387" s="7">
-        <v>99</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13141,29 +13141,29 @@
         <v>13</v>
       </c>
       <c r="B388" s="7">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c t="s" r="C388" s="7">
         <v>14</v>
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>292</v>
+        <v>223</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13174,29 +13174,29 @@
         <v>13</v>
       </c>
       <c r="B389" s="7">
-        <v>303</v>
+        <v>374</v>
       </c>
       <c t="s" r="C389" s="7">
         <v>14</v>
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G389" s="8">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>17</v>
+        <v>349</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>223</v>
+        <v>43</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13207,29 +13207,29 @@
         <v>13</v>
       </c>
       <c r="B390" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="C390" s="7">
         <v>14</v>
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>17</v>
+        <v>349</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>348</v>
+        <v>17</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13240,29 +13240,29 @@
         <v>13</v>
       </c>
       <c r="B391" s="7">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c t="s" r="C391" s="7">
         <v>14</v>
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>348</v>
+        <v>17</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>17</v>
+        <v>300</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>44</v>
+        <v>361</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13273,29 +13273,29 @@
         <v>13</v>
       </c>
       <c r="B392" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c t="s" r="C392" s="7">
         <v>14</v>
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>17</v>
+        <v>300</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>298</v>
+        <v>17</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>359</v>
+        <v>119</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13306,29 +13306,29 @@
         <v>13</v>
       </c>
       <c r="B393" s="7">
-        <v>385</v>
+        <v>1312</v>
       </c>
       <c t="s" r="C393" s="7">
         <v>14</v>
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>298</v>
+        <v>17</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>104</v>
+        <v>311</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13339,78 +13339,78 @@
         <v>13</v>
       </c>
       <c r="B394" s="7">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c t="s" r="C394" s="7">
         <v>14</v>
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c t="s" r="H394" s="8">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>134</v>
+        <v>362</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>309</v>
+        <v>371</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c r="M394" s="7"/>
     </row>
     <row r="395" ht="15" customHeight="1">
-      <c t="s" r="A395" s="6">
-        <v>13</v>
-      </c>
-      <c r="B395" s="7">
-        <v>1311</v>
-      </c>
-      <c t="s" r="C395" s="7">
-        <v>14</v>
-      </c>
+      <c r="A395" s="6"/>
+      <c r="B395" s="7"/>
+      <c r="C395" s="7"/>
       <c r="D395" s="7"/>
-      <c t="s" r="E395" s="7">
-        <v>372</v>
-      </c>
-      <c r="F395" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G395" s="8">
-        <v>32</v>
-      </c>
-      <c t="s" r="H395" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I395" s="7">
-        <v>360</v>
-      </c>
-      <c t="s" r="J395" s="7">
-        <v>373</v>
-      </c>
+      <c r="E395" s="7"/>
+      <c r="F395" s="7"/>
+      <c r="G395" s="8"/>
+      <c r="H395" s="8"/>
+      <c r="I395" s="7"/>
+      <c r="J395" s="7"/>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c r="M395" s="7"/>
     </row>
     <row r="396" ht="14.25" customHeight="1">
-      <c r="A396" s="6"/>
-      <c r="B396" s="7"/>
-      <c r="C396" s="7"/>
+      <c t="s" r="A396" s="6">
+        <v>13</v>
+      </c>
+      <c r="B396" s="7">
+        <v>886</v>
+      </c>
+      <c t="s" r="C396" s="7">
+        <v>14</v>
+      </c>
       <c r="D396" s="7"/>
-      <c r="E396" s="7"/>
-      <c r="F396" s="7"/>
-      <c r="G396" s="8"/>
-      <c r="H396" s="8"/>
-      <c r="I396" s="7"/>
-      <c r="J396" s="7"/>
+      <c t="s" r="E396" s="7">
+        <v>372</v>
+      </c>
+      <c r="F396" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G396" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H396" s="8">
+        <v>66</v>
+      </c>
+      <c t="s" r="I396" s="7">
+        <v>85</v>
+      </c>
+      <c t="s" r="J396" s="7">
+        <v>148</v>
+      </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c r="M396" s="7"/>
@@ -13420,29 +13420,29 @@
         <v>13</v>
       </c>
       <c r="B397" s="7">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c t="s" r="C397" s="7">
         <v>14</v>
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G397" s="8">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>85</v>
+        <v>373</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>148</v>
+        <v>244</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13453,29 +13453,29 @@
         <v>13</v>
       </c>
       <c r="B398" s="7">
-        <v>885</v>
+        <v>144</v>
       </c>
       <c t="s" r="C398" s="7">
         <v>14</v>
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>375</v>
+        <v>33</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>244</v>
+        <v>332</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13486,29 +13486,29 @@
         <v>13</v>
       </c>
       <c r="B399" s="7">
-        <v>144</v>
+        <v>455</v>
       </c>
       <c t="s" r="C399" s="7">
         <v>14</v>
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>331</v>
+        <v>236</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13519,78 +13519,78 @@
         <v>13</v>
       </c>
       <c r="B400" s="7">
-        <v>455</v>
+        <v>968</v>
       </c>
       <c t="s" r="C400" s="7">
         <v>14</v>
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>121</v>
+        <v>194</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>236</v>
+        <v>98</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c r="M400" s="7"/>
     </row>
     <row r="401" ht="14.25" customHeight="1">
-      <c t="s" r="A401" s="6">
-        <v>13</v>
-      </c>
-      <c r="B401" s="7">
-        <v>968</v>
-      </c>
-      <c t="s" r="C401" s="7">
-        <v>14</v>
-      </c>
+      <c r="A401" s="6"/>
+      <c r="B401" s="7"/>
+      <c r="C401" s="7"/>
       <c r="D401" s="7"/>
-      <c t="s" r="E401" s="7">
-        <v>374</v>
-      </c>
-      <c r="F401" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G401" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="H401" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="I401" s="7">
-        <v>194</v>
-      </c>
-      <c t="s" r="J401" s="7">
-        <v>98</v>
-      </c>
+      <c r="E401" s="7"/>
+      <c r="F401" s="7"/>
+      <c r="G401" s="8"/>
+      <c r="H401" s="8"/>
+      <c r="I401" s="7"/>
+      <c r="J401" s="7"/>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c r="M401" s="7"/>
     </row>
     <row r="402" ht="14.25" customHeight="1">
-      <c r="A402" s="6"/>
-      <c r="B402" s="7"/>
-      <c r="C402" s="7"/>
+      <c t="s" r="A402" s="6">
+        <v>13</v>
+      </c>
+      <c r="B402" s="7">
+        <v>939</v>
+      </c>
+      <c t="s" r="C402" s="7">
+        <v>14</v>
+      </c>
       <c r="D402" s="7"/>
-      <c r="E402" s="7"/>
-      <c r="F402" s="7"/>
-      <c r="G402" s="8"/>
-      <c r="H402" s="8"/>
-      <c r="I402" s="7"/>
-      <c r="J402" s="7"/>
+      <c t="s" r="E402" s="7">
+        <v>374</v>
+      </c>
+      <c r="F402" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G402" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H402" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="I402" s="7">
+        <v>191</v>
+      </c>
+      <c t="s" r="J402" s="7">
+        <v>101</v>
+      </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
       <c r="M402" s="7"/>
@@ -13600,29 +13600,29 @@
         <v>13</v>
       </c>
       <c r="B403" s="7">
-        <v>939</v>
+        <v>143</v>
       </c>
       <c t="s" r="C403" s="7">
         <v>14</v>
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>191</v>
+        <v>224</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -13633,29 +13633,29 @@
         <v>13</v>
       </c>
       <c r="B404" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c t="s" r="C404" s="7">
         <v>14</v>
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G404" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H404" s="8">
         <v>27</v>
       </c>
-      <c t="s" r="H404" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I404" s="7">
-        <v>224</v>
+        <v>327</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13666,78 +13666,78 @@
         <v>13</v>
       </c>
       <c r="B405" s="7">
-        <v>146</v>
+        <v>523</v>
       </c>
       <c t="s" r="C405" s="7">
         <v>14</v>
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>326</v>
+        <v>151</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>36</v>
+        <v>208</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c r="M405" s="7"/>
     </row>
     <row r="406" ht="14.25" customHeight="1">
-      <c t="s" r="A406" s="6">
-        <v>13</v>
-      </c>
-      <c r="B406" s="7">
-        <v>523</v>
-      </c>
-      <c t="s" r="C406" s="7">
-        <v>14</v>
-      </c>
+      <c r="A406" s="6"/>
+      <c r="B406" s="7"/>
+      <c r="C406" s="7"/>
       <c r="D406" s="7"/>
-      <c t="s" r="E406" s="7">
-        <v>376</v>
-      </c>
-      <c r="F406" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G406" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H406" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I406" s="7">
-        <v>151</v>
-      </c>
-      <c t="s" r="J406" s="7">
-        <v>208</v>
-      </c>
+      <c r="E406" s="7"/>
+      <c r="F406" s="7"/>
+      <c r="G406" s="8"/>
+      <c r="H406" s="8"/>
+      <c r="I406" s="7"/>
+      <c r="J406" s="7"/>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c r="M406" s="7"/>
     </row>
     <row r="407" ht="14.25" customHeight="1">
-      <c r="A407" s="6"/>
-      <c r="B407" s="7"/>
-      <c r="C407" s="7"/>
+      <c t="s" r="A407" s="6">
+        <v>13</v>
+      </c>
+      <c r="B407" s="7">
+        <v>272</v>
+      </c>
+      <c t="s" r="C407" s="7">
+        <v>14</v>
+      </c>
       <c r="D407" s="7"/>
-      <c r="E407" s="7"/>
-      <c r="F407" s="7"/>
-      <c r="G407" s="8"/>
-      <c r="H407" s="8"/>
-      <c r="I407" s="7"/>
-      <c r="J407" s="7"/>
+      <c t="s" r="E407" s="7">
+        <v>375</v>
+      </c>
+      <c r="F407" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G407" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H407" s="8">
+        <v>102</v>
+      </c>
+      <c t="s" r="I407" s="7">
+        <v>87</v>
+      </c>
+      <c t="s" r="J407" s="7">
+        <v>355</v>
+      </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c r="M407" s="7"/>
@@ -13747,29 +13747,29 @@
         <v>13</v>
       </c>
       <c r="B408" s="7">
-        <v>813</v>
+        <v>7078</v>
       </c>
       <c t="s" r="C408" s="7">
         <v>14</v>
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G408" s="8">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>106</v>
+        <v>264</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>292</v>
+        <v>376</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -13780,29 +13780,29 @@
         <v>13</v>
       </c>
       <c r="B409" s="7">
-        <v>970</v>
+        <v>7079</v>
       </c>
       <c t="s" r="C409" s="7">
         <v>14</v>
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>106</v>
+        <v>264</v>
       </c>
       <c t="s" r="H409" s="8">
-        <v>41</v>
+        <v>102</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>275</v>
+        <v>225</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -13813,29 +13813,29 @@
         <v>13</v>
       </c>
       <c r="B410" s="7">
-        <v>633</v>
+        <v>273</v>
       </c>
       <c t="s" r="C410" s="7">
         <v>14</v>
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G410" s="8">
-        <v>41</v>
+        <v>102</v>
       </c>
       <c t="s" r="H410" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>244</v>
+        <v>68</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>306</v>
+        <v>57</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -13846,29 +13846,29 @@
         <v>13</v>
       </c>
       <c r="B411" s="7">
-        <v>262</v>
+        <v>1216</v>
       </c>
       <c t="s" r="C411" s="7">
         <v>14</v>
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
+        <v>375</v>
+      </c>
+      <c r="F411" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G411" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H411" s="8">
+        <v>269</v>
+      </c>
+      <c t="s" r="I411" s="7">
         <v>377</v>
       </c>
-      <c r="F411" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G411" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H411" s="8">
-        <v>291</v>
-      </c>
-      <c t="s" r="I411" s="7">
-        <v>35</v>
-      </c>
       <c t="s" r="J411" s="7">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -13879,29 +13879,29 @@
         <v>13</v>
       </c>
       <c r="B412" s="7">
-        <v>263</v>
+        <v>1217</v>
       </c>
       <c t="s" r="C412" s="7">
         <v>14</v>
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>327</v>
+        <v>212</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -13946,7 +13946,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>147</v>
@@ -14063,7 +14063,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14255,7 +14255,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="J425" s="7">
         <v>45</v>
@@ -14384,10 +14384,10 @@
         <v>389</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>

--- a/Data/FlightPlan/FPL_09SEP26.xlsx
+++ b/Data/FlightPlan/FPL_09SEP26.xlsx
@@ -656,208 +656,385 @@
     <t>VN-A580</t>
   </si>
   <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
     <t>11:30</t>
   </si>
   <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>RMQ</t>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>VN-A655</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>ENH</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A662</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>13:40</t>
   </si>
   <si>
     <t>PVG</t>
@@ -869,183 +1046,6 @@
     <t>05:25</t>
   </si>
   <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>VN-A655</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>ENH</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>VN-A662</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
     <t>VN-A671</t>
   </si>
   <si>
@@ -1184,7 +1184,7 @@
     <t>Total Record(s): 351</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 08, 2026 23:36</t>
+    <t xml:space="preserve">Generated on  Sep 08, 2026 23:54</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -5809,7 +5809,7 @@
         <v>13</v>
       </c>
       <c r="B144" s="7">
-        <v>1624</v>
+        <v>852</v>
       </c>
       <c t="s" r="C144" s="7">
         <v>14</v>
@@ -5825,13 +5825,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>41</v>
+        <v>215</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>65</v>
+        <v>217</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -5842,7 +5842,7 @@
         <v>13</v>
       </c>
       <c r="B145" s="7">
-        <v>715</v>
+        <v>853</v>
       </c>
       <c t="s" r="C145" s="7">
         <v>14</v>
@@ -5855,16 +5855,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>41</v>
+        <v>215</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -5875,7 +5875,7 @@
         <v>13</v>
       </c>
       <c r="B146" s="7">
-        <v>714</v>
+        <v>646</v>
       </c>
       <c t="s" r="C146" s="7">
         <v>14</v>
@@ -5888,16 +5888,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c t="s" r="H146" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>157</v>
+        <v>218</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>119</v>
+        <v>219</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -5939,7 +5939,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="I148" s="7">
         <v>181</v>
@@ -5963,19 +5963,19 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
+        <v>221</v>
+      </c>
+      <c t="s" r="H149" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I149" s="7">
         <v>217</v>
-      </c>
-      <c t="s" r="H149" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I149" s="7">
-        <v>218</v>
       </c>
       <c t="s" r="J149" s="7">
         <v>92</v>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6005,7 +6005,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c t="s" r="I150" s="7">
         <v>157</v>
@@ -6029,22 +6029,22 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6077,7 +6077,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6122,7 +6122,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>56</v>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6155,7 +6155,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>166</v>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6188,7 +6188,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="J156" s="7">
         <v>68</v>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6224,7 +6224,7 @@
         <v>103</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6254,7 +6254,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c t="s" r="J158" s="7">
         <v>124</v>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6302,10 +6302,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6335,7 +6335,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c t="s" r="J161" s="7">
         <v>139</v>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6368,7 +6368,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c t="s" r="J162" s="7">
         <v>33</v>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6437,7 +6437,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6482,7 +6482,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c t="s" r="J166" s="7">
         <v>124</v>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6515,7 +6515,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c t="s" r="J167" s="7">
         <v>29</v>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6581,7 +6581,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c t="s" r="J169" s="7">
         <v>171</v>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6647,10 +6647,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6683,7 +6683,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6695,7 +6695,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c t="s" r="J173" s="7">
         <v>139</v>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6764,7 +6764,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6791,7 +6791,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c t="s" r="I176" s="7">
         <v>80</v>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -6845,7 +6845,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -6863,7 +6863,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -6878,7 +6878,7 @@
         <v>100</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -6911,7 +6911,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -6941,7 +6941,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>171</v>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -6974,10 +6974,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7022,7 +7022,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c t="s" r="J184" s="7">
         <v>181</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7058,7 +7058,7 @@
         <v>200</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7154,7 +7154,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c t="s" r="J188" s="7">
         <v>121</v>
@@ -7175,7 +7175,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7187,10 +7187,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7235,10 +7235,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>254</v>
+        <v>216</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7271,7 +7271,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7289,7 +7289,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7301,7 +7301,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>95</v>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7349,7 +7349,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="J195" s="7">
         <v>127</v>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7382,10 +7382,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7403,7 +7403,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7412,7 +7412,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="I197" s="7">
         <v>147</v>
@@ -7436,13 +7436,13 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>27</v>
@@ -7451,7 +7451,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7526,7 +7526,7 @@
         <v>72</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="I201" s="7">
         <v>67</v>
@@ -7550,22 +7550,22 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="H202" s="8">
         <v>72</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7598,7 +7598,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7640,10 +7640,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>190</v>
@@ -7664,19 +7664,19 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>83</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="J206" s="7">
         <v>138</v>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7706,13 +7706,13 @@
         <v>83</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7730,13 +7730,13 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>17</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7775,7 +7775,7 @@
         <v>102</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="J209" s="7">
         <v>33</v>
@@ -7796,7 +7796,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -7859,7 +7859,7 @@
         <v>84</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -7877,7 +7877,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -7892,7 +7892,7 @@
         <v>161</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -7925,7 +7925,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -7988,7 +7988,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>111</v>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8024,7 +8024,7 @@
         <v>104</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>277</v>
+        <v>218</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8057,7 +8057,7 @@
         <v>211</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8099,7 +8099,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="I220" s="7">
         <v>86</v>
@@ -8123,13 +8123,13 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>17</v>
@@ -8138,7 +8138,7 @@
         <v>29</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8189,7 +8189,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8204,7 +8204,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8230,14 +8230,14 @@
         <v>13</v>
       </c>
       <c r="B225" s="7">
-        <v>852</v>
+        <v>270</v>
       </c>
       <c t="s" r="C225" s="7">
         <v>14</v>
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8246,13 +8246,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>282</v>
+        <v>102</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>254</v>
+        <v>175</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>218</v>
+        <v>85</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8263,29 +8263,29 @@
         <v>13</v>
       </c>
       <c r="B226" s="7">
-        <v>853</v>
+        <v>271</v>
       </c>
       <c t="s" r="C226" s="7">
         <v>14</v>
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>282</v>
+        <v>102</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>156</v>
+        <v>86</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>47</v>
+        <v>283</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8296,14 +8296,14 @@
         <v>13</v>
       </c>
       <c r="B227" s="7">
-        <v>3900</v>
+        <v>1624</v>
       </c>
       <c t="s" r="C227" s="7">
         <v>14</v>
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8312,13 +8312,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>283</v>
+        <v>41</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>134</v>
+        <v>284</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>204</v>
+        <v>65</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8326,81 +8326,81 @@
     </row>
     <row r="228" ht="14.25" customHeight="1">
       <c t="s" r="A228" s="6">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B228" s="7">
-        <v>3901</v>
+        <v>715</v>
       </c>
       <c t="s" r="C228" s="7">
         <v>14</v>
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>283</v>
+        <v>41</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>284</v>
+        <v>178</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>285</v>
+        <v>33</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c r="M228" s="7"/>
     </row>
     <row r="229" ht="14.25" customHeight="1">
-      <c r="A229" s="6"/>
-      <c r="B229" s="7"/>
-      <c r="C229" s="7"/>
+      <c t="s" r="A229" s="6">
+        <v>13</v>
+      </c>
+      <c r="B229" s="7">
+        <v>714</v>
+      </c>
+      <c t="s" r="C229" s="7">
+        <v>14</v>
+      </c>
       <c r="D229" s="7"/>
-      <c r="E229" s="7"/>
-      <c r="F229" s="7"/>
-      <c r="G229" s="8"/>
-      <c r="H229" s="8"/>
-      <c r="I229" s="7"/>
-      <c r="J229" s="7"/>
+      <c t="s" r="E229" s="7">
+        <v>282</v>
+      </c>
+      <c r="F229" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G229" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="H229" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I229" s="7">
+        <v>157</v>
+      </c>
+      <c t="s" r="J229" s="7">
+        <v>119</v>
+      </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c r="M229" s="7"/>
     </row>
     <row r="230" ht="15" customHeight="1">
-      <c t="s" r="A230" s="6">
-        <v>13</v>
-      </c>
-      <c r="B230" s="7">
-        <v>823</v>
-      </c>
-      <c t="s" r="C230" s="7">
-        <v>14</v>
-      </c>
+      <c r="A230" s="6"/>
+      <c r="B230" s="7"/>
+      <c r="C230" s="7"/>
       <c r="D230" s="7"/>
-      <c t="s" r="E230" s="7">
-        <v>286</v>
-      </c>
-      <c r="F230" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G230" s="8">
-        <v>113</v>
-      </c>
-      <c t="s" r="H230" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I230" s="7">
-        <v>287</v>
-      </c>
-      <c t="s" r="J230" s="7">
-        <v>42</v>
-      </c>
+      <c r="E230" s="7"/>
+      <c r="F230" s="7"/>
+      <c r="G230" s="8"/>
+      <c r="H230" s="8"/>
+      <c r="I230" s="7"/>
+      <c r="J230" s="7"/>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c r="M230" s="7"/>
@@ -8410,29 +8410,29 @@
         <v>13</v>
       </c>
       <c r="B231" s="7">
-        <v>327</v>
+        <v>823</v>
       </c>
       <c t="s" r="C231" s="7">
         <v>14</v>
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
+        <v>285</v>
+      </c>
+      <c r="F231" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G231" s="8">
+        <v>113</v>
+      </c>
+      <c t="s" r="H231" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I231" s="7">
         <v>286</v>
       </c>
-      <c r="F231" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G231" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H231" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="I231" s="7">
-        <v>244</v>
-      </c>
       <c t="s" r="J231" s="7">
-        <v>262</v>
+        <v>42</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8443,29 +8443,29 @@
         <v>13</v>
       </c>
       <c r="B232" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="C232" s="7">
         <v>14</v>
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H232" s="8">
         <v>20</v>
       </c>
-      <c t="s" r="H232" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I232" s="7">
-        <v>182</v>
+        <v>247</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>183</v>
+        <v>264</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8473,81 +8473,81 @@
     </row>
     <row r="233" ht="14.25" customHeight="1">
       <c t="s" r="A233" s="6">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B233" s="7">
-        <v>91</v>
+        <v>326</v>
       </c>
       <c t="s" r="C233" s="7">
         <v>14</v>
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>288</v>
+        <v>17</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>287</v>
+        <v>183</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c r="M233" s="7"/>
     </row>
     <row r="234" ht="14.25" customHeight="1">
-      <c r="A234" s="6"/>
-      <c r="B234" s="7"/>
-      <c r="C234" s="7"/>
+      <c t="s" r="A234" s="6">
+        <v>37</v>
+      </c>
+      <c r="B234" s="7">
+        <v>91</v>
+      </c>
+      <c t="s" r="C234" s="7">
+        <v>14</v>
+      </c>
       <c r="D234" s="7"/>
-      <c r="E234" s="7"/>
-      <c r="F234" s="7"/>
-      <c r="G234" s="8"/>
-      <c r="H234" s="8"/>
-      <c r="I234" s="7"/>
-      <c r="J234" s="7"/>
+      <c t="s" r="E234" s="7">
+        <v>285</v>
+      </c>
+      <c r="F234" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G234" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H234" s="8">
+        <v>287</v>
+      </c>
+      <c t="s" r="I234" s="7">
+        <v>204</v>
+      </c>
+      <c t="s" r="J234" s="7">
+        <v>286</v>
+      </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c r="M234" s="7"/>
     </row>
     <row r="235" ht="15" customHeight="1">
-      <c t="s" r="A235" s="6">
-        <v>13</v>
-      </c>
-      <c r="B235" s="7">
-        <v>503</v>
-      </c>
-      <c t="s" r="C235" s="7">
-        <v>14</v>
-      </c>
+      <c r="A235" s="6"/>
+      <c r="B235" s="7"/>
+      <c r="C235" s="7"/>
       <c r="D235" s="7"/>
-      <c t="s" r="E235" s="7">
-        <v>289</v>
-      </c>
-      <c r="F235" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G235" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H235" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I235" s="7">
-        <v>85</v>
-      </c>
-      <c t="s" r="J235" s="7">
-        <v>146</v>
-      </c>
+      <c r="E235" s="7"/>
+      <c r="F235" s="7"/>
+      <c r="G235" s="8"/>
+      <c r="H235" s="8"/>
+      <c r="I235" s="7"/>
+      <c r="J235" s="7"/>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c r="M235" s="7"/>
@@ -8557,29 +8557,29 @@
         <v>13</v>
       </c>
       <c r="B236" s="7">
-        <v>701</v>
+        <v>503</v>
       </c>
       <c t="s" r="C236" s="7">
         <v>14</v>
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H236" s="8">
         <v>41</v>
       </c>
-      <c t="s" r="H236" s="8">
-        <v>28</v>
-      </c>
       <c t="s" r="I236" s="7">
-        <v>162</v>
+        <v>85</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8590,78 +8590,78 @@
         <v>13</v>
       </c>
       <c r="B237" s="7">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c t="s" r="C237" s="7">
         <v>14</v>
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="H237" s="8">
         <v>28</v>
       </c>
-      <c t="s" r="H237" s="8">
-        <v>41</v>
-      </c>
       <c t="s" r="I237" s="7">
-        <v>231</v>
+        <v>162</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
       <c r="M237" s="7"/>
     </row>
     <row r="238" ht="14.25" customHeight="1">
-      <c r="A238" s="6"/>
-      <c r="B238" s="7"/>
-      <c r="C238" s="7"/>
+      <c t="s" r="A238" s="6">
+        <v>13</v>
+      </c>
+      <c r="B238" s="7">
+        <v>702</v>
+      </c>
+      <c t="s" r="C238" s="7">
+        <v>14</v>
+      </c>
       <c r="D238" s="7"/>
-      <c r="E238" s="7"/>
-      <c r="F238" s="7"/>
-      <c r="G238" s="8"/>
-      <c r="H238" s="8"/>
-      <c r="I238" s="7"/>
-      <c r="J238" s="7"/>
+      <c t="s" r="E238" s="7">
+        <v>288</v>
+      </c>
+      <c r="F238" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G238" s="8">
+        <v>28</v>
+      </c>
+      <c t="s" r="H238" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I238" s="7">
+        <v>234</v>
+      </c>
+      <c t="s" r="J238" s="7">
+        <v>91</v>
+      </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
       <c r="M238" s="7"/>
     </row>
     <row r="239" ht="14.25" customHeight="1">
-      <c t="s" r="A239" s="6">
-        <v>13</v>
-      </c>
-      <c r="B239" s="7">
-        <v>809</v>
-      </c>
-      <c t="s" r="C239" s="7">
-        <v>14</v>
-      </c>
+      <c r="A239" s="6"/>
+      <c r="B239" s="7"/>
+      <c r="C239" s="7"/>
       <c r="D239" s="7"/>
-      <c t="s" r="E239" s="7">
-        <v>290</v>
-      </c>
-      <c r="F239" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G239" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H239" s="8">
-        <v>291</v>
-      </c>
-      <c t="s" r="I239" s="7">
-        <v>146</v>
-      </c>
-      <c t="s" r="J239" s="7">
-        <v>200</v>
-      </c>
+      <c r="E239" s="7"/>
+      <c r="F239" s="7"/>
+      <c r="G239" s="8"/>
+      <c r="H239" s="8"/>
+      <c r="I239" s="7"/>
+      <c r="J239" s="7"/>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c r="M239" s="7"/>
@@ -8671,29 +8671,29 @@
         <v>13</v>
       </c>
       <c r="B240" s="7">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c t="s" r="C240" s="7">
         <v>14</v>
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
+        <v>289</v>
+      </c>
+      <c r="F240" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G240" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H240" s="8">
         <v>290</v>
       </c>
-      <c r="F240" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G240" s="8">
-        <v>291</v>
-      </c>
-      <c t="s" r="H240" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I240" s="7">
-        <v>292</v>
+        <v>146</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>293</v>
+        <v>200</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8704,29 +8704,29 @@
         <v>13</v>
       </c>
       <c r="B241" s="7">
-        <v>876</v>
+        <v>808</v>
       </c>
       <c t="s" r="C241" s="7">
         <v>14</v>
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
+        <v>289</v>
+      </c>
+      <c r="F241" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G241" s="8">
         <v>290</v>
       </c>
-      <c r="F241" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G241" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="H241" s="8">
-        <v>294</v>
+        <v>17</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>31</v>
+        <v>291</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>69</v>
+        <v>292</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8737,78 +8737,78 @@
         <v>13</v>
       </c>
       <c r="B242" s="7">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c t="s" r="C242" s="7">
         <v>14</v>
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>294</v>
+        <v>17</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>17</v>
+        <v>293</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>295</v>
+        <v>69</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c r="M242" s="7"/>
     </row>
     <row r="243" ht="14.25" customHeight="1">
-      <c r="A243" s="6"/>
-      <c r="B243" s="7"/>
-      <c r="C243" s="7"/>
+      <c t="s" r="A243" s="6">
+        <v>13</v>
+      </c>
+      <c r="B243" s="7">
+        <v>877</v>
+      </c>
+      <c t="s" r="C243" s="7">
+        <v>14</v>
+      </c>
       <c r="D243" s="7"/>
-      <c r="E243" s="7"/>
-      <c r="F243" s="7"/>
-      <c r="G243" s="8"/>
-      <c r="H243" s="8"/>
-      <c r="I243" s="7"/>
-      <c r="J243" s="7"/>
+      <c t="s" r="E243" s="7">
+        <v>289</v>
+      </c>
+      <c r="F243" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G243" s="8">
+        <v>293</v>
+      </c>
+      <c t="s" r="H243" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I243" s="7">
+        <v>57</v>
+      </c>
+      <c t="s" r="J243" s="7">
+        <v>294</v>
+      </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c r="M243" s="7"/>
     </row>
     <row r="244" ht="14.25" customHeight="1">
-      <c t="s" r="A244" s="6">
-        <v>13</v>
-      </c>
-      <c r="B244" s="7">
-        <v>260</v>
-      </c>
-      <c t="s" r="C244" s="7">
-        <v>14</v>
-      </c>
+      <c r="A244" s="6"/>
+      <c r="B244" s="7"/>
+      <c r="C244" s="7"/>
       <c r="D244" s="7"/>
-      <c t="s" r="E244" s="7">
-        <v>296</v>
-      </c>
-      <c r="F244" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G244" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H244" s="8">
-        <v>297</v>
-      </c>
-      <c t="s" r="I244" s="7">
-        <v>52</v>
-      </c>
-      <c t="s" r="J244" s="7">
-        <v>229</v>
-      </c>
+      <c r="E244" s="7"/>
+      <c r="F244" s="7"/>
+      <c r="G244" s="8"/>
+      <c r="H244" s="8"/>
+      <c r="I244" s="7"/>
+      <c r="J244" s="7"/>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c r="M244" s="7"/>
@@ -8818,29 +8818,29 @@
         <v>13</v>
       </c>
       <c r="B245" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c t="s" r="C245" s="7">
         <v>14</v>
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
+        <v>295</v>
+      </c>
+      <c r="F245" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G245" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H245" s="8">
         <v>296</v>
       </c>
-      <c r="F245" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G245" s="8">
-        <v>297</v>
-      </c>
-      <c t="s" r="H245" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I245" s="7">
-        <v>117</v>
+        <v>52</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>298</v>
+        <v>232</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -8851,29 +8851,29 @@
         <v>13</v>
       </c>
       <c r="B246" s="7">
-        <v>807</v>
+        <v>261</v>
       </c>
       <c t="s" r="C246" s="7">
         <v>14</v>
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
+        <v>295</v>
+      </c>
+      <c r="F246" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G246" s="8">
         <v>296</v>
       </c>
-      <c r="F246" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G246" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="H246" s="8">
-        <v>261</v>
+        <v>17</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>44</v>
+        <v>297</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -8884,29 +8884,29 @@
         <v>13</v>
       </c>
       <c r="B247" s="7">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c t="s" r="C247" s="7">
         <v>14</v>
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>261</v>
+        <v>17</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>17</v>
+        <v>263</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>167</v>
+        <v>44</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -8917,78 +8917,78 @@
         <v>13</v>
       </c>
       <c r="B248" s="7">
-        <v>154</v>
+        <v>800</v>
       </c>
       <c t="s" r="C248" s="7">
         <v>14</v>
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>17</v>
+        <v>263</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>239</v>
+        <v>110</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>58</v>
+        <v>167</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c r="M248" s="7"/>
     </row>
     <row r="249" ht="14.25" customHeight="1">
-      <c r="A249" s="6"/>
-      <c r="B249" s="7"/>
-      <c r="C249" s="7"/>
+      <c t="s" r="A249" s="6">
+        <v>13</v>
+      </c>
+      <c r="B249" s="7">
+        <v>154</v>
+      </c>
+      <c t="s" r="C249" s="7">
+        <v>14</v>
+      </c>
       <c r="D249" s="7"/>
-      <c r="E249" s="7"/>
-      <c r="F249" s="7"/>
-      <c r="G249" s="8"/>
-      <c r="H249" s="8"/>
-      <c r="I249" s="7"/>
-      <c r="J249" s="7"/>
+      <c t="s" r="E249" s="7">
+        <v>295</v>
+      </c>
+      <c r="F249" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G249" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H249" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="I249" s="7">
+        <v>242</v>
+      </c>
+      <c t="s" r="J249" s="7">
+        <v>58</v>
+      </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c r="M249" s="7"/>
     </row>
     <row r="250" ht="15" customHeight="1">
-      <c t="s" r="A250" s="6">
-        <v>13</v>
-      </c>
-      <c r="B250" s="7">
-        <v>431</v>
-      </c>
-      <c t="s" r="C250" s="7">
-        <v>14</v>
-      </c>
+      <c r="A250" s="6"/>
+      <c r="B250" s="7"/>
+      <c r="C250" s="7"/>
       <c r="D250" s="7"/>
-      <c t="s" r="E250" s="7">
-        <v>299</v>
-      </c>
-      <c r="F250" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G250" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H250" s="8">
-        <v>300</v>
-      </c>
-      <c t="s" r="I250" s="7">
-        <v>198</v>
-      </c>
-      <c t="s" r="J250" s="7">
-        <v>301</v>
-      </c>
+      <c r="E250" s="7"/>
+      <c r="F250" s="7"/>
+      <c r="G250" s="8"/>
+      <c r="H250" s="8"/>
+      <c r="I250" s="7"/>
+      <c r="J250" s="7"/>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c r="M250" s="7"/>
@@ -8998,29 +8998,29 @@
         <v>13</v>
       </c>
       <c r="B251" s="7">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c t="s" r="C251" s="7">
         <v>14</v>
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F251" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G251" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H251" s="8">
+        <v>299</v>
+      </c>
+      <c t="s" r="I251" s="7">
+        <v>198</v>
+      </c>
+      <c t="s" r="J251" s="7">
         <v>300</v>
-      </c>
-      <c t="s" r="H251" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="I251" s="7">
-        <v>229</v>
-      </c>
-      <c t="s" r="J251" s="7">
-        <v>196</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9031,29 +9031,29 @@
         <v>13</v>
       </c>
       <c r="B252" s="7">
-        <v>403</v>
+        <v>430</v>
       </c>
       <c t="s" r="C252" s="7">
         <v>14</v>
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F252" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G252" s="8">
+        <v>299</v>
+      </c>
+      <c t="s" r="H252" s="8">
         <v>27</v>
       </c>
-      <c t="s" r="H252" s="8">
-        <v>302</v>
-      </c>
       <c t="s" r="I252" s="7">
-        <v>181</v>
+        <v>232</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>250</v>
+        <v>196</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9064,29 +9064,29 @@
         <v>13</v>
       </c>
       <c r="B253" s="7">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c t="s" r="C253" s="7">
         <v>14</v>
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F253" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G253" s="8">
-        <v>302</v>
+        <v>27</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>27</v>
+        <v>301</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>90</v>
+        <v>181</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>303</v>
+        <v>253</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9097,29 +9097,29 @@
         <v>13</v>
       </c>
       <c r="B254" s="7">
-        <v>7712</v>
+        <v>404</v>
       </c>
       <c t="s" r="C254" s="7">
         <v>14</v>
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F254" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G254" s="8">
+        <v>301</v>
+      </c>
+      <c t="s" r="H254" s="8">
         <v>27</v>
       </c>
-      <c t="s" r="H254" s="8">
-        <v>304</v>
-      </c>
       <c t="s" r="I254" s="7">
-        <v>266</v>
+        <v>90</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9127,81 +9127,81 @@
     </row>
     <row r="255" ht="15" customHeight="1">
       <c t="s" r="A255" s="6">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B255" s="7">
-        <v>7713</v>
+        <v>7712</v>
       </c>
       <c t="s" r="C255" s="7">
         <v>14</v>
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F255" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G255" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H255" s="8">
+        <v>303</v>
+      </c>
+      <c t="s" r="I255" s="7">
+        <v>268</v>
+      </c>
+      <c t="s" r="J255" s="7">
         <v>304</v>
-      </c>
-      <c t="s" r="H255" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="I255" s="7">
-        <v>38</v>
-      </c>
-      <c t="s" r="J255" s="7">
-        <v>306</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c r="M255" s="7"/>
     </row>
     <row r="256" ht="14.25" customHeight="1">
-      <c r="A256" s="6"/>
-      <c r="B256" s="7"/>
-      <c r="C256" s="7"/>
+      <c t="s" r="A256" s="6">
+        <v>37</v>
+      </c>
+      <c r="B256" s="7">
+        <v>7713</v>
+      </c>
+      <c t="s" r="C256" s="7">
+        <v>14</v>
+      </c>
       <c r="D256" s="7"/>
-      <c r="E256" s="7"/>
-      <c r="F256" s="7"/>
-      <c r="G256" s="8"/>
-      <c r="H256" s="8"/>
-      <c r="I256" s="7"/>
-      <c r="J256" s="7"/>
+      <c t="s" r="E256" s="7">
+        <v>298</v>
+      </c>
+      <c r="F256" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G256" s="8">
+        <v>303</v>
+      </c>
+      <c t="s" r="H256" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="I256" s="7">
+        <v>38</v>
+      </c>
+      <c t="s" r="J256" s="7">
+        <v>305</v>
+      </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c r="M256" s="7"/>
     </row>
     <row r="257" ht="14.25" customHeight="1">
-      <c t="s" r="A257" s="6">
-        <v>13</v>
-      </c>
-      <c r="B257" s="7">
-        <v>123</v>
-      </c>
-      <c t="s" r="C257" s="7">
-        <v>14</v>
-      </c>
+      <c r="A257" s="6"/>
+      <c r="B257" s="7"/>
+      <c r="C257" s="7"/>
       <c r="D257" s="7"/>
-      <c t="s" r="E257" s="7">
-        <v>307</v>
-      </c>
-      <c r="F257" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G257" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H257" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I257" s="7">
-        <v>175</v>
-      </c>
-      <c t="s" r="J257" s="7">
-        <v>301</v>
-      </c>
+      <c r="E257" s="7"/>
+      <c r="F257" s="7"/>
+      <c r="G257" s="8"/>
+      <c r="H257" s="8"/>
+      <c r="I257" s="7"/>
+      <c r="J257" s="7"/>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c r="M257" s="7"/>
@@ -9211,29 +9211,29 @@
         <v>13</v>
       </c>
       <c r="B258" s="7">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c t="s" r="C258" s="7">
         <v>14</v>
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>117</v>
+        <v>175</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>242</v>
+        <v>300</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9244,29 +9244,29 @@
         <v>13</v>
       </c>
       <c r="B259" s="7">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c t="s" r="C259" s="7">
         <v>14</v>
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H259" s="8">
         <v>27</v>
       </c>
-      <c t="s" r="H259" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I259" s="7">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>56</v>
+        <v>245</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9277,29 +9277,29 @@
         <v>13</v>
       </c>
       <c r="B260" s="7">
-        <v>308</v>
+        <v>133</v>
       </c>
       <c t="s" r="C260" s="7">
         <v>14</v>
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9310,78 +9310,78 @@
         <v>13</v>
       </c>
       <c r="B261" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="C261" s="7">
         <v>14</v>
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H261" s="8">
         <v>32</v>
       </c>
-      <c t="s" r="H261" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I261" s="7">
-        <v>308</v>
+        <v>43</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>309</v>
+        <v>78</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c r="M261" s="7"/>
     </row>
     <row r="262" ht="14.25" customHeight="1">
-      <c r="A262" s="6"/>
-      <c r="B262" s="7"/>
-      <c r="C262" s="7"/>
+      <c t="s" r="A262" s="6">
+        <v>13</v>
+      </c>
+      <c r="B262" s="7">
+        <v>307</v>
+      </c>
+      <c t="s" r="C262" s="7">
+        <v>14</v>
+      </c>
       <c r="D262" s="7"/>
-      <c r="E262" s="7"/>
-      <c r="F262" s="7"/>
-      <c r="G262" s="8"/>
-      <c r="H262" s="8"/>
-      <c r="I262" s="7"/>
-      <c r="J262" s="7"/>
+      <c t="s" r="E262" s="7">
+        <v>306</v>
+      </c>
+      <c r="F262" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G262" s="8">
+        <v>32</v>
+      </c>
+      <c t="s" r="H262" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I262" s="7">
+        <v>307</v>
+      </c>
+      <c t="s" r="J262" s="7">
+        <v>308</v>
+      </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c r="M262" s="7"/>
     </row>
     <row r="263" ht="14.25" customHeight="1">
-      <c t="s" r="A263" s="6">
-        <v>13</v>
-      </c>
-      <c r="B263" s="7">
-        <v>122</v>
-      </c>
-      <c t="s" r="C263" s="7">
-        <v>14</v>
-      </c>
+      <c r="A263" s="6"/>
+      <c r="B263" s="7"/>
+      <c r="C263" s="7"/>
       <c r="D263" s="7"/>
-      <c t="s" r="E263" s="7">
-        <v>310</v>
-      </c>
-      <c r="F263" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G263" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H263" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="I263" s="7">
-        <v>61</v>
-      </c>
-      <c t="s" r="J263" s="7">
-        <v>249</v>
-      </c>
+      <c r="E263" s="7"/>
+      <c r="F263" s="7"/>
+      <c r="G263" s="8"/>
+      <c r="H263" s="8"/>
+      <c r="I263" s="7"/>
+      <c r="J263" s="7"/>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c r="M263" s="7"/>
@@ -9391,29 +9391,29 @@
         <v>13</v>
       </c>
       <c r="B264" s="7">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c t="s" r="C264" s="7">
         <v>14</v>
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H264" s="8">
         <v>27</v>
       </c>
-      <c t="s" r="H264" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I264" s="7">
-        <v>254</v>
+        <v>61</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>101</v>
+        <v>252</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9424,29 +9424,29 @@
         <v>13</v>
       </c>
       <c r="B265" s="7">
-        <v>842</v>
+        <v>135</v>
       </c>
       <c t="s" r="C265" s="7">
         <v>14</v>
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>187</v>
+        <v>17</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>56</v>
+        <v>216</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9457,78 +9457,78 @@
         <v>13</v>
       </c>
       <c r="B266" s="7">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c t="s" r="C266" s="7">
         <v>14</v>
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H266" s="8">
         <v>187</v>
       </c>
-      <c t="s" r="H266" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I266" s="7">
-        <v>179</v>
+        <v>56</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>311</v>
+        <v>47</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c r="M266" s="7"/>
     </row>
     <row r="267" ht="14.25" customHeight="1">
-      <c r="A267" s="6"/>
-      <c r="B267" s="7"/>
-      <c r="C267" s="7"/>
+      <c t="s" r="A267" s="6">
+        <v>13</v>
+      </c>
+      <c r="B267" s="7">
+        <v>843</v>
+      </c>
+      <c t="s" r="C267" s="7">
+        <v>14</v>
+      </c>
       <c r="D267" s="7"/>
-      <c r="E267" s="7"/>
-      <c r="F267" s="7"/>
-      <c r="G267" s="8"/>
-      <c r="H267" s="8"/>
-      <c r="I267" s="7"/>
-      <c r="J267" s="7"/>
+      <c t="s" r="E267" s="7">
+        <v>309</v>
+      </c>
+      <c r="F267" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G267" s="8">
+        <v>187</v>
+      </c>
+      <c t="s" r="H267" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I267" s="7">
+        <v>179</v>
+      </c>
+      <c t="s" r="J267" s="7">
+        <v>310</v>
+      </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c r="M267" s="7"/>
     </row>
     <row r="268" ht="14.25" customHeight="1">
-      <c t="s" r="A268" s="6">
-        <v>13</v>
-      </c>
-      <c r="B268" s="7">
-        <v>447</v>
-      </c>
-      <c t="s" r="C268" s="7">
-        <v>14</v>
-      </c>
+      <c r="A268" s="6"/>
+      <c r="B268" s="7"/>
+      <c r="C268" s="7"/>
       <c r="D268" s="7"/>
-      <c t="s" r="E268" s="7">
-        <v>312</v>
-      </c>
-      <c r="F268" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G268" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="H268" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="I268" s="7">
-        <v>138</v>
-      </c>
-      <c t="s" r="J268" s="7">
-        <v>242</v>
-      </c>
+      <c r="E268" s="7"/>
+      <c r="F268" s="7"/>
+      <c r="G268" s="8"/>
+      <c r="H268" s="8"/>
+      <c r="I268" s="7"/>
+      <c r="J268" s="7"/>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c r="M268" s="7"/>
@@ -9538,29 +9538,29 @@
         <v>13</v>
       </c>
       <c r="B269" s="7">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c t="s" r="C269" s="7">
         <v>14</v>
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G269" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H269" s="8">
         <v>20</v>
       </c>
-      <c t="s" r="H269" s="8">
-        <v>27</v>
-      </c>
       <c t="s" r="I269" s="7">
-        <v>313</v>
+        <v>138</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>56</v>
+        <v>245</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9571,29 +9571,29 @@
         <v>13</v>
       </c>
       <c r="B270" s="7">
-        <v>903</v>
+        <v>440</v>
       </c>
       <c t="s" r="C270" s="7">
         <v>14</v>
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G270" s="8">
+        <v>20</v>
+      </c>
+      <c t="s" r="H270" s="8">
         <v>27</v>
       </c>
-      <c t="s" r="H270" s="8">
-        <v>261</v>
-      </c>
       <c t="s" r="I270" s="7">
-        <v>110</v>
+        <v>312</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9604,29 +9604,29 @@
         <v>13</v>
       </c>
       <c r="B271" s="7">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c t="s" r="C271" s="7">
         <v>14</v>
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F271" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>261</v>
+        <v>27</v>
       </c>
       <c t="s" r="H271" s="8">
-        <v>27</v>
+        <v>263</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>239</v>
+        <v>110</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>314</v>
+        <v>24</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9634,81 +9634,81 @@
     </row>
     <row r="272" ht="14.25" customHeight="1">
       <c t="s" r="A272" s="6">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B272" s="7">
-        <v>1980</v>
+        <v>904</v>
       </c>
       <c t="s" r="C272" s="7">
         <v>14</v>
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G272" s="8">
+        <v>263</v>
+      </c>
+      <c t="s" r="H272" s="8">
         <v>27</v>
       </c>
-      <c t="s" r="H272" s="8">
-        <v>315</v>
-      </c>
       <c t="s" r="I272" s="7">
-        <v>316</v>
+        <v>242</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>18</v>
+        <v>313</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c r="M272" s="7"/>
     </row>
     <row r="273" ht="14.25" customHeight="1">
-      <c r="A273" s="6"/>
-      <c r="B273" s="7"/>
-      <c r="C273" s="7"/>
+      <c t="s" r="A273" s="6">
+        <v>37</v>
+      </c>
+      <c r="B273" s="7">
+        <v>1980</v>
+      </c>
+      <c t="s" r="C273" s="7">
+        <v>14</v>
+      </c>
       <c r="D273" s="7"/>
-      <c r="E273" s="7"/>
-      <c r="F273" s="7"/>
-      <c r="G273" s="8"/>
-      <c r="H273" s="8"/>
-      <c r="I273" s="7"/>
-      <c r="J273" s="7"/>
+      <c t="s" r="E273" s="7">
+        <v>311</v>
+      </c>
+      <c r="F273" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G273" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H273" s="8">
+        <v>314</v>
+      </c>
+      <c t="s" r="I273" s="7">
+        <v>315</v>
+      </c>
+      <c t="s" r="J273" s="7">
+        <v>18</v>
+      </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c r="M273" s="7"/>
     </row>
     <row r="274" ht="14.25" customHeight="1">
-      <c t="s" r="A274" s="6">
-        <v>13</v>
-      </c>
-      <c r="B274" s="7">
-        <v>126</v>
-      </c>
-      <c t="s" r="C274" s="7">
-        <v>14</v>
-      </c>
+      <c r="A274" s="6"/>
+      <c r="B274" s="7"/>
+      <c r="C274" s="7"/>
       <c r="D274" s="7"/>
-      <c t="s" r="E274" s="7">
-        <v>317</v>
-      </c>
-      <c r="F274" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G274" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H274" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="I274" s="7">
-        <v>85</v>
-      </c>
-      <c t="s" r="J274" s="7">
-        <v>162</v>
-      </c>
+      <c r="E274" s="7"/>
+      <c r="F274" s="7"/>
+      <c r="G274" s="8"/>
+      <c r="H274" s="8"/>
+      <c r="I274" s="7"/>
+      <c r="J274" s="7"/>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c r="M274" s="7"/>
@@ -9718,29 +9718,29 @@
         <v>13</v>
       </c>
       <c r="B275" s="7">
-        <v>1491</v>
+        <v>126</v>
       </c>
       <c t="s" r="C275" s="7">
         <v>14</v>
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G275" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H275" s="8">
         <v>27</v>
       </c>
-      <c t="s" r="H275" s="8">
-        <v>83</v>
-      </c>
       <c t="s" r="I275" s="7">
-        <v>318</v>
+        <v>85</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>250</v>
+        <v>162</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9751,29 +9751,29 @@
         <v>13</v>
       </c>
       <c r="B276" s="7">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c t="s" r="C276" s="7">
         <v>14</v>
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
+        <v>316</v>
+      </c>
+      <c r="F276" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G276" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H276" s="8">
+        <v>83</v>
+      </c>
+      <c t="s" r="I276" s="7">
         <v>317</v>
       </c>
-      <c r="F276" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G276" s="8">
-        <v>83</v>
-      </c>
-      <c t="s" r="H276" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="I276" s="7">
-        <v>90</v>
-      </c>
       <c t="s" r="J276" s="7">
-        <v>218</v>
+        <v>253</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9784,29 +9784,29 @@
         <v>13</v>
       </c>
       <c r="B277" s="7">
-        <v>511</v>
+        <v>1492</v>
       </c>
       <c t="s" r="C277" s="7">
         <v>14</v>
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
+        <v>83</v>
+      </c>
+      <c t="s" r="H277" s="8">
         <v>27</v>
       </c>
-      <c t="s" r="H277" s="8">
-        <v>41</v>
-      </c>
       <c t="s" r="I277" s="7">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -9817,29 +9817,29 @@
         <v>13</v>
       </c>
       <c r="B278" s="7">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c t="s" r="C278" s="7">
         <v>14</v>
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G278" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H278" s="8">
         <v>41</v>
       </c>
-      <c t="s" r="H278" s="8">
-        <v>27</v>
-      </c>
       <c t="s" r="I278" s="7">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>119</v>
+        <v>182</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -9850,29 +9850,29 @@
         <v>13</v>
       </c>
       <c r="B279" s="7">
-        <v>1127</v>
+        <v>512</v>
       </c>
       <c t="s" r="C279" s="7">
         <v>14</v>
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="H279" s="8">
         <v>27</v>
       </c>
-      <c t="s" r="H279" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I279" s="7">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>295</v>
+        <v>119</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -9883,78 +9883,78 @@
         <v>13</v>
       </c>
       <c r="B280" s="7">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c t="s" r="C280" s="7">
         <v>14</v>
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>319</v>
+        <v>104</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>320</v>
+        <v>294</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c r="M280" s="7"/>
     </row>
     <row r="281" ht="14.25" customHeight="1">
-      <c r="A281" s="6"/>
-      <c r="B281" s="7"/>
-      <c r="C281" s="7"/>
+      <c t="s" r="A281" s="6">
+        <v>13</v>
+      </c>
+      <c r="B281" s="7">
+        <v>1128</v>
+      </c>
+      <c t="s" r="C281" s="7">
+        <v>14</v>
+      </c>
       <c r="D281" s="7"/>
-      <c r="E281" s="7"/>
-      <c r="F281" s="7"/>
-      <c r="G281" s="8"/>
-      <c r="H281" s="8"/>
-      <c r="I281" s="7"/>
-      <c r="J281" s="7"/>
+      <c t="s" r="E281" s="7">
+        <v>316</v>
+      </c>
+      <c r="F281" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G281" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H281" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="I281" s="7">
+        <v>318</v>
+      </c>
+      <c t="s" r="J281" s="7">
+        <v>319</v>
+      </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c r="M281" s="7"/>
     </row>
     <row r="282" ht="14.25" customHeight="1">
-      <c t="s" r="A282" s="6">
-        <v>13</v>
-      </c>
-      <c r="B282" s="7">
-        <v>801</v>
-      </c>
-      <c t="s" r="C282" s="7">
-        <v>14</v>
-      </c>
+      <c r="A282" s="6"/>
+      <c r="B282" s="7"/>
+      <c r="C282" s="7"/>
       <c r="D282" s="7"/>
-      <c t="s" r="E282" s="7">
-        <v>321</v>
-      </c>
-      <c r="F282" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G282" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H282" s="8">
-        <v>261</v>
-      </c>
-      <c t="s" r="I282" s="7">
-        <v>274</v>
-      </c>
-      <c t="s" r="J282" s="7">
-        <v>322</v>
-      </c>
+      <c r="E282" s="7"/>
+      <c r="F282" s="7"/>
+      <c r="G282" s="8"/>
+      <c r="H282" s="8"/>
+      <c r="I282" s="7"/>
+      <c r="J282" s="7"/>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c r="M282" s="7"/>
@@ -9964,29 +9964,29 @@
         <v>13</v>
       </c>
       <c r="B283" s="7">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c t="s" r="C283" s="7">
         <v>14</v>
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>261</v>
+        <v>17</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>17</v>
+        <v>263</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>215</v>
+        <v>276</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>19</v>
+        <v>321</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -9997,29 +9997,29 @@
         <v>13</v>
       </c>
       <c r="B284" s="7">
-        <v>3674</v>
+        <v>802</v>
       </c>
       <c t="s" r="C284" s="7">
         <v>14</v>
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>17</v>
+        <v>263</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>323</v>
+        <v>17</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>67</v>
+        <v>284</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>179</v>
+        <v>19</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10030,78 +10030,78 @@
         <v>13</v>
       </c>
       <c r="B285" s="7">
-        <v>3675</v>
+        <v>3674</v>
       </c>
       <c t="s" r="C285" s="7">
         <v>14</v>
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>323</v>
+        <v>17</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>17</v>
+        <v>322</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>134</v>
+        <v>67</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>59</v>
+        <v>179</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c r="M285" s="7"/>
     </row>
     <row r="286" ht="14.25" customHeight="1">
-      <c r="A286" s="6"/>
-      <c r="B286" s="7"/>
-      <c r="C286" s="7"/>
+      <c t="s" r="A286" s="6">
+        <v>13</v>
+      </c>
+      <c r="B286" s="7">
+        <v>3675</v>
+      </c>
+      <c t="s" r="C286" s="7">
+        <v>14</v>
+      </c>
       <c r="D286" s="7"/>
-      <c r="E286" s="7"/>
-      <c r="F286" s="7"/>
-      <c r="G286" s="8"/>
-      <c r="H286" s="8"/>
-      <c r="I286" s="7"/>
-      <c r="J286" s="7"/>
+      <c t="s" r="E286" s="7">
+        <v>320</v>
+      </c>
+      <c r="F286" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G286" s="8">
+        <v>322</v>
+      </c>
+      <c t="s" r="H286" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I286" s="7">
+        <v>134</v>
+      </c>
+      <c t="s" r="J286" s="7">
+        <v>59</v>
+      </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c r="M286" s="7"/>
     </row>
     <row r="287" ht="14.25" customHeight="1">
-      <c t="s" r="A287" s="6">
-        <v>13</v>
-      </c>
-      <c r="B287" s="7">
-        <v>879</v>
-      </c>
-      <c t="s" r="C287" s="7">
-        <v>14</v>
-      </c>
+      <c r="A287" s="6"/>
+      <c r="B287" s="7"/>
+      <c r="C287" s="7"/>
       <c r="D287" s="7"/>
-      <c t="s" r="E287" s="7">
-        <v>324</v>
-      </c>
-      <c r="F287" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G287" s="8">
-        <v>23</v>
-      </c>
-      <c t="s" r="H287" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I287" s="7">
-        <v>160</v>
-      </c>
-      <c t="s" r="J287" s="7">
-        <v>162</v>
-      </c>
+      <c r="E287" s="7"/>
+      <c r="F287" s="7"/>
+      <c r="G287" s="8"/>
+      <c r="H287" s="8"/>
+      <c r="I287" s="7"/>
+      <c r="J287" s="7"/>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c r="M287" s="7"/>
@@ -10111,29 +10111,29 @@
         <v>13</v>
       </c>
       <c r="B288" s="7">
-        <v>973</v>
+        <v>879</v>
       </c>
       <c t="s" r="C288" s="7">
         <v>14</v>
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G288" s="8">
+        <v>23</v>
+      </c>
+      <c t="s" r="H288" s="8">
         <v>41</v>
       </c>
-      <c t="s" r="H288" s="8">
-        <v>106</v>
-      </c>
       <c t="s" r="I288" s="7">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10144,29 +10144,29 @@
         <v>13</v>
       </c>
       <c r="B289" s="7">
-        <v>814</v>
+        <v>973</v>
       </c>
       <c t="s" r="C289" s="7">
         <v>14</v>
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G289" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="H289" s="8">
         <v>106</v>
       </c>
-      <c t="s" r="H289" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I289" s="7">
-        <v>280</v>
+        <v>164</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>179</v>
+        <v>130</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10177,111 +10177,111 @@
         <v>13</v>
       </c>
       <c r="B290" s="7">
-        <v>646</v>
+        <v>814</v>
       </c>
       <c t="s" r="C290" s="7">
         <v>14</v>
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>325</v>
+        <v>179</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c r="M290" s="7"/>
     </row>
     <row r="291" ht="14.25" customHeight="1">
-      <c r="A291" s="6"/>
-      <c r="B291" s="7"/>
-      <c r="C291" s="7"/>
+      <c t="s" r="A291" s="6">
+        <v>13</v>
+      </c>
+      <c r="B291" s="7">
+        <v>3908</v>
+      </c>
+      <c t="s" r="C291" s="7">
+        <v>14</v>
+      </c>
       <c r="D291" s="7"/>
-      <c r="E291" s="7"/>
-      <c r="F291" s="7"/>
-      <c r="G291" s="8"/>
-      <c r="H291" s="8"/>
-      <c r="I291" s="7"/>
-      <c r="J291" s="7"/>
+      <c t="s" r="E291" s="7">
+        <v>323</v>
+      </c>
+      <c r="F291" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G291" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H291" s="8">
+        <v>324</v>
+      </c>
+      <c t="s" r="I291" s="7">
+        <v>325</v>
+      </c>
+      <c t="s" r="J291" s="7">
+        <v>326</v>
+      </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c r="M291" s="7"/>
     </row>
     <row r="292" ht="14.25" customHeight="1">
       <c t="s" r="A292" s="6">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B292" s="7">
-        <v>451</v>
+        <v>3909</v>
       </c>
       <c t="s" r="C292" s="7">
         <v>14</v>
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F292" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>27</v>
+        <v>324</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>231</v>
+        <v>327</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>272</v>
+        <v>328</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c r="M292" s="7"/>
     </row>
     <row r="293" ht="14.25" customHeight="1">
-      <c t="s" r="A293" s="6">
-        <v>13</v>
-      </c>
-      <c r="B293" s="7">
-        <v>454</v>
-      </c>
-      <c t="s" r="C293" s="7">
-        <v>14</v>
-      </c>
+      <c r="A293" s="6"/>
+      <c r="B293" s="7"/>
+      <c r="C293" s="7"/>
       <c r="D293" s="7"/>
-      <c t="s" r="E293" s="7">
-        <v>326</v>
-      </c>
-      <c r="F293" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G293" s="8">
-        <v>20</v>
-      </c>
-      <c t="s" r="H293" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="I293" s="7">
-        <v>67</v>
-      </c>
-      <c t="s" r="J293" s="7">
-        <v>327</v>
-      </c>
+      <c r="E293" s="7"/>
+      <c r="F293" s="7"/>
+      <c r="G293" s="8"/>
+      <c r="H293" s="8"/>
+      <c r="I293" s="7"/>
+      <c r="J293" s="7"/>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c r="M293" s="7"/>
@@ -10291,14 +10291,14 @@
         <v>13</v>
       </c>
       <c r="B294" s="7">
-        <v>495</v>
+        <v>451</v>
       </c>
       <c t="s" r="C294" s="7">
         <v>14</v>
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10307,13 +10307,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10324,45 +10324,63 @@
         <v>13</v>
       </c>
       <c r="B295" s="7">
-        <v>496</v>
+        <v>454</v>
       </c>
       <c t="s" r="C295" s="7">
         <v>14</v>
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>328</v>
+        <v>67</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>295</v>
+        <v>330</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c r="M295" s="7"/>
     </row>
     <row r="296" ht="14.25" customHeight="1">
-      <c r="A296" s="6"/>
-      <c r="B296" s="7"/>
-      <c r="C296" s="7"/>
+      <c t="s" r="A296" s="6">
+        <v>13</v>
+      </c>
+      <c r="B296" s="7">
+        <v>495</v>
+      </c>
+      <c t="s" r="C296" s="7">
+        <v>14</v>
+      </c>
       <c r="D296" s="7"/>
-      <c r="E296" s="7"/>
-      <c r="F296" s="7"/>
-      <c r="G296" s="8"/>
-      <c r="H296" s="8"/>
-      <c r="I296" s="7"/>
-      <c r="J296" s="7"/>
+      <c t="s" r="E296" s="7">
+        <v>329</v>
+      </c>
+      <c r="F296" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G296" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H296" s="8">
+        <v>83</v>
+      </c>
+      <c t="s" r="I296" s="7">
+        <v>183</v>
+      </c>
+      <c t="s" r="J296" s="7">
+        <v>258</v>
+      </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c r="M296" s="7"/>
@@ -10372,7 +10390,7 @@
         <v>13</v>
       </c>
       <c r="B297" s="7">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c t="s" r="C297" s="7">
         <v>14</v>
@@ -10385,50 +10403,32 @@
         <v>320</v>
       </c>
       <c t="s" r="G297" s="8">
+        <v>83</v>
+      </c>
+      <c t="s" r="H297" s="8">
         <v>27</v>
       </c>
-      <c t="s" r="H297" s="8">
-        <v>41</v>
-      </c>
       <c t="s" r="I297" s="7">
-        <v>147</v>
+        <v>331</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>30</v>
+        <v>294</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c r="M297" s="7"/>
     </row>
     <row r="298" ht="14.25" customHeight="1">
-      <c t="s" r="A298" s="6">
-        <v>13</v>
-      </c>
-      <c r="B298" s="7">
-        <v>510</v>
-      </c>
-      <c t="s" r="C298" s="7">
-        <v>14</v>
-      </c>
+      <c r="A298" s="6"/>
+      <c r="B298" s="7"/>
+      <c r="C298" s="7"/>
       <c r="D298" s="7"/>
-      <c t="s" r="E298" s="7">
-        <v>329</v>
-      </c>
-      <c r="F298" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G298" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="H298" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="I298" s="7">
-        <v>91</v>
-      </c>
-      <c t="s" r="J298" s="7">
-        <v>67</v>
-      </c>
+      <c r="E298" s="7"/>
+      <c r="F298" s="7"/>
+      <c r="G298" s="8"/>
+      <c r="H298" s="8"/>
+      <c r="I298" s="7"/>
+      <c r="J298" s="7"/>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c r="M298" s="7"/>
@@ -10438,14 +10438,14 @@
         <v>13</v>
       </c>
       <c r="B299" s="7">
-        <v>439</v>
+        <v>507</v>
       </c>
       <c t="s" r="C299" s="7">
         <v>14</v>
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10454,13 +10454,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>300</v>
+        <v>41</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>167</v>
+        <v>30</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10471,29 +10471,29 @@
         <v>13</v>
       </c>
       <c r="B300" s="7">
-        <v>438</v>
+        <v>510</v>
       </c>
       <c t="s" r="C300" s="7">
         <v>14</v>
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>300</v>
+        <v>41</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10504,14 +10504,14 @@
         <v>13</v>
       </c>
       <c r="B301" s="7">
-        <v>163</v>
+        <v>439</v>
       </c>
       <c t="s" r="C301" s="7">
         <v>14</v>
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -10520,29 +10520,47 @@
         <v>27</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>17</v>
+        <v>299</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>311</v>
+        <v>78</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>114</v>
+        <v>167</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
       <c r="M301" s="7"/>
     </row>
     <row r="302" ht="14.25" customHeight="1">
-      <c r="A302" s="6"/>
-      <c r="B302" s="7"/>
-      <c r="C302" s="7"/>
+      <c t="s" r="A302" s="6">
+        <v>13</v>
+      </c>
+      <c r="B302" s="7">
+        <v>438</v>
+      </c>
+      <c t="s" r="C302" s="7">
+        <v>14</v>
+      </c>
       <c r="D302" s="7"/>
-      <c r="E302" s="7"/>
-      <c r="F302" s="7"/>
-      <c r="G302" s="8"/>
-      <c r="H302" s="8"/>
-      <c r="I302" s="7"/>
-      <c r="J302" s="7"/>
+      <c t="s" r="E302" s="7">
+        <v>332</v>
+      </c>
+      <c r="F302" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G302" s="8">
+        <v>299</v>
+      </c>
+      <c t="s" r="H302" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="I302" s="7">
+        <v>24</v>
+      </c>
+      <c t="s" r="J302" s="7">
+        <v>49</v>
+      </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
       <c r="M302" s="7"/>
@@ -10552,63 +10570,45 @@
         <v>13</v>
       </c>
       <c r="B303" s="7">
-        <v>905</v>
+        <v>163</v>
       </c>
       <c t="s" r="C303" s="7">
         <v>14</v>
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F303" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G303" s="8">
         <v>27</v>
       </c>
       <c t="s" r="H303" s="8">
-        <v>217</v>
+        <v>17</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>176</v>
+        <v>310</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>215</v>
+        <v>114</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
       <c r="M303" s="7"/>
     </row>
     <row r="304" ht="14.25" customHeight="1">
-      <c t="s" r="A304" s="6">
-        <v>13</v>
-      </c>
-      <c r="B304" s="7">
-        <v>906</v>
-      </c>
-      <c t="s" r="C304" s="7">
-        <v>14</v>
-      </c>
+      <c r="A304" s="6"/>
+      <c r="B304" s="7"/>
+      <c r="C304" s="7"/>
       <c r="D304" s="7"/>
-      <c t="s" r="E304" s="7">
-        <v>330</v>
-      </c>
-      <c r="F304" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G304" s="8">
-        <v>217</v>
-      </c>
-      <c t="s" r="H304" s="8">
-        <v>27</v>
-      </c>
-      <c t="s" r="I304" s="7">
-        <v>30</v>
-      </c>
-      <c t="s" r="J304" s="7">
-        <v>235</v>
-      </c>
+      <c r="E304" s="7"/>
+      <c r="F304" s="7"/>
+      <c r="G304" s="8"/>
+      <c r="H304" s="8"/>
+      <c r="I304" s="7"/>
+      <c r="J304" s="7"/>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c r="M304" s="7"/>
@@ -10618,14 +10618,14 @@
         <v>13</v>
       </c>
       <c r="B305" s="7">
-        <v>913</v>
+        <v>905</v>
       </c>
       <c t="s" r="C305" s="7">
         <v>14</v>
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -10634,13 +10634,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>331</v>
+        <v>221</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>332</v>
+        <v>284</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10651,29 +10651,29 @@
         <v>13</v>
       </c>
       <c r="B306" s="7">
-        <v>914</v>
+        <v>906</v>
       </c>
       <c t="s" r="C306" s="7">
         <v>14</v>
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>331</v>
+        <v>221</v>
       </c>
       <c t="s" r="H306" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>168</v>
+        <v>30</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>333</v>
+        <v>238</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10684,14 +10684,14 @@
         <v>13</v>
       </c>
       <c r="B307" s="7">
-        <v>7526</v>
+        <v>913</v>
       </c>
       <c t="s" r="C307" s="7">
         <v>14</v>
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -10703,10 +10703,10 @@
         <v>334</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>278</v>
+        <v>128</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>25</v>
+        <v>335</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10714,17 +10714,17 @@
     </row>
     <row r="308" ht="14.25" customHeight="1">
       <c t="s" r="A308" s="6">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B308" s="7">
-        <v>7527</v>
+        <v>914</v>
       </c>
       <c t="s" r="C308" s="7">
         <v>14</v>
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -10736,7 +10736,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>335</v>
+        <v>168</v>
       </c>
       <c t="s" r="J308" s="7">
         <v>336</v>
@@ -10746,82 +10746,82 @@
       <c r="M308" s="7"/>
     </row>
     <row r="309" ht="14.25" customHeight="1">
-      <c r="A309" s="6"/>
-      <c r="B309" s="7"/>
-      <c r="C309" s="7"/>
+      <c t="s" r="A309" s="6">
+        <v>13</v>
+      </c>
+      <c r="B309" s="7">
+        <v>7526</v>
+      </c>
+      <c t="s" r="C309" s="7">
+        <v>14</v>
+      </c>
       <c r="D309" s="7"/>
-      <c r="E309" s="7"/>
-      <c r="F309" s="7"/>
-      <c r="G309" s="8"/>
-      <c r="H309" s="8"/>
-      <c r="I309" s="7"/>
-      <c r="J309" s="7"/>
+      <c t="s" r="E309" s="7">
+        <v>333</v>
+      </c>
+      <c r="F309" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G309" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="H309" s="8">
+        <v>324</v>
+      </c>
+      <c t="s" r="I309" s="7">
+        <v>279</v>
+      </c>
+      <c t="s" r="J309" s="7">
+        <v>25</v>
+      </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c r="M309" s="7"/>
     </row>
     <row r="310" ht="15" customHeight="1">
       <c t="s" r="A310" s="6">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B310" s="7">
-        <v>1729</v>
+        <v>7527</v>
       </c>
       <c t="s" r="C310" s="7">
         <v>14</v>
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
+        <v>333</v>
+      </c>
+      <c r="F310" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G310" s="8">
+        <v>324</v>
+      </c>
+      <c t="s" r="H310" s="8">
+        <v>27</v>
+      </c>
+      <c t="s" r="I310" s="7">
         <v>337</v>
       </c>
-      <c r="F310" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G310" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="H310" s="8">
-        <v>302</v>
-      </c>
-      <c t="s" r="I310" s="7">
-        <v>43</v>
-      </c>
       <c t="s" r="J310" s="7">
-        <v>245</v>
+        <v>338</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c r="M310" s="7"/>
     </row>
     <row r="311" ht="14.25" customHeight="1">
-      <c t="s" r="A311" s="6">
-        <v>13</v>
-      </c>
-      <c r="B311" s="7">
-        <v>1728</v>
-      </c>
-      <c t="s" r="C311" s="7">
-        <v>14</v>
-      </c>
+      <c r="A311" s="6"/>
+      <c r="B311" s="7"/>
+      <c r="C311" s="7"/>
       <c r="D311" s="7"/>
-      <c t="s" r="E311" s="7">
-        <v>337</v>
-      </c>
-      <c r="F311" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G311" s="8">
-        <v>302</v>
-      </c>
-      <c t="s" r="H311" s="8">
-        <v>41</v>
-      </c>
-      <c t="s" r="I311" s="7">
-        <v>262</v>
-      </c>
-      <c t="s" r="J311" s="7">
-        <v>130</v>
-      </c>
+      <c r="E311" s="7"/>
+      <c r="F311" s="7"/>
+      <c r="G311" s="8"/>
+      <c r="H311" s="8"/>
+      <c r="I311" s="7"/>
+      <c r="J311" s="7"/>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c r="M311" s="7"/>
@@ -10831,14 +10831,14 @@
         <v>13</v>
       </c>
       <c r="B312" s="7">
-        <v>526</v>
+        <v>1729</v>
       </c>
       <c t="s" r="C312" s="7">
         <v>14</v>
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -10847,29 +10847,47 @@
         <v>41</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>27</v>
+        <v>301</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>338</v>
+        <v>43</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>59</v>
+        <v>248</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c r="M312" s="7"/>
     </row>
     <row r="313" ht="14.25" customHeight="1">
-      <c r="A313" s="6"/>
-      <c r="B313" s="7"/>
-      <c r="C313" s="7"/>
+      <c t="s" r="A313" s="6">
+        <v>13</v>
+      </c>
+      <c r="B313" s="7">
+        <v>1728</v>
+      </c>
+      <c t="s" r="C313" s="7">
+        <v>14</v>
+      </c>
       <c r="D313" s="7"/>
-      <c r="E313" s="7"/>
-      <c r="F313" s="7"/>
-      <c r="G313" s="8"/>
-      <c r="H313" s="8"/>
-      <c r="I313" s="7"/>
-      <c r="J313" s="7"/>
+      <c t="s" r="E313" s="7">
+        <v>339</v>
+      </c>
+      <c r="F313" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G313" s="8">
+        <v>301</v>
+      </c>
+      <c t="s" r="H313" s="8">
+        <v>41</v>
+      </c>
+      <c t="s" r="I313" s="7">
+        <v>264</v>
+      </c>
+      <c t="s" r="J313" s="7">
+        <v>130</v>
+      </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c r="M313" s="7"/>
@@ -10879,7 +10897,7 @@
         <v>13</v>
       </c>
       <c r="B314" s="7">
-        <v>270</v>
+        <v>526</v>
       </c>
       <c t="s" r="C314" s="7">
         <v>14</v>
@@ -10889,53 +10907,35 @@
         <v>339</v>
       </c>
       <c r="F314" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>102</v>
+        <v>27</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c r="M314" s="7"/>
     </row>
     <row r="315" ht="15" customHeight="1">
-      <c t="s" r="A315" s="6">
-        <v>13</v>
-      </c>
-      <c r="B315" s="7">
-        <v>271</v>
-      </c>
-      <c t="s" r="C315" s="7">
-        <v>14</v>
-      </c>
+      <c r="A315" s="6"/>
+      <c r="B315" s="7"/>
+      <c r="C315" s="7"/>
       <c r="D315" s="7"/>
-      <c t="s" r="E315" s="7">
-        <v>339</v>
-      </c>
-      <c r="F315" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G315" s="8">
-        <v>102</v>
-      </c>
-      <c t="s" r="H315" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I315" s="7">
-        <v>86</v>
-      </c>
-      <c t="s" r="J315" s="7">
-        <v>340</v>
-      </c>
+      <c r="E315" s="7"/>
+      <c r="F315" s="7"/>
+      <c r="G315" s="8"/>
+      <c r="H315" s="8"/>
+      <c r="I315" s="7"/>
+      <c r="J315" s="7"/>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c r="M315" s="7"/>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -10985,7 +10985,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -10997,10 +10997,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11011,14 +11011,14 @@
         <v>13</v>
       </c>
       <c r="B318" s="7">
-        <v>3908</v>
+        <v>3900</v>
       </c>
       <c t="s" r="C318" s="7">
         <v>14</v>
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11027,13 +11027,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>338</v>
+        <v>134</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>342</v>
+        <v>204</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11044,20 +11044,20 @@
         <v>37</v>
       </c>
       <c r="B319" s="7">
-        <v>3909</v>
+        <v>3901</v>
       </c>
       <c t="s" r="C319" s="7">
         <v>14</v>
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>17</v>
@@ -11108,7 +11108,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c t="s" r="I321" s="7">
         <v>346</v>
@@ -11138,13 +11138,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c t="s" r="J322" s="7">
         <v>147</v>
@@ -11174,7 +11174,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="I323" s="7">
         <v>148</v>
@@ -11204,7 +11204,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>17</v>
@@ -11213,7 +11213,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11240,13 +11240,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="I325" s="7">
         <v>167</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11270,16 +11270,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11426,7 +11426,7 @@
         <v>191</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11486,7 +11486,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c t="s" r="I333" s="7">
         <v>67</v>
@@ -11516,13 +11516,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="J334" s="7">
         <v>130</v>
@@ -11552,10 +11552,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>51</v>
@@ -11582,16 +11582,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11639,7 +11639,7 @@
         <v>352</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11666,13 +11666,13 @@
         <v>102</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11696,7 +11696,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>102</v>
@@ -11705,7 +11705,7 @@
         <v>94</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11780,7 +11780,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c t="s" r="I343" s="7">
         <v>160</v>
@@ -11810,10 +11810,10 @@
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="I344" s="7">
         <v>191</v>
@@ -11843,13 +11843,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>215</v>
+        <v>284</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>108</v>
@@ -11876,7 +11876,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>27</v>
@@ -11912,7 +11912,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c t="s" r="I347" s="7">
         <v>33</v>
@@ -11942,7 +11942,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>27</v>
@@ -11978,7 +11978,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>283</v>
+        <v>342</v>
       </c>
       <c t="s" r="I349" s="7">
         <v>201</v>
@@ -12008,7 +12008,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>283</v>
+        <v>342</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>27</v>
@@ -12128,10 +12128,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12164,7 +12164,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12242,7 +12242,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="J358" s="7">
         <v>160</v>
@@ -12305,13 +12305,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12335,13 +12335,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J361" s="7">
         <v>361</v>
@@ -12371,13 +12371,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="I362" s="7">
         <v>119</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12401,7 +12401,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>41</v>
@@ -12488,7 +12488,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c t="s" r="J366" s="7">
         <v>101</v>
@@ -12518,7 +12518,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>282</v>
+        <v>215</v>
       </c>
       <c t="s" r="I367" s="7">
         <v>56</v>
@@ -12548,7 +12548,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>282</v>
+        <v>215</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>27</v>
@@ -12638,7 +12638,7 @@
         <v>124</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12668,7 +12668,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J372" s="7">
         <v>164</v>
@@ -12701,10 +12701,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12731,13 +12731,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c t="s" r="I374" s="7">
         <v>35</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12761,13 +12761,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c t="s" r="J375" s="7">
         <v>135</v>
@@ -12800,10 +12800,10 @@
         <v>365</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -12884,7 +12884,7 @@
         <v>173</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -12911,13 +12911,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="I380" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -12941,7 +12941,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>17</v>
@@ -12950,7 +12950,7 @@
         <v>139</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13016,7 +13016,7 @@
         <v>369</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13058,10 +13058,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="J385" s="7">
         <v>73</v>
@@ -13088,7 +13088,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>17</v>
@@ -13130,7 +13130,7 @@
         <v>146</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13163,7 +13163,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13256,7 +13256,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c t="s" r="I391" s="7">
         <v>361</v>
@@ -13286,7 +13286,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>17</v>
@@ -13328,7 +13328,7 @@
         <v>134</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13442,7 +13442,7 @@
         <v>373</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13475,7 +13475,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13508,7 +13508,7 @@
         <v>121</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13619,7 +13619,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>93</v>
@@ -13652,7 +13652,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>36</v>
@@ -13763,7 +13763,7 @@
         <v>102</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="I408" s="7">
         <v>207</v>
@@ -13793,13 +13793,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>102</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="J409" s="7">
         <v>171</v>
@@ -13862,13 +13862,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="I411" s="7">
         <v>377</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -13892,7 +13892,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>17</v>
@@ -13946,7 +13946,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>340</v>
+        <v>283</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>147</v>
@@ -13979,7 +13979,7 @@
         <v>379</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>95</v>
@@ -14093,7 +14093,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c t="s" r="J419" s="7">
         <v>382</v>
@@ -14141,7 +14141,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>254</v>
+        <v>216</v>
       </c>
       <c t="s" r="J421" s="7">
         <v>101</v>
@@ -14210,7 +14210,7 @@
         <v>157</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14255,7 +14255,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c t="s" r="J425" s="7">
         <v>45</v>
@@ -14288,10 +14288,10 @@
         <v>385</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14339,7 +14339,7 @@
         <v>160</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -14384,10 +14384,10 @@
         <v>389</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -14417,10 +14417,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>

--- a/Data/FlightPlan/FPL_09SEP26.xlsx
+++ b/Data/FlightPlan/FPL_09SEP26.xlsx
@@ -395,6 +395,9 @@
     <t>07:35</t>
   </si>
   <si>
+    <t>07:17</t>
+  </si>
+  <si>
     <t>16:20</t>
   </si>
   <si>
@@ -689,339 +692,339 @@
     <t>VN-A629</t>
   </si>
   <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
     <t>12:10</t>
   </si>
   <si>
-    <t>14:05</t>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>VN-A655</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>ENH</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A662</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
   </si>
   <si>
     <t>16:00</t>
   </si>
   <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>VN-A655</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>ENH</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A662</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
     <t>02:10</t>
   </si>
   <si>
@@ -1184,7 +1187,7 @@
     <t>Total Record(s): 351</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 08, 2026 23:54</t>
+    <t xml:space="preserve">Generated on  Sep 09, 2026 02:26</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3432,7 +3435,9 @@
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
-      <c r="M63" s="7"/>
+      <c t="s" r="M63" s="7">
+        <v>128</v>
+      </c>
     </row>
     <row r="64" ht="14.25" customHeight="1">
       <c t="s" r="A64" s="6">
@@ -3527,7 +3532,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -3554,10 +3559,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H67" s="8">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c t="s" r="J67" s="7">
         <v>59</v>
@@ -3584,16 +3589,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G68" s="8">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="H68" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3626,7 +3631,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -3638,10 +3643,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3674,7 +3679,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3683,13 +3688,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H72" s="8">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -3707,13 +3712,13 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G73" s="8">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="H73" s="8">
         <v>17</v>
@@ -3722,7 +3727,7 @@
         <v>67</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3740,7 +3745,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -3749,13 +3754,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H74" s="8">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -3773,19 +3778,19 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G75" s="8">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="H75" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="J75" s="7">
         <v>84</v>
@@ -3821,7 +3826,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -3836,7 +3841,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -3854,7 +3859,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -3869,7 +3874,7 @@
         <v>64</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -3887,7 +3892,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -3899,10 +3904,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -3920,7 +3925,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -3953,7 +3958,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -3965,10 +3970,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -3986,7 +3991,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -3998,10 +4003,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4019,7 +4024,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4031,10 +4036,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4067,7 +4072,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4082,7 +4087,7 @@
         <v>115</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4100,7 +4105,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4112,7 +4117,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J86" s="7">
         <v>121</v>
@@ -4133,7 +4138,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4145,7 +4150,7 @@
         <v>113</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J87" s="7">
         <v>86</v>
@@ -4181,7 +4186,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4193,10 +4198,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4214,7 +4219,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4226,10 +4231,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4247,7 +4252,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4259,10 +4264,10 @@
         <v>72</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4280,7 +4285,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4292,10 +4297,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4313,7 +4318,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4328,7 +4333,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4346,7 +4351,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4358,7 +4363,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="J94" s="7">
         <v>58</v>
@@ -4394,7 +4399,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4403,7 +4408,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H96" s="8">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="I96" s="7">
         <v>115</v>
@@ -4427,13 +4432,13 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="H97" s="8">
         <v>17</v>
@@ -4442,7 +4447,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4460,7 +4465,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4469,7 +4474,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="I98" s="7">
         <v>104</v>
@@ -4493,13 +4498,13 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="H99" s="8">
         <v>17</v>
@@ -4508,7 +4513,7 @@
         <v>114</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4541,7 +4546,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4553,7 +4558,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J101" s="7">
         <v>61</v>
@@ -4574,7 +4579,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4586,10 +4591,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4607,7 +4612,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4619,7 +4624,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="J103" s="7">
         <v>89</v>
@@ -4640,7 +4645,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4673,7 +4678,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4685,10 +4690,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4706,7 +4711,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4718,10 +4723,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4754,7 +4759,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4763,13 +4768,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4787,22 +4792,22 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -4820,7 +4825,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -4832,10 +4837,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -4868,7 +4873,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -4901,7 +4906,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -4910,7 +4915,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H113" s="8">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="I113" s="7">
         <v>21</v>
@@ -4934,19 +4939,19 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G114" s="8">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="H114" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J114" s="7">
         <v>58</v>
@@ -4967,7 +4972,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -4979,7 +4984,7 @@
         <v>63</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J115" s="7">
         <v>86</v>
@@ -5015,7 +5020,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5027,10 +5032,10 @@
         <v>88</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5048,7 +5053,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5060,7 +5065,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J118" s="7">
         <v>100</v>
@@ -5081,7 +5086,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5093,7 +5098,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J119" s="7">
         <v>19</v>
@@ -5114,7 +5119,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5123,13 +5128,13 @@
         <v>72</v>
       </c>
       <c t="s" r="H120" s="8">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="I120" s="7">
         <v>43</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5147,22 +5152,22 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="H121" s="8">
         <v>72</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5180,7 +5185,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5192,10 +5197,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5228,7 +5233,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5240,10 +5245,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5261,7 +5266,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5273,10 +5278,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5294,7 +5299,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5327,7 +5332,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5339,10 +5344,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5375,13 +5380,13 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="H129" s="8">
         <v>27</v>
@@ -5408,7 +5413,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5420,7 +5425,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J130" s="7">
         <v>46</v>
@@ -5441,7 +5446,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5456,7 +5461,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5474,7 +5479,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5486,7 +5491,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="J132" s="7">
         <v>81</v>
@@ -5522,7 +5527,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5555,7 +5560,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5567,10 +5572,10 @@
         <v>102</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5588,7 +5593,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5621,7 +5626,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5633,10 +5638,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5669,7 +5674,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5681,10 +5686,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5702,7 +5707,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5711,10 +5716,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J140" s="7">
         <v>94</v>
@@ -5735,22 +5740,22 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5768,7 +5773,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5780,10 +5785,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5816,7 +5821,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5825,13 +5830,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -5849,19 +5854,19 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="H145" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="J145" s="7">
         <v>47</v>
@@ -5882,7 +5887,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -5894,10 +5899,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -5930,7 +5935,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -5939,10 +5944,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J148" s="7">
         <v>56</v>
@@ -5963,19 +5968,19 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J149" s="7">
         <v>92</v>
@@ -5996,7 +6001,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6005,13 +6010,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6029,22 +6034,22 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6077,7 +6082,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6092,7 +6097,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6103,14 +6108,14 @@
         <v>13</v>
       </c>
       <c r="B154" s="7">
-        <v>515</v>
+        <v>775</v>
       </c>
       <c t="s" r="C154" s="7">
         <v>14</v>
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6119,13 +6124,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>56</v>
+        <v>140</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6136,29 +6141,29 @@
         <v>13</v>
       </c>
       <c r="B155" s="7">
-        <v>508</v>
+        <v>772</v>
       </c>
       <c t="s" r="C155" s="7">
         <v>14</v>
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>166</v>
+        <v>33</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6169,14 +6174,14 @@
         <v>13</v>
       </c>
       <c r="B156" s="7">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c t="s" r="C156" s="7">
         <v>14</v>
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6188,10 +6193,10 @@
         <v>72</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>228</v>
+        <v>119</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>68</v>
+        <v>121</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6202,14 +6207,14 @@
         <v>13</v>
       </c>
       <c r="B157" s="7">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c t="s" r="C157" s="7">
         <v>14</v>
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6221,7 +6226,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c t="s" r="J157" s="7">
         <v>229</v>
@@ -6242,7 +6247,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6307,16 +6312,20 @@
       <c t="s" r="J160" s="7">
         <v>233</v>
       </c>
-      <c r="K160" s="7"/>
+      <c t="s" r="K160" s="7">
+        <v>139</v>
+      </c>
       <c r="L160" s="7"/>
-      <c r="M160" s="7"/>
+      <c t="s" r="M160" s="7">
+        <v>234</v>
+      </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
       <c t="s" r="A161" s="6">
         <v>13</v>
       </c>
       <c r="B161" s="7">
-        <v>775</v>
+        <v>515</v>
       </c>
       <c t="s" r="C161" s="7">
         <v>14</v>
@@ -6332,13 +6341,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H161" s="8">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>139</v>
+        <v>56</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6349,7 +6358,7 @@
         <v>13</v>
       </c>
       <c r="B162" s="7">
-        <v>772</v>
+        <v>508</v>
       </c>
       <c t="s" r="C162" s="7">
         <v>14</v>
@@ -6362,16 +6371,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G162" s="8">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c t="s" r="H162" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>33</v>
+        <v>167</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6382,7 +6391,7 @@
         <v>13</v>
       </c>
       <c r="B163" s="7">
-        <v>781</v>
+        <v>913</v>
       </c>
       <c t="s" r="C163" s="7">
         <v>14</v>
@@ -6398,13 +6407,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>72</v>
+        <v>236</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>121</v>
+        <v>237</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6415,7 +6424,7 @@
         <v>13</v>
       </c>
       <c r="B164" s="7">
-        <v>780</v>
+        <v>914</v>
       </c>
       <c t="s" r="C164" s="7">
         <v>14</v>
@@ -6428,16 +6437,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>72</v>
+        <v>236</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6470,7 +6479,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6482,7 +6491,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c t="s" r="J166" s="7">
         <v>124</v>
@@ -6503,7 +6512,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6536,7 +6545,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6548,10 +6557,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6569,7 +6578,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6581,10 +6590,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6602,7 +6611,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6617,7 +6626,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6635,7 +6644,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6647,10 +6656,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6683,7 +6692,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6695,10 +6704,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6716,7 +6725,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6749,7 +6758,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6764,7 +6773,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6782,7 +6791,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6791,7 +6800,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="I176" s="7">
         <v>80</v>
@@ -6830,7 +6839,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -6845,7 +6854,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -6863,7 +6872,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -6878,7 +6887,7 @@
         <v>100</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -6896,7 +6905,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -6911,7 +6920,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -6929,7 +6938,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -6941,10 +6950,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -6962,7 +6971,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -6974,10 +6983,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7010,7 +7019,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7022,10 +7031,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7043,7 +7052,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7055,10 +7064,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7076,7 +7085,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7109,7 +7118,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7142,7 +7151,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7154,7 +7163,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c t="s" r="J188" s="7">
         <v>121</v>
@@ -7175,7 +7184,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7187,10 +7196,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7223,7 +7232,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7235,10 +7244,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7256,7 +7265,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7271,7 +7280,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7289,7 +7298,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7301,7 +7310,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>95</v>
@@ -7337,7 +7346,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7349,7 +7358,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c t="s" r="J195" s="7">
         <v>127</v>
@@ -7370,7 +7379,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7382,10 +7391,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7403,7 +7412,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7412,10 +7421,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>19</v>
@@ -7436,13 +7445,13 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>27</v>
@@ -7451,7 +7460,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7484,7 +7493,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7496,14 +7505,18 @@
         <v>72</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>139</v>
-      </c>
-      <c r="K200" s="7"/>
+        <v>140</v>
+      </c>
+      <c t="s" r="K200" s="7">
+        <v>148</v>
+      </c>
       <c r="L200" s="7"/>
-      <c r="M200" s="7"/>
+      <c t="s" r="M200" s="7">
+        <v>270</v>
+      </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
       <c t="s" r="A201" s="6">
@@ -7517,7 +7530,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7526,7 +7539,7 @@
         <v>72</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c t="s" r="I201" s="7">
         <v>67</v>
@@ -7550,22 +7563,22 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c t="s" r="H202" s="8">
         <v>72</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7583,7 +7596,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7598,7 +7611,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7631,7 +7644,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7640,13 +7653,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7664,22 +7677,22 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>83</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7697,7 +7710,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7706,10 +7719,10 @@
         <v>83</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c t="s" r="J207" s="7">
         <v>233</v>
@@ -7730,19 +7743,19 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>19</v>
@@ -7763,7 +7776,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7775,7 +7788,7 @@
         <v>102</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c t="s" r="J209" s="7">
         <v>33</v>
@@ -7796,7 +7809,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7808,7 +7821,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J210" s="7">
         <v>94</v>
@@ -7844,7 +7857,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -7859,7 +7872,7 @@
         <v>84</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -7877,7 +7890,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -7889,10 +7902,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -7910,7 +7923,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -7925,7 +7938,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -7943,7 +7956,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -7958,7 +7971,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -7976,7 +7989,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -7988,7 +8001,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>111</v>
@@ -8009,7 +8022,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8024,7 +8037,7 @@
         <v>104</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8042,7 +8055,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8054,10 +8067,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8090,7 +8103,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8099,13 +8112,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c t="s" r="I220" s="7">
         <v>86</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8123,13 +8136,13 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>17</v>
@@ -8138,7 +8151,7 @@
         <v>29</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8156,7 +8169,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8189,7 +8202,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8204,7 +8217,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8237,7 +8250,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8249,7 +8262,7 @@
         <v>102</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>85</v>
@@ -8270,7 +8283,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8285,7 +8298,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8303,7 +8316,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8315,7 +8328,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c t="s" r="J227" s="7">
         <v>65</v>
@@ -8336,7 +8349,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8348,7 +8361,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J228" s="7">
         <v>33</v>
@@ -8369,7 +8382,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8381,7 +8394,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J229" s="7">
         <v>119</v>
@@ -8417,7 +8430,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8429,7 +8442,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c t="s" r="J231" s="7">
         <v>42</v>
@@ -8450,7 +8463,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8462,10 +8475,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8483,7 +8496,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8495,10 +8508,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8516,7 +8529,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8525,13 +8538,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8564,7 +8577,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8579,7 +8592,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8597,7 +8610,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8609,10 +8622,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8630,7 +8643,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8642,7 +8655,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c t="s" r="J238" s="7">
         <v>91</v>
@@ -8678,7 +8691,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8687,13 +8700,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8711,22 +8724,22 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8744,7 +8757,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8753,7 +8766,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c t="s" r="I242" s="7">
         <v>31</v>
@@ -8777,13 +8790,13 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>17</v>
@@ -8792,7 +8805,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8825,7 +8838,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -8834,7 +8847,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c t="s" r="I245" s="7">
         <v>52</v>
@@ -8858,13 +8871,13 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c t="s" r="H246" s="8">
         <v>17</v>
@@ -8873,7 +8886,7 @@
         <v>117</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -8891,7 +8904,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -8900,7 +8913,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H247" s="8">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="I247" s="7">
         <v>91</v>
@@ -8924,13 +8937,13 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="H248" s="8">
         <v>17</v>
@@ -8939,7 +8952,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -8957,7 +8970,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -8969,7 +8982,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>58</v>
@@ -9005,7 +9018,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="F251" s="7">
         <v>320</v>
@@ -9014,13 +9027,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9038,13 +9051,13 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="F252" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c t="s" r="H252" s="8">
         <v>27</v>
@@ -9053,7 +9066,7 @@
         <v>232</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9071,7 +9084,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="F253" s="7">
         <v>320</v>
@@ -9080,13 +9093,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9104,13 +9117,13 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="F254" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>27</v>
@@ -9119,7 +9132,7 @@
         <v>90</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9137,7 +9150,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="F255" s="7">
         <v>320</v>
@@ -9146,13 +9159,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9170,13 +9183,13 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="F256" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>27</v>
@@ -9185,7 +9198,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9218,7 +9231,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9230,10 +9243,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9251,7 +9264,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9266,7 +9279,7 @@
         <v>117</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9284,7 +9297,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9317,7 +9330,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9350,7 +9363,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9362,10 +9375,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9398,7 +9411,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9413,7 +9426,7 @@
         <v>61</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9431,7 +9444,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9443,7 +9456,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>101</v>
@@ -9464,7 +9477,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9473,7 +9486,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="I266" s="7">
         <v>56</v>
@@ -9497,22 +9510,22 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9545,7 +9558,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
@@ -9557,10 +9570,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9578,7 +9591,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
@@ -9590,7 +9603,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>312</v>
+        <v>234</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>56</v>
@@ -9611,7 +9624,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F271" s="7">
         <v>320</v>
@@ -9620,7 +9633,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H271" s="8">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="I271" s="7">
         <v>110</v>
@@ -9644,22 +9657,22 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G272" s="8">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="H272" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9677,7 +9690,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
@@ -9686,10 +9699,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>18</v>
@@ -9725,7 +9738,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -9740,7 +9753,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9758,7 +9771,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -9770,10 +9783,10 @@
         <v>83</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9791,7 +9804,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -9806,7 +9819,7 @@
         <v>90</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -9824,7 +9837,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -9839,7 +9852,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -9857,7 +9870,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -9869,7 +9882,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>119</v>
@@ -9890,7 +9903,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -9905,7 +9918,7 @@
         <v>104</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -9923,7 +9936,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -9935,10 +9948,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -9971,7 +9984,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -9980,13 +9993,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10004,19 +10017,19 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>19</v>
@@ -10037,7 +10050,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10046,13 +10059,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c t="s" r="I285" s="7">
         <v>67</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10070,19 +10083,19 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>59</v>
@@ -10118,7 +10131,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10130,10 +10143,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10151,7 +10164,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10163,10 +10176,10 @@
         <v>106</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10184,7 +10197,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10196,10 +10209,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10217,7 +10230,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10226,13 +10239,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10250,22 +10263,22 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10298,7 +10311,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10310,10 +10323,10 @@
         <v>20</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10331,7 +10344,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10346,7 +10359,7 @@
         <v>67</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10364,7 +10377,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -10376,10 +10389,10 @@
         <v>83</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10397,7 +10410,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10409,10 +10422,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10445,7 +10458,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10457,7 +10470,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>30</v>
@@ -10478,7 +10491,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -10511,7 +10524,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -10520,13 +10533,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c t="s" r="I301" s="7">
         <v>78</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10544,13 +10557,13 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>27</v>
@@ -10577,7 +10590,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
@@ -10589,7 +10602,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>114</v>
@@ -10625,7 +10638,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -10634,13 +10647,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10658,13 +10671,13 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="H306" s="8">
         <v>27</v>
@@ -10673,7 +10686,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10684,14 +10697,14 @@
         <v>13</v>
       </c>
       <c r="B307" s="7">
-        <v>913</v>
+        <v>773</v>
       </c>
       <c t="s" r="C307" s="7">
         <v>14</v>
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -10700,13 +10713,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>334</v>
+        <v>72</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>128</v>
+        <v>337</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>335</v>
+        <v>68</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10717,29 +10730,29 @@
         <v>13</v>
       </c>
       <c r="B308" s="7">
-        <v>914</v>
+        <v>776</v>
       </c>
       <c t="s" r="C308" s="7">
         <v>14</v>
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>334</v>
+        <v>72</v>
       </c>
       <c t="s" r="H308" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>168</v>
+        <v>103</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>336</v>
+        <v>242</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10757,7 +10770,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -10766,10 +10779,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>25</v>
@@ -10790,22 +10803,22 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c t="s" r="H310" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -10838,7 +10851,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -10847,13 +10860,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="I312" s="7">
         <v>43</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -10871,22 +10884,22 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="H313" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -10904,7 +10917,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -10916,7 +10929,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c t="s" r="J314" s="7">
         <v>59</v>
@@ -10952,7 +10965,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -10964,7 +10977,7 @@
         <v>88</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>78</v>
@@ -10985,7 +10998,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -10997,10 +11010,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11018,7 +11031,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11027,13 +11040,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11051,22 +11064,22 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11099,7 +11112,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11108,10 +11121,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c t="s" r="J321" s="7">
         <v>55</v>
@@ -11132,22 +11145,22 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11165,7 +11178,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11174,10 +11187,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J323" s="7">
         <v>56</v>
@@ -11198,13 +11211,13 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>17</v>
@@ -11213,7 +11226,7 @@
         <v>118</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11231,7 +11244,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11240,13 +11253,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11264,22 +11277,22 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11297,7 +11310,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11309,10 +11322,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11345,7 +11358,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11354,10 +11367,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>98</v>
@@ -11378,13 +11391,13 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="H330" s="8">
         <v>17</v>
@@ -11411,7 +11424,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11420,10 +11433,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>233</v>
@@ -11444,19 +11457,19 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="J332" s="7">
         <v>30</v>
@@ -11477,7 +11490,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11486,13 +11499,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="I333" s="7">
         <v>67</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11510,22 +11523,22 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>228</v>
+        <v>337</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11543,7 +11556,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -11552,10 +11565,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>335</v>
+        <v>237</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>51</v>
@@ -11576,13 +11589,13 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>17</v>
@@ -11591,7 +11604,7 @@
         <v>230</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11624,7 +11637,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -11636,10 +11649,10 @@
         <v>102</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11657,7 +11670,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -11666,13 +11679,13 @@
         <v>102</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11690,13 +11703,13 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>102</v>
@@ -11705,7 +11718,7 @@
         <v>94</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11723,7 +11736,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -11735,10 +11748,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -11771,7 +11784,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -11780,13 +11793,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -11804,22 +11817,22 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -11837,19 +11850,19 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>108</v>
@@ -11870,22 +11883,22 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -11903,7 +11916,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -11912,7 +11925,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="I347" s="7">
         <v>33</v>
@@ -11936,13 +11949,13 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>27</v>
@@ -11969,7 +11982,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -11978,13 +11991,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12002,22 +12015,22 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12050,7 +12063,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12083,7 +12096,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12116,7 +12129,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -12128,10 +12141,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12149,7 +12162,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -12164,7 +12177,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12182,7 +12195,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -12194,10 +12207,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12230,7 +12243,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12242,10 +12255,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12263,7 +12276,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12278,7 +12291,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12296,7 +12309,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12305,13 +12318,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12329,22 +12342,22 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12362,7 +12375,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12371,13 +12384,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c t="s" r="I362" s="7">
         <v>119</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>336</v>
+        <v>238</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12395,22 +12408,22 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12443,7 +12456,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12455,10 +12468,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12476,7 +12489,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -12488,7 +12501,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="J366" s="7">
         <v>101</v>
@@ -12509,7 +12522,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12518,13 +12531,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="I367" s="7">
         <v>56</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12542,13 +12555,13 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>27</v>
@@ -12575,7 +12588,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12587,7 +12600,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>115</v>
@@ -12623,7 +12636,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -12638,7 +12651,7 @@
         <v>124</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12656,7 +12669,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -12668,10 +12681,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12689,7 +12702,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -12701,10 +12714,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12722,7 +12735,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -12731,13 +12744,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c t="s" r="I374" s="7">
         <v>35</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12755,22 +12768,22 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12788,7 +12801,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -12797,13 +12810,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -12821,22 +12834,22 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -12869,7 +12882,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -12881,7 +12894,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="J379" s="7">
         <v>232</v>
@@ -12902,7 +12915,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -12911,13 +12924,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="I380" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -12935,22 +12948,22 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -12968,7 +12981,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -12980,7 +12993,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J382" s="7">
         <v>49</v>
@@ -13001,7 +13014,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13013,10 +13026,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13049,7 +13062,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
@@ -13058,10 +13071,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c t="s" r="J385" s="7">
         <v>73</v>
@@ -13082,19 +13095,19 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c t="s" r="J386" s="7">
         <v>99</v>
@@ -13115,7 +13128,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -13127,10 +13140,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13148,7 +13161,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
@@ -13163,7 +13176,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13181,7 +13194,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -13190,7 +13203,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="I389" s="7">
         <v>42</v>
@@ -13214,13 +13227,13 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>17</v>
@@ -13247,7 +13260,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -13256,10 +13269,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="J391" s="7">
         <v>24</v>
@@ -13280,13 +13293,13 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>17</v>
@@ -13313,7 +13326,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -13325,10 +13338,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13346,7 +13359,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
@@ -13358,10 +13371,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13394,7 +13407,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -13409,7 +13422,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13427,7 +13440,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -13439,10 +13452,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13460,7 +13473,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -13475,7 +13488,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>335</v>
+        <v>237</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13493,7 +13506,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -13508,7 +13521,7 @@
         <v>121</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13526,7 +13539,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -13538,7 +13551,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>98</v>
@@ -13574,7 +13587,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -13586,7 +13599,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="J402" s="7">
         <v>101</v>
@@ -13607,7 +13620,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -13619,7 +13632,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>93</v>
@@ -13640,7 +13653,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -13652,7 +13665,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>36</v>
@@ -13673,7 +13686,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -13685,10 +13698,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13721,7 +13734,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -13736,7 +13749,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -13754,7 +13767,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -13763,13 +13776,13 @@
         <v>102</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -13787,22 +13800,22 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>102</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>228</v>
+        <v>337</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -13820,7 +13833,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -13853,7 +13866,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -13862,13 +13875,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -13886,22 +13899,22 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -13934,7 +13947,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
@@ -13946,10 +13959,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -13967,7 +13980,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
@@ -13976,10 +13989,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H415" s="8">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>95</v>
@@ -14000,13 +14013,13 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G416" s="8">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="H416" s="8">
         <v>41</v>
@@ -14048,7 +14061,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
@@ -14057,13 +14070,13 @@
         <v>41</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="I418" s="7">
         <v>39</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14081,22 +14094,22 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F419" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="H419" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14129,7 +14142,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
@@ -14141,7 +14154,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="J421" s="7">
         <v>101</v>
@@ -14162,7 +14175,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F422" s="7">
         <v>330</v>
@@ -14177,7 +14190,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14195,7 +14208,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F423" s="7">
         <v>330</v>
@@ -14207,10 +14220,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14243,19 +14256,19 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F425" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G425" s="8">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c t="s" r="H425" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c t="s" r="J425" s="7">
         <v>45</v>
@@ -14276,7 +14289,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F426" s="7">
         <v>330</v>
@@ -14285,13 +14298,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H426" s="8">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14324,22 +14337,22 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F428" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G428" s="8">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c t="s" r="H428" s="8">
         <v>72</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -14372,7 +14385,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
@@ -14381,13 +14394,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H430" s="8">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -14405,22 +14418,22 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F431" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G431" s="8">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c t="s" r="H431" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14428,7 +14441,7 @@
     </row>
     <row r="432" ht="15.75" customHeight="1">
       <c t="s" r="A432" s="9">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B432" s="9"/>
       <c r="C432" s="9"/>
@@ -14448,7 +14461,7 @@
     <row r="433" ht="65.25" customHeight="1"/>
     <row r="434" ht="16.5" customHeight="1">
       <c t="s" r="A434" s="10">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B434" s="10"/>
       <c r="C434" s="10"/>
@@ -14461,7 +14474,7 @@
       <c r="J434" s="10"/>
       <c r="K434" s="10"/>
       <c t="s" r="L434" s="11">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M434" s="11"/>
       <c r="N434" s="11"/>

--- a/Data/FlightPlan/FPL_09SEP26.xlsx
+++ b/Data/FlightPlan/FPL_09SEP26.xlsx
@@ -314,7 +314,7 @@
     <t>06:40</t>
   </si>
   <si>
-    <t>07:47</t>
+    <t>07:45</t>
   </si>
   <si>
     <t>08:20</t>
@@ -587,6 +587,9 @@
     <t>06:50</t>
   </si>
   <si>
+    <t>08:46</t>
+  </si>
+  <si>
     <t>09:20</t>
   </si>
   <si>
@@ -719,270 +722,273 @@
     <t>10:40</t>
   </si>
   <si>
+    <t>11:52</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>10:01</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>07:36</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>06:43</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>08:27</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>08:02</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>07:38</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>07:41</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>08:52</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>VN-A655</t>
+  </si>
+  <si>
     <t>11:25</t>
   </si>
   <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>10:01</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>07:36</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>06:43</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>08:27</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>08:02</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>07:38</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>07:41</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>VN-A655</t>
-  </si>
-  <si>
     <t>20:25</t>
   </si>
   <si>
@@ -1232,7 +1238,7 @@
     <t>Total Record(s): 350</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 09, 2026 06:50</t>
+    <t xml:space="preserve">Generated on  Sep 09, 2026 07:09</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -5063,7 +5069,9 @@
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
-      <c r="M116" s="7"/>
+      <c t="s" r="M116" s="7">
+        <v>192</v>
+      </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
       <c t="s" r="A117" s="6">
@@ -5089,7 +5097,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>103</v>
@@ -5122,7 +5130,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J118" s="7">
         <v>19</v>
@@ -5152,7 +5160,7 @@
         <v>72</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="I119" s="7">
         <v>43</v>
@@ -5182,7 +5190,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>72</v>
@@ -5191,7 +5199,7 @@
         <v>134</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5221,10 +5229,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5257,7 +5265,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5269,15 +5277,15 @@
         <v>27</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
@@ -5292,7 +5300,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5307,7 +5315,7 @@
         <v>138</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5325,7 +5333,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5358,7 +5366,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5370,7 +5378,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J126" s="7">
         <v>158</v>
@@ -5406,13 +5414,13 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G128" s="8">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="H128" s="8">
         <v>27</v>
@@ -5439,7 +5447,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5472,7 +5480,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5505,7 +5513,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5517,7 +5525,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J131" s="7">
         <v>82</v>
@@ -5553,7 +5561,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5573,7 +5581,7 @@
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
@@ -5588,7 +5596,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5600,10 +5608,10 @@
         <v>105</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5621,7 +5629,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5654,7 +5662,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5669,7 +5677,7 @@
         <v>134</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5702,7 +5710,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5735,7 +5743,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5744,7 +5752,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H139" s="8">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="I139" s="7">
         <v>183</v>
@@ -5768,13 +5776,13 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G140" s="8">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="H140" s="8">
         <v>17</v>
@@ -5783,7 +5791,7 @@
         <v>142</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5801,7 +5809,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5813,10 +5821,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5849,7 +5857,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -5858,13 +5866,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5882,13 +5890,13 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G144" s="8">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="H144" s="8">
         <v>17</v>
@@ -5915,7 +5923,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -5927,10 +5935,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -5963,7 +5971,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -5972,7 +5980,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H147" s="8">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="I147" s="7">
         <v>182</v>
@@ -5996,19 +6004,19 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="J148" s="7">
         <v>94</v>
@@ -6029,7 +6037,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6038,13 +6046,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="I149" s="7">
         <v>157</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6062,22 +6070,22 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6110,7 +6118,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6125,7 +6133,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6143,7 +6151,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6155,7 +6163,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J153" s="7">
         <v>139</v>
@@ -6176,7 +6184,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6188,7 +6196,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>33</v>
@@ -6209,7 +6217,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6242,7 +6250,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6257,7 +6265,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6275,7 +6283,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6287,7 +6295,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J157" s="7">
         <v>87</v>
@@ -6323,7 +6331,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6335,17 +6343,17 @@
         <v>27</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="K159" s="7">
         <v>138</v>
       </c>
       <c r="L159" s="7"/>
       <c t="s" r="M159" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
@@ -6360,7 +6368,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6372,7 +6380,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J160" s="7">
         <v>56</v>
@@ -6393,7 +6401,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6405,7 +6413,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J161" s="7">
         <v>166</v>
@@ -6426,7 +6434,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6435,13 +6443,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="I162" s="7">
         <v>128</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6459,13 +6467,13 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>27</v>
@@ -6474,7 +6482,7 @@
         <v>168</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6507,7 +6515,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6519,7 +6527,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J165" s="7">
         <v>87</v>
@@ -6527,7 +6535,7 @@
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -6542,7 +6550,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6554,7 +6562,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J166" s="7">
         <v>29</v>
@@ -6575,7 +6583,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6587,7 +6595,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J167" s="7">
         <v>179</v>
@@ -6608,7 +6616,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6620,7 +6628,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J168" s="7">
         <v>171</v>
@@ -6641,7 +6649,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6674,7 +6682,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6686,10 +6694,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6722,7 +6730,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6734,7 +6742,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>139</v>
@@ -6755,7 +6763,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6788,7 +6796,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6803,7 +6811,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6821,7 +6829,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6830,7 +6838,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="I175" s="7">
         <v>81</v>
@@ -6869,7 +6877,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6884,7 +6892,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6902,7 +6910,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -6917,7 +6925,7 @@
         <v>103</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -6935,7 +6943,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -6950,7 +6958,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -6968,7 +6976,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -6980,7 +6988,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>171</v>
@@ -7001,7 +7009,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7013,10 +7021,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7049,7 +7057,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7061,7 +7069,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J183" s="7">
         <v>182</v>
@@ -7082,7 +7090,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7094,10 +7102,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7115,7 +7123,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7148,7 +7156,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7181,7 +7189,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7193,7 +7201,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J187" s="7">
         <v>124</v>
@@ -7214,7 +7222,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7226,10 +7234,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7262,7 +7270,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7274,10 +7282,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>263</v>
+        <v>101</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7297,7 +7305,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7330,7 +7338,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7539,7 +7547,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="J199" s="7">
         <v>139</v>
@@ -7690,7 +7698,7 @@
         <v>282</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J204" s="7">
         <v>191</v>
@@ -7761,7 +7769,7 @@
         <v>285</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7976,7 +7984,7 @@
         <v>104</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8075,7 +8083,7 @@
         <v>107</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8105,7 +8113,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="J217" s="7">
         <v>292</v>
@@ -8156,7 +8164,7 @@
         <v>88</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8189,7 +8197,7 @@
         <v>29</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8515,7 +8523,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J231" s="7">
         <v>274</v>
@@ -8581,7 +8589,7 @@
         <v>300</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>299</v>
@@ -8695,7 +8703,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>93</v>
@@ -8809,7 +8817,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J241" s="7">
         <v>304</v>
@@ -8926,7 +8934,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9057,7 +9065,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>58</v>
@@ -9105,7 +9113,7 @@
         <v>310</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J251" s="7">
         <v>311</v>
@@ -9140,10 +9148,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9176,7 +9184,7 @@
         <v>182</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9358,7 +9366,7 @@
         <v>120</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9505,11 +9513,13 @@
         <v>61</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
-      <c r="M264" s="7"/>
+      <c t="s" r="M264" s="7">
+        <v>322</v>
+      </c>
     </row>
     <row r="265" ht="15" customHeight="1">
       <c t="s" r="A265" s="6">
@@ -9535,7 +9545,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>104</v>
@@ -9604,7 +9614,7 @@
         <v>180</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9637,7 +9647,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
@@ -9652,7 +9662,7 @@
         <v>138</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9670,7 +9680,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
@@ -9682,7 +9692,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>236</v>
+        <v>325</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>56</v>
@@ -9703,7 +9713,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F271" s="7">
         <v>320</v>
@@ -9736,7 +9746,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
@@ -9748,10 +9758,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9769,7 +9779,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
@@ -9778,10 +9788,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>18</v>
@@ -9817,7 +9827,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -9850,7 +9860,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -9862,10 +9872,10 @@
         <v>84</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9883,7 +9893,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -9898,7 +9908,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -9916,7 +9926,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -9949,7 +9959,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -9982,7 +9992,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -9997,7 +10007,7 @@
         <v>107</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10015,7 +10025,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10027,10 +10037,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10063,7 +10073,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10078,7 +10088,7 @@
         <v>288</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10096,7 +10106,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10129,7 +10139,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10138,7 +10148,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c t="s" r="I285" s="7">
         <v>67</v>
@@ -10162,13 +10172,13 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>17</v>
@@ -10210,7 +10220,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10230,7 +10240,7 @@
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -10245,7 +10255,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10278,7 +10288,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10311,7 +10321,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10320,13 +10330,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10344,22 +10354,22 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10392,7 +10402,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10404,7 +10414,7 @@
         <v>20</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>286</v>
@@ -10425,7 +10435,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10440,7 +10450,7 @@
         <v>67</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10458,7 +10468,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -10491,7 +10501,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10506,7 +10516,7 @@
         <v>306</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10539,7 +10549,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10572,7 +10582,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -10605,7 +10615,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -10638,7 +10648,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
@@ -10671,7 +10681,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
@@ -10683,7 +10693,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>117</v>
@@ -10719,7 +10729,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -10728,7 +10738,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="I305" s="7">
         <v>177</v>
@@ -10752,13 +10762,13 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="H306" s="8">
         <v>27</v>
@@ -10767,7 +10777,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10785,7 +10795,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -10797,7 +10807,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="J307" s="7">
         <v>68</v>
@@ -10818,7 +10828,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -10833,7 +10843,7 @@
         <v>106</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10851,7 +10861,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -10860,7 +10870,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c t="s" r="I309" s="7">
         <v>292</v>
@@ -10884,22 +10894,22 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c t="s" r="H310" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -10932,7 +10942,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -10947,7 +10957,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -10965,7 +10975,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -10998,7 +11008,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11010,7 +11020,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="J314" s="7">
         <v>59</v>
@@ -11046,7 +11056,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -11058,7 +11068,7 @@
         <v>90</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>79</v>
@@ -11079,7 +11089,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -11112,7 +11122,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11121,13 +11131,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c t="s" r="I318" s="7">
         <v>134</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11145,22 +11155,22 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11193,7 +11203,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11205,7 +11215,7 @@
         <v>310</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c t="s" r="J321" s="7">
         <v>55</v>
@@ -11226,7 +11236,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11238,7 +11248,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c t="s" r="J322" s="7">
         <v>147</v>
@@ -11259,7 +11269,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11292,7 +11302,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11325,7 +11335,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11340,7 +11350,7 @@
         <v>167</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11358,7 +11368,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11373,7 +11383,7 @@
         <v>279</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11391,7 +11401,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11403,10 +11413,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11439,7 +11449,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11448,10 +11458,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>100</v>
@@ -11474,13 +11484,13 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="H330" s="8">
         <v>17</v>
@@ -11507,7 +11517,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11516,13 +11526,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11540,13 +11550,13 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>17</v>
@@ -11573,7 +11583,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11606,7 +11616,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11618,7 +11628,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="J334" s="7">
         <v>130</v>
@@ -11639,7 +11649,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -11651,7 +11661,7 @@
         <v>315</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>51</v>
@@ -11672,7 +11682,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -11684,10 +11694,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11720,7 +11730,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -11732,7 +11742,7 @@
         <v>105</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>272</v>
@@ -11740,7 +11750,7 @@
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -11755,7 +11765,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -11788,7 +11798,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -11803,7 +11813,7 @@
         <v>96</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11821,7 +11831,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
@@ -11833,7 +11843,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>132</v>
@@ -11869,7 +11879,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -11902,7 +11912,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -11914,10 +11924,10 @@
         <v>282</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -11935,7 +11945,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -11968,7 +11978,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -12001,7 +12011,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12034,7 +12044,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -12067,7 +12077,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -12076,13 +12086,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12100,22 +12110,22 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12148,7 +12158,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12181,7 +12191,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12214,7 +12224,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -12226,10 +12236,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12247,7 +12257,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -12280,7 +12290,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -12292,7 +12302,7 @@
         <v>23</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c t="s" r="J356" s="7">
         <v>173</v>
@@ -12328,7 +12338,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12348,7 +12358,7 @@
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c t="s" r="M358" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
@@ -12363,7 +12373,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12396,7 +12406,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12408,10 +12418,10 @@
         <v>277</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12429,7 +12439,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12444,7 +12454,7 @@
         <v>274</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12462,7 +12472,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12477,7 +12487,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12495,7 +12505,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12507,10 +12517,10 @@
         <v>41</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12543,7 +12553,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12555,10 +12565,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12576,7 +12586,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -12588,7 +12598,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J366" s="7">
         <v>104</v>
@@ -12609,7 +12619,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12618,7 +12628,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="I367" s="7">
         <v>56</v>
@@ -12642,13 +12652,13 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>27</v>
@@ -12675,7 +12685,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12723,7 +12733,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -12732,13 +12742,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c t="s" r="I371" s="7">
         <v>146</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12756,19 +12766,19 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c t="s" r="H372" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c t="s" r="J372" s="7">
         <v>276</v>
@@ -12789,7 +12799,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -12798,7 +12808,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="I373" s="7">
         <v>31</v>
@@ -12822,13 +12832,13 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="H374" s="8">
         <v>17</v>
@@ -12837,7 +12847,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12855,7 +12865,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -12864,13 +12874,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12888,22 +12898,22 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -12936,7 +12946,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -12951,7 +12961,7 @@
         <v>173</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -12971,7 +12981,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -12980,13 +12990,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="I379" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13004,13 +13014,13 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>17</v>
@@ -13037,7 +13047,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13070,7 +13080,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13082,10 +13092,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13118,7 +13128,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
@@ -13138,7 +13148,7 @@
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -13153,7 +13163,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
@@ -13165,7 +13175,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c t="s" r="J385" s="7">
         <v>102</v>
@@ -13186,7 +13196,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
@@ -13219,7 +13229,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -13234,7 +13244,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13252,7 +13262,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
@@ -13261,7 +13271,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="I388" s="7">
         <v>42</v>
@@ -13285,13 +13295,13 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G389" s="8">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="H389" s="8">
         <v>17</v>
@@ -13318,7 +13328,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -13330,7 +13340,7 @@
         <v>310</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>24</v>
@@ -13351,7 +13361,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -13384,7 +13394,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -13399,7 +13409,7 @@
         <v>134</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13417,7 +13427,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -13429,10 +13439,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13465,7 +13475,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -13498,7 +13508,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -13510,10 +13520,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13531,7 +13541,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -13546,7 +13556,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13564,7 +13574,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -13579,7 +13589,7 @@
         <v>124</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13597,7 +13607,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -13609,7 +13619,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J399" s="7">
         <v>100</v>
@@ -13645,7 +13655,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -13657,7 +13667,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>104</v>
@@ -13678,7 +13688,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -13690,7 +13700,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J402" s="7">
         <v>95</v>
@@ -13711,7 +13721,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -13723,7 +13733,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>36</v>
@@ -13744,7 +13754,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -13759,7 +13769,7 @@
         <v>151</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13792,7 +13802,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -13807,7 +13817,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -13825,7 +13835,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -13837,10 +13847,10 @@
         <v>277</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -13858,7 +13868,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -13870,7 +13880,7 @@
         <v>105</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>171</v>
@@ -13891,7 +13901,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -13924,7 +13934,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -13936,10 +13946,10 @@
         <v>282</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -13957,7 +13967,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -13969,7 +13979,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>158</v>
@@ -14005,7 +14015,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F413" s="7">
         <v>330</v>
@@ -14038,7 +14048,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
@@ -14047,10 +14057,10 @@
         <v>41</v>
       </c>
       <c t="s" r="H414" s="8">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>97</v>
@@ -14071,13 +14081,13 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c t="s" r="H415" s="8">
         <v>41</v>
@@ -14119,7 +14129,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
@@ -14128,17 +14138,21 @@
         <v>41</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c t="s" r="I417" s="7">
         <v>39</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>351</v>
-      </c>
-      <c r="K417" s="7"/>
+        <v>353</v>
+      </c>
+      <c t="s" r="K417" s="7">
+        <v>18</v>
+      </c>
       <c r="L417" s="7"/>
-      <c r="M417" s="7"/>
+      <c t="s" r="M417" s="7">
+        <v>256</v>
+      </c>
     </row>
     <row r="418" ht="14.25" customHeight="1">
       <c t="s" r="A418" s="6">
@@ -14152,26 +14166,30 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>41</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>398</v>
-      </c>
-      <c r="K418" s="7"/>
+        <v>400</v>
+      </c>
+      <c t="s" r="K418" s="7">
+        <v>171</v>
+      </c>
       <c r="L418" s="7"/>
-      <c r="M418" s="7"/>
+      <c t="s" r="M418" s="7">
+        <v>173</v>
+      </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
       <c r="A419" s="6"/>
@@ -14200,7 +14218,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F420" s="7">
         <v>330</v>
@@ -14212,7 +14230,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J420" s="7">
         <v>104</v>
@@ -14233,7 +14251,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
@@ -14266,7 +14284,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F422" s="7">
         <v>330</v>
@@ -14314,13 +14332,13 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F424" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G424" s="8">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c t="s" r="H424" s="8">
         <v>17</v>
@@ -14347,7 +14365,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F425" s="7">
         <v>330</v>
@@ -14356,7 +14374,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c t="s" r="I425" s="7">
         <v>279</v>
@@ -14395,13 +14413,13 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F427" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G427" s="8">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c t="s" r="H427" s="8">
         <v>72</v>
@@ -14410,7 +14428,7 @@
         <v>160</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -14443,7 +14461,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F429" s="7">
         <v>330</v>
@@ -14452,13 +14470,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H429" s="8">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c t="s" r="I429" s="7">
         <v>303</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -14476,22 +14494,22 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G430" s="8">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c t="s" r="H430" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -14499,7 +14517,7 @@
     </row>
     <row r="431" ht="15.75" customHeight="1">
       <c t="s" r="A431" s="9">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B431" s="9"/>
       <c r="C431" s="9"/>
@@ -14519,7 +14537,7 @@
     <row r="432" ht="65.25" customHeight="1"/>
     <row r="433" ht="16.5" customHeight="1">
       <c t="s" r="A433" s="10">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B433" s="10"/>
       <c r="C433" s="10"/>
@@ -14532,7 +14550,7 @@
       <c r="J433" s="10"/>
       <c r="K433" s="10"/>
       <c t="s" r="L433" s="11">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M433" s="11"/>
       <c r="N433" s="11"/>

--- a/Data/FlightPlan/FPL_09SEP26.xlsx
+++ b/Data/FlightPlan/FPL_09SEP26.xlsx
@@ -128,7 +128,7 @@
     <t>17:10</t>
   </si>
   <si>
-    <t>17:27</t>
+    <t>17:33</t>
   </si>
   <si>
     <t>17:40</t>
@@ -284,6 +284,9 @@
     <t>15:40</t>
   </si>
   <si>
+    <t>23:05</t>
+  </si>
+  <si>
     <t>02:05</t>
   </si>
   <si>
@@ -338,7 +341,7 @@
     <t>18:25</t>
   </si>
   <si>
-    <t>18:31</t>
+    <t>18:44</t>
   </si>
   <si>
     <t>21:05</t>
@@ -371,9 +374,6 @@
     <t>14:50</t>
   </si>
   <si>
-    <t>17:33</t>
-  </si>
-  <si>
     <t>18:20</t>
   </si>
   <si>
@@ -488,9 +488,6 @@
     <t>16:55</t>
   </si>
   <si>
-    <t>23:05</t>
-  </si>
-  <si>
     <t>00:15</t>
   </si>
   <si>
@@ -704,6 +701,9 @@
     <t>19:00</t>
   </si>
   <si>
+    <t>19:07</t>
+  </si>
+  <si>
     <t>MNL</t>
   </si>
   <si>
@@ -731,7 +731,7 @@
     <t>17:30</t>
   </si>
   <si>
-    <t>22:08</t>
+    <t>21:41</t>
   </si>
   <si>
     <t>01:40</t>
@@ -896,7 +896,7 @@
     <t>HND</t>
   </si>
   <si>
-    <t>00:18</t>
+    <t>00:27</t>
   </si>
   <si>
     <t>02:00</t>
@@ -953,6 +953,9 @@
     <t>18:05</t>
   </si>
   <si>
+    <t>18:21</t>
+  </si>
+  <si>
     <t>20:50</t>
   </si>
   <si>
@@ -1064,6 +1067,15 @@
     <t>09:55</t>
   </si>
   <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
     <t>VN-A640</t>
   </si>
   <si>
@@ -1100,7 +1112,7 @@
     <t>13:55</t>
   </si>
   <si>
-    <t>18:42</t>
+    <t>18:41</t>
   </si>
   <si>
     <t>VN-A642</t>
@@ -1130,7 +1142,10 @@
     <t>15:07</t>
   </si>
   <si>
-    <t>18:22</t>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>23:30</t>
   </si>
   <si>
     <t>VN-A645</t>
@@ -1151,6 +1166,9 @@
     <t>16:04</t>
   </si>
   <si>
+    <t>18:33</t>
+  </si>
+  <si>
     <t>VN-A646</t>
   </si>
   <si>
@@ -1163,6 +1181,9 @@
     <t>15:33</t>
   </si>
   <si>
+    <t>17:44</t>
+  </si>
+  <si>
     <t>PER</t>
   </si>
   <si>
@@ -1190,9 +1211,6 @@
     <t>19:45</t>
   </si>
   <si>
-    <t>21:20</t>
-  </si>
-  <si>
     <t>VN-A649</t>
   </si>
   <si>
@@ -1202,12 +1220,6 @@
     <t>14:42</t>
   </si>
   <si>
-    <t>17:19</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
     <t>VN-A650</t>
   </si>
   <si>
@@ -1253,6 +1265,9 @@
     <t>17:35</t>
   </si>
   <si>
+    <t>18:07</t>
+  </si>
+  <si>
     <t>VN-A653</t>
   </si>
   <si>
@@ -1301,15 +1316,6 @@
     <t>16:48</t>
   </si>
   <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
     <t>VN-A658</t>
   </si>
   <si>
@@ -1325,6 +1331,9 @@
     <t>VN-A661</t>
   </si>
   <si>
+    <t>18:56</t>
+  </si>
+  <si>
     <t>21:45</t>
   </si>
   <si>
@@ -1367,9 +1376,6 @@
     <t>16:00</t>
   </si>
   <si>
-    <t>18:14</t>
-  </si>
-  <si>
     <t>VN-A669</t>
   </si>
   <si>
@@ -1460,6 +1466,9 @@
     <t>12:46</t>
   </si>
   <si>
+    <t>17:59</t>
+  </si>
+  <si>
     <t>01:15</t>
   </si>
   <si>
@@ -1502,7 +1511,7 @@
     <t>12:24</t>
   </si>
   <si>
-    <t>19:21</t>
+    <t>20:14</t>
   </si>
   <si>
     <t>VN-A685</t>
@@ -1586,6 +1595,9 @@
     <t>VN-A814</t>
   </si>
   <si>
+    <t>19:08</t>
+  </si>
+  <si>
     <t>VN-A815</t>
   </si>
   <si>
@@ -1616,7 +1628,7 @@
     <t>Total Record(s): 351</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 09, 2026 16:41</t>
+    <t xml:space="preserve">Generated on  Sep 09, 2026 17:20</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3023,7 +3035,9 @@
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
+      <c t="s" r="M34" s="7">
+        <v>91</v>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c t="s" r="A35" s="6">
@@ -3049,10 +3063,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I35" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J35" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -3085,7 +3099,7 @@
       </c>
       <c r="D37" s="7"/>
       <c t="s" r="E37" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F37" s="7">
         <v>321</v>
@@ -3094,18 +3108,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H37" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="I37" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="J37" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
       <c t="s" r="M37" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1">
@@ -3120,27 +3134,27 @@
       </c>
       <c r="D38" s="7"/>
       <c t="s" r="E38" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F38" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G38" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="H38" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J38" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
       <c t="s" r="M38" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
@@ -3155,7 +3169,7 @@
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F39" s="7">
         <v>321</v>
@@ -3164,18 +3178,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H39" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="J39" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
       <c t="s" r="M39" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
@@ -3190,27 +3204,27 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G40" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H40" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I40" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J40" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
       <c t="s" r="M40" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1">
@@ -3225,7 +3239,7 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
@@ -3237,15 +3251,15 @@
         <v>29</v>
       </c>
       <c t="s" r="I41" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
       <c t="s" r="M41" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
@@ -3260,7 +3274,7 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
@@ -3275,7 +3289,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -3308,7 +3322,7 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
@@ -3317,20 +3331,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H44" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="J44" s="7">
         <v>44</v>
       </c>
       <c t="s" r="K44" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L44" s="7"/>
       <c t="s" r="M44" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
@@ -3345,25 +3359,25 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G45" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H45" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="J45" s="7">
         <v>18</v>
       </c>
       <c t="s" r="K45" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L45" s="7"/>
       <c t="s" r="M45" s="7">
@@ -3382,7 +3396,7 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
@@ -3394,7 +3408,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J46" s="7">
         <v>33</v>
@@ -3402,7 +3416,7 @@
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
       <c t="s" r="M46" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
@@ -3417,7 +3431,7 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
@@ -3426,7 +3440,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H47" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="I47" s="7">
         <v>19</v>
@@ -3437,7 +3451,7 @@
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c t="s" r="M47" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
@@ -3452,13 +3466,13 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G48" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="H48" s="8">
         <v>21</v>
@@ -3472,7 +3486,7 @@
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
       <c t="s" r="M48" s="7">
-        <v>120</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
@@ -3487,7 +3501,7 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
@@ -3520,7 +3534,7 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3553,7 +3567,7 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
@@ -3613,7 +3627,7 @@
         <v>128</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="J53" s="7">
         <v>129</v>
@@ -3905,7 +3919,7 @@
         <v>149</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3985,7 +3999,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="J65" s="7">
         <v>62</v>
@@ -4020,7 +4034,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="J66" s="7">
         <v>129</v>
@@ -4093,7 +4107,7 @@
         <v>158</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>159</v>
+        <v>91</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -4123,10 +4137,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I69" s="7">
+        <v>159</v>
+      </c>
+      <c t="s" r="J69" s="7">
         <v>160</v>
-      </c>
-      <c t="s" r="J69" s="7">
-        <v>161</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -4159,7 +4173,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -4171,10 +4185,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I71" s="7">
+        <v>162</v>
+      </c>
+      <c t="s" r="J71" s="7">
         <v>163</v>
-      </c>
-      <c t="s" r="J71" s="7">
-        <v>164</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -4207,27 +4221,27 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
+        <v>164</v>
+      </c>
+      <c r="F73" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G73" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H73" s="8">
         <v>165</v>
       </c>
-      <c r="F73" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G73" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H73" s="8">
+      <c t="s" r="I73" s="7">
         <v>166</v>
       </c>
-      <c t="s" r="I73" s="7">
+      <c t="s" r="J73" s="7">
         <v>167</v>
-      </c>
-      <c t="s" r="J73" s="7">
-        <v>168</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
       <c t="s" r="M73" s="7">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
@@ -4242,13 +4256,13 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
+        <v>164</v>
+      </c>
+      <c r="F74" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G74" s="8">
         <v>165</v>
-      </c>
-      <c r="F74" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G74" s="8">
-        <v>166</v>
       </c>
       <c t="s" r="H74" s="8">
         <v>17</v>
@@ -4257,12 +4271,12 @@
         <v>76</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
       <c t="s" r="M74" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
@@ -4277,7 +4291,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -4286,13 +4300,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H75" s="8">
+        <v>171</v>
+      </c>
+      <c t="s" r="I75" s="7">
         <v>172</v>
       </c>
-      <c t="s" r="I75" s="7">
+      <c t="s" r="J75" s="7">
         <v>173</v>
-      </c>
-      <c t="s" r="J75" s="7">
-        <v>174</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
@@ -4310,22 +4324,22 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G76" s="8">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c t="s" r="H76" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -4358,7 +4372,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4373,12 +4387,12 @@
         <v>44</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
       <c t="s" r="M78" s="7">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
@@ -4393,7 +4407,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -4408,12 +4422,12 @@
         <v>73</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
       <c t="s" r="M79" s="7">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
@@ -4428,7 +4442,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4440,15 +4454,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I80" s="7">
+        <v>180</v>
+      </c>
+      <c t="s" r="J80" s="7">
         <v>181</v>
-      </c>
-      <c t="s" r="J80" s="7">
-        <v>182</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c t="s" r="M80" s="7">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -4463,7 +4477,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4483,7 +4497,7 @@
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
       <c t="s" r="M81" s="7">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -4498,7 +4512,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4510,14 +4524,16 @@
         <v>30</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
-      <c r="M82" s="7"/>
+      <c t="s" r="M82" s="7">
+        <v>137</v>
+      </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c t="s" r="A83" s="6">
@@ -4531,7 +4547,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4543,10 +4559,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I83" s="7">
+        <v>184</v>
+      </c>
+      <c t="s" r="J83" s="7">
         <v>185</v>
-      </c>
-      <c t="s" r="J83" s="7">
-        <v>186</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4564,7 +4580,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4576,10 +4592,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I84" s="7">
+        <v>186</v>
+      </c>
+      <c t="s" r="J84" s="7">
         <v>187</v>
-      </c>
-      <c t="s" r="J84" s="7">
-        <v>188</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4612,7 +4628,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4621,10 +4637,10 @@
         <v>29</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c t="s" r="J86" s="7">
         <v>19</v>
@@ -4632,7 +4648,7 @@
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
       <c t="s" r="M86" s="7">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
@@ -4647,13 +4663,13 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
+        <v>188</v>
+      </c>
+      <c r="F87" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G87" s="8">
         <v>189</v>
-      </c>
-      <c r="F87" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G87" s="8">
-        <v>190</v>
       </c>
       <c t="s" r="H87" s="8">
         <v>29</v>
@@ -4662,12 +4678,12 @@
         <v>143</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
       <c t="s" r="M87" s="7">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
@@ -4682,7 +4698,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4715,7 +4731,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4730,7 +4746,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4763,7 +4779,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4778,7 +4794,7 @@
         <v>139</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4798,7 +4814,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4810,7 +4826,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c t="s" r="J92" s="7">
         <v>147</v>
@@ -4818,7 +4834,7 @@
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
       <c t="s" r="M92" s="7">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
@@ -4833,7 +4849,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4848,7 +4864,7 @@
         <v>126</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4881,7 +4897,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4893,15 +4909,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I95" s="7">
+        <v>199</v>
+      </c>
+      <c t="s" r="J95" s="7">
         <v>200</v>
-      </c>
-      <c t="s" r="J95" s="7">
-        <v>201</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -4916,7 +4932,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4928,15 +4944,15 @@
         <v>29</v>
       </c>
       <c t="s" r="I96" s="7">
+        <v>202</v>
+      </c>
+      <c t="s" r="J96" s="7">
         <v>203</v>
-      </c>
-      <c t="s" r="J96" s="7">
-        <v>204</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -4951,7 +4967,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4966,12 +4982,12 @@
         <v>20</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -4986,7 +5002,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4998,10 +5014,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I98" s="7">
+        <v>207</v>
+      </c>
+      <c t="s" r="J98" s="7">
         <v>208</v>
-      </c>
-      <c t="s" r="J98" s="7">
-        <v>209</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -5021,7 +5037,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -5036,14 +5052,14 @@
         <v>26</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c t="s" r="K99" s="7">
         <v>121</v>
       </c>
       <c r="L99" s="7"/>
       <c t="s" r="M99" s="7">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
@@ -5058,7 +5074,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -5070,17 +5086,17 @@
         <v>29</v>
       </c>
       <c t="s" r="I100" s="7">
+        <v>210</v>
+      </c>
+      <c t="s" r="J100" s="7">
         <v>211</v>
       </c>
-      <c t="s" r="J100" s="7">
+      <c t="s" r="K100" s="7">
         <v>212</v>
-      </c>
-      <c t="s" r="K100" s="7">
-        <v>213</v>
       </c>
       <c r="L100" s="7"/>
       <c t="s" r="M100" s="7">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
@@ -5110,7 +5126,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -5119,7 +5135,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c t="s" r="I102" s="7">
         <v>139</v>
@@ -5145,13 +5161,13 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c t="s" r="H103" s="8">
         <v>17</v>
@@ -5160,12 +5176,12 @@
         <v>143</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
       <c t="s" r="M103" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
@@ -5180,7 +5196,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5189,13 +5205,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H104" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="I104" s="7">
         <v>40</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -5213,19 +5229,19 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G105" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="H105" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c t="s" r="J105" s="7">
         <v>124</v>
@@ -5246,7 +5262,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5258,10 +5274,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -5294,7 +5310,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5306,15 +5322,15 @@
         <v>36</v>
       </c>
       <c t="s" r="I108" s="7">
+        <v>220</v>
+      </c>
+      <c t="s" r="J108" s="7">
         <v>221</v>
-      </c>
-      <c t="s" r="J108" s="7">
-        <v>222</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
       <c t="s" r="M108" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -5329,7 +5345,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5341,15 +5357,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
       <c t="s" r="M109" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
@@ -5364,7 +5380,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5376,15 +5392,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
       <c t="s" r="M110" s="7">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -5399,7 +5415,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5411,7 +5427,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J111" s="7">
         <v>33</v>
@@ -5419,7 +5435,7 @@
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5434,7 +5450,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5446,7 +5462,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c t="s" r="J112" s="7">
         <v>155</v>
@@ -5454,7 +5470,7 @@
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5469,7 +5485,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5481,14 +5497,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
-      <c r="M113" s="7"/>
+      <c t="s" r="M113" s="7">
+        <v>230</v>
+      </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
       <c t="s" r="A114" s="6">
@@ -5502,7 +5520,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5514,7 +5532,7 @@
         <v>231</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c t="s" r="J114" s="7">
         <v>232</v>
@@ -5535,7 +5553,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5592,7 +5610,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c t="s" r="I117" s="7">
         <v>236</v>
@@ -5624,7 +5642,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G118" s="8">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c t="s" r="H118" s="8">
         <v>29</v>
@@ -5633,7 +5651,7 @@
         <v>239</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5668,7 +5686,7 @@
         <v>241</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5783,10 +5801,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5819,7 +5837,7 @@
         <v>245</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5861,13 +5879,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H126" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I126" s="7">
         <v>247</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5893,7 +5911,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G127" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H127" s="8">
         <v>17</v>
@@ -5902,7 +5920,7 @@
         <v>249</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5972,7 +5990,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -6120,7 +6138,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>263</v>
@@ -6238,7 +6256,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J138" s="7">
         <v>22</v>
@@ -6273,7 +6291,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c t="s" r="J139" s="7">
         <v>53</v>
@@ -6311,7 +6329,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -6425,7 +6443,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -6454,7 +6472,7 @@
         <v>82</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="I145" s="7">
         <v>275</v>
@@ -6486,7 +6504,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="H146" s="8">
         <v>82</v>
@@ -6575,10 +6593,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6613,7 +6631,7 @@
         <v>237</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6645,7 +6663,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c t="s" r="J151" s="7">
         <v>282</v>
@@ -6761,7 +6779,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>54</v>
@@ -6799,7 +6817,7 @@
         <v>58</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6882,7 +6900,7 @@
         <v>287</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6914,10 +6932,10 @@
         <v>294</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -7005,7 +7023,7 @@
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c t="s" r="M163" s="7">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -7035,7 +7053,7 @@
         <v>299</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -7171,7 +7189,7 @@
         <v>305</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -7222,7 +7240,7 @@
         <v>308</v>
       </c>
       <c t="s" r="K170" s="7">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
@@ -7261,7 +7279,7 @@
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -7291,7 +7309,7 @@
         <v>300</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -7330,7 +7348,9 @@
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
-      <c r="M173" s="7"/>
+      <c t="s" r="M173" s="7">
+        <v>314</v>
+      </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
       <c t="s" r="A174" s="6">
@@ -7356,10 +7376,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -7386,10 +7406,10 @@
         <v>29</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="J175" s="7">
         <v>27</v>
@@ -7416,7 +7436,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>29</v>
@@ -7425,7 +7445,7 @@
         <v>232</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7458,7 +7478,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7470,15 +7490,15 @@
         <v>29</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -7493,7 +7513,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7513,7 +7533,7 @@
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -7528,7 +7548,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7543,12 +7563,12 @@
         <v>154</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7563,7 +7583,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7575,15 +7595,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7598,7 +7618,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7631,7 +7651,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7643,10 +7663,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>159</v>
+        <v>91</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7679,7 +7699,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7691,10 +7711,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7714,7 +7734,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7723,7 +7743,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I186" s="7">
         <v>87</v>
@@ -7734,7 +7754,7 @@
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -7749,13 +7769,13 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>29</v>
@@ -7782,7 +7802,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7791,10 +7811,10 @@
         <v>29</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J188" s="7">
         <v>139</v>
@@ -7830,7 +7850,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7839,18 +7859,18 @@
         <v>46</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="I190" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -7865,27 +7885,27 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="H191" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -7900,7 +7920,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7915,12 +7935,12 @@
         <v>86</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -7935,7 +7955,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7947,15 +7967,15 @@
         <v>46</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -7985,7 +8005,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7997,7 +8017,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c t="s" r="J195" s="7">
         <v>236</v>
@@ -8005,7 +8025,7 @@
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -8020,7 +8040,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -8035,12 +8055,12 @@
         <v>263</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -8055,7 +8075,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -8075,7 +8095,7 @@
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -8090,7 +8110,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8110,7 +8130,7 @@
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -8140,7 +8160,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8152,7 +8172,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J200" s="7">
         <v>286</v>
@@ -8160,7 +8180,7 @@
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -8175,7 +8195,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8190,12 +8210,12 @@
         <v>48</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -8210,7 +8230,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8222,10 +8242,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -8258,7 +8278,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8270,7 +8290,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c t="s" r="J204" s="7">
         <v>152</v>
@@ -8278,7 +8298,7 @@
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -8293,7 +8313,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8305,28 +8325,46 @@
         <v>29</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
-      <c r="A206" s="6"/>
-      <c r="B206" s="7"/>
-      <c r="C206" s="7"/>
+      <c t="s" r="A206" s="6">
+        <v>13</v>
+      </c>
+      <c r="B206" s="7">
+        <v>1127</v>
+      </c>
+      <c t="s" r="C206" s="7">
+        <v>14</v>
+      </c>
       <c r="D206" s="7"/>
-      <c r="E206" s="7"/>
-      <c r="F206" s="7"/>
-      <c r="G206" s="8"/>
-      <c r="H206" s="8"/>
-      <c r="I206" s="7"/>
-      <c r="J206" s="7"/>
+      <c t="s" r="E206" s="7">
+        <v>347</v>
+      </c>
+      <c r="F206" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G206" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H206" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I206" s="7">
+        <v>67</v>
+      </c>
+      <c t="s" r="J206" s="7">
+        <v>352</v>
+      </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
       <c r="M206" s="7"/>
@@ -8336,119 +8374,99 @@
         <v>13</v>
       </c>
       <c r="B207" s="7">
-        <v>919</v>
+        <v>1128</v>
       </c>
       <c t="s" r="C207" s="7">
         <v>14</v>
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G207" s="8">
-        <v>256</v>
+        <v>17</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>263</v>
+        <v>353</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>168</v>
-      </c>
-      <c t="s" r="K207" s="7">
-        <v>179</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="K207" s="7"/>
       <c r="L207" s="7"/>
-      <c t="s" r="M207" s="7">
-        <v>228</v>
-      </c>
+      <c r="M207" s="7"/>
     </row>
     <row r="208" ht="14.25" customHeight="1">
-      <c t="s" r="A208" s="6">
-        <v>13</v>
-      </c>
-      <c r="B208" s="7">
-        <v>5530</v>
-      </c>
-      <c t="s" r="C208" s="7">
-        <v>14</v>
-      </c>
+      <c r="A208" s="6"/>
+      <c r="B208" s="7"/>
+      <c r="C208" s="7"/>
       <c r="D208" s="7"/>
-      <c t="s" r="E208" s="7">
-        <v>351</v>
-      </c>
-      <c r="F208" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G208" s="8">
-        <v>82</v>
-      </c>
-      <c t="s" r="H208" s="8">
-        <v>352</v>
-      </c>
-      <c t="s" r="I208" s="7">
-        <v>76</v>
-      </c>
-      <c t="s" r="J208" s="7">
-        <v>40</v>
-      </c>
+      <c r="E208" s="7"/>
+      <c r="F208" s="7"/>
+      <c r="G208" s="8"/>
+      <c r="H208" s="8"/>
+      <c r="I208" s="7"/>
+      <c r="J208" s="7"/>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
-      <c t="s" r="M208" s="7">
-        <v>144</v>
-      </c>
+      <c r="M208" s="7"/>
     </row>
     <row r="209" ht="14.25" customHeight="1">
       <c t="s" r="A209" s="6">
         <v>13</v>
       </c>
       <c r="B209" s="7">
-        <v>5531</v>
+        <v>919</v>
       </c>
       <c t="s" r="C209" s="7">
         <v>14</v>
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>352</v>
+        <v>256</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>82</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>353</v>
+        <v>263</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>354</v>
-      </c>
-      <c r="K209" s="7"/>
+        <v>167</v>
+      </c>
+      <c t="s" r="K209" s="7">
+        <v>178</v>
+      </c>
       <c r="L209" s="7"/>
-      <c r="M209" s="7"/>
+      <c t="s" r="M209" s="7">
+        <v>227</v>
+      </c>
     </row>
     <row r="210" ht="15" customHeight="1">
       <c t="s" r="A210" s="6">
         <v>13</v>
       </c>
       <c r="B210" s="7">
-        <v>834</v>
+        <v>5530</v>
       </c>
       <c t="s" r="C210" s="7">
         <v>14</v>
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8457,29 +8475,49 @@
         <v>82</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>25</v>
+        <v>356</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>355</v>
+        <v>40</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
-      <c r="M210" s="7"/>
+      <c t="s" r="M210" s="7">
+        <v>144</v>
+      </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
-      <c r="A211" s="6"/>
-      <c r="B211" s="7"/>
-      <c r="C211" s="7"/>
+      <c t="s" r="A211" s="6">
+        <v>13</v>
+      </c>
+      <c r="B211" s="7">
+        <v>5531</v>
+      </c>
+      <c t="s" r="C211" s="7">
+        <v>14</v>
+      </c>
       <c r="D211" s="7"/>
-      <c r="E211" s="7"/>
-      <c r="F211" s="7"/>
-      <c r="G211" s="8"/>
-      <c r="H211" s="8"/>
-      <c r="I211" s="7"/>
-      <c r="J211" s="7"/>
+      <c t="s" r="E211" s="7">
+        <v>355</v>
+      </c>
+      <c r="F211" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G211" s="8">
+        <v>356</v>
+      </c>
+      <c t="s" r="H211" s="8">
+        <v>82</v>
+      </c>
+      <c t="s" r="I211" s="7">
+        <v>357</v>
+      </c>
+      <c t="s" r="J211" s="7">
+        <v>358</v>
+      </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c r="M211" s="7"/>
@@ -8489,104 +8527,82 @@
         <v>13</v>
       </c>
       <c r="B212" s="7">
-        <v>224</v>
+        <v>834</v>
       </c>
       <c t="s" r="C212" s="7">
         <v>14</v>
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>122</v>
+        <v>25</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>319</v>
+        <v>57</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>247</v>
+        <v>359</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
-      <c t="s" r="M212" s="7">
-        <v>357</v>
-      </c>
+      <c r="M212" s="7"/>
     </row>
     <row r="213" ht="14.25" customHeight="1">
-      <c t="s" r="A213" s="6">
-        <v>13</v>
-      </c>
-      <c r="B213" s="7">
-        <v>741</v>
-      </c>
-      <c t="s" r="C213" s="7">
-        <v>14</v>
-      </c>
+      <c r="A213" s="6"/>
+      <c r="B213" s="7"/>
+      <c r="C213" s="7"/>
       <c r="D213" s="7"/>
-      <c t="s" r="E213" s="7">
-        <v>356</v>
-      </c>
-      <c r="F213" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G213" s="8">
-        <v>122</v>
-      </c>
-      <c t="s" r="H213" s="8">
-        <v>94</v>
-      </c>
-      <c t="s" r="I213" s="7">
-        <v>358</v>
-      </c>
-      <c t="s" r="J213" s="7">
-        <v>167</v>
-      </c>
+      <c r="E213" s="7"/>
+      <c r="F213" s="7"/>
+      <c r="G213" s="8"/>
+      <c r="H213" s="8"/>
+      <c r="I213" s="7"/>
+      <c r="J213" s="7"/>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
-      <c t="s" r="M213" s="7">
-        <v>141</v>
-      </c>
+      <c r="M213" s="7"/>
     </row>
     <row r="214" ht="14.25" customHeight="1">
       <c t="s" r="A214" s="6">
         <v>13</v>
       </c>
       <c r="B214" s="7">
-        <v>740</v>
+        <v>224</v>
       </c>
       <c t="s" r="C214" s="7">
         <v>14</v>
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c t="s" r="H214" s="8">
         <v>122</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>359</v>
+        <v>320</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>308</v>
+        <v>247</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -8594,14 +8610,14 @@
         <v>13</v>
       </c>
       <c r="B215" s="7">
-        <v>227</v>
+        <v>741</v>
       </c>
       <c t="s" r="C215" s="7">
         <v>14</v>
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8610,18 +8626,18 @@
         <v>122</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>179</v>
+        <v>362</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>19</v>
+        <v>166</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>361</v>
+        <v>141</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -8629,34 +8645,34 @@
         <v>13</v>
       </c>
       <c r="B216" s="7">
-        <v>278</v>
+        <v>740</v>
       </c>
       <c t="s" r="C216" s="7">
         <v>14</v>
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>37</v>
+        <v>308</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>192</v>
+        <v>364</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -8664,134 +8680,134 @@
         <v>13</v>
       </c>
       <c r="B217" s="7">
-        <v>279</v>
+        <v>227</v>
       </c>
       <c t="s" r="C217" s="7">
         <v>14</v>
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>237</v>
+        <v>178</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>108</v>
+        <v>19</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
-      <c r="A218" s="6"/>
-      <c r="B218" s="7"/>
-      <c r="C218" s="7"/>
+      <c t="s" r="A218" s="6">
+        <v>13</v>
+      </c>
+      <c r="B218" s="7">
+        <v>278</v>
+      </c>
+      <c t="s" r="C218" s="7">
+        <v>14</v>
+      </c>
       <c r="D218" s="7"/>
-      <c r="E218" s="7"/>
-      <c r="F218" s="7"/>
-      <c r="G218" s="8"/>
-      <c r="H218" s="8"/>
-      <c r="I218" s="7"/>
-      <c r="J218" s="7"/>
+      <c t="s" r="E218" s="7">
+        <v>360</v>
+      </c>
+      <c r="F218" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G218" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H218" s="8">
+        <v>119</v>
+      </c>
+      <c t="s" r="I218" s="7">
+        <v>366</v>
+      </c>
+      <c t="s" r="J218" s="7">
+        <v>37</v>
+      </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
-      <c r="M218" s="7"/>
+      <c t="s" r="M218" s="7">
+        <v>191</v>
+      </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
       <c t="s" r="A219" s="6">
         <v>13</v>
       </c>
       <c r="B219" s="7">
-        <v>449</v>
+        <v>279</v>
       </c>
       <c t="s" r="C219" s="7">
         <v>14</v>
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>29</v>
+        <v>119</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>95</v>
+        <v>237</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>365</v>
+        <v>109</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
-      <c t="s" r="A220" s="6">
-        <v>13</v>
-      </c>
-      <c r="B220" s="7">
-        <v>450</v>
-      </c>
-      <c t="s" r="C220" s="7">
-        <v>14</v>
-      </c>
+      <c r="A220" s="6"/>
+      <c r="B220" s="7"/>
+      <c r="C220" s="7"/>
       <c r="D220" s="7"/>
-      <c t="s" r="E220" s="7">
-        <v>364</v>
-      </c>
-      <c r="F220" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G220" s="8">
-        <v>21</v>
-      </c>
-      <c t="s" r="H220" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I220" s="7">
-        <v>201</v>
-      </c>
-      <c t="s" r="J220" s="7">
-        <v>367</v>
-      </c>
+      <c r="E220" s="7"/>
+      <c r="F220" s="7"/>
+      <c r="G220" s="8"/>
+      <c r="H220" s="8"/>
+      <c r="I220" s="7"/>
+      <c r="J220" s="7"/>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
-      <c t="s" r="M220" s="7">
-        <v>367</v>
-      </c>
+      <c r="M220" s="7"/>
     </row>
     <row r="221" ht="14.25" customHeight="1">
       <c t="s" r="A221" s="6">
         <v>13</v>
       </c>
       <c r="B221" s="7">
-        <v>137</v>
+        <v>449</v>
       </c>
       <c t="s" r="C221" s="7">
         <v>14</v>
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8800,18 +8816,18 @@
         <v>29</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>287</v>
+        <v>369</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>287</v>
+        <v>370</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -8819,34 +8835,34 @@
         <v>13</v>
       </c>
       <c r="B222" s="7">
-        <v>640</v>
+        <v>450</v>
       </c>
       <c t="s" r="C222" s="7">
         <v>14</v>
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>197</v>
+        <v>371</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -8854,47 +8870,49 @@
         <v>13</v>
       </c>
       <c r="B223" s="7">
-        <v>639</v>
+        <v>137</v>
       </c>
       <c t="s" r="C223" s="7">
         <v>14</v>
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c t="s" r="H223" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>135</v>
+        <v>287</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
-      <c r="M223" s="7"/>
+      <c t="s" r="M223" s="7">
+        <v>287</v>
+      </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
       <c t="s" r="A224" s="6">
         <v>13</v>
       </c>
       <c r="B224" s="7">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c t="s" r="C224" s="7">
         <v>14</v>
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8906,28 +8924,30 @@
         <v>46</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
-      <c r="M224" s="7"/>
+      <c t="s" r="M224" s="7">
+        <v>372</v>
+      </c>
     </row>
     <row r="225" ht="15" customHeight="1">
       <c t="s" r="A225" s="6">
         <v>13</v>
       </c>
       <c r="B225" s="7">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c t="s" r="C225" s="7">
         <v>14</v>
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8939,26 +8959,46 @@
         <v>17</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>282</v>
+        <v>65</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>316</v>
+        <v>135</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
-      <c r="M225" s="7"/>
+      <c t="s" r="M225" s="7">
+        <v>281</v>
+      </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
-      <c r="A226" s="6"/>
-      <c r="B226" s="7"/>
-      <c r="C226" s="7"/>
+      <c t="s" r="A226" s="6">
+        <v>13</v>
+      </c>
+      <c r="B226" s="7">
+        <v>644</v>
+      </c>
+      <c t="s" r="C226" s="7">
+        <v>14</v>
+      </c>
       <c r="D226" s="7"/>
-      <c r="E226" s="7"/>
-      <c r="F226" s="7"/>
-      <c r="G226" s="8"/>
-      <c r="H226" s="8"/>
-      <c r="I226" s="7"/>
-      <c r="J226" s="7"/>
+      <c t="s" r="E226" s="7">
+        <v>368</v>
+      </c>
+      <c r="F226" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G226" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H226" s="8">
+        <v>46</v>
+      </c>
+      <c t="s" r="I226" s="7">
+        <v>67</v>
+      </c>
+      <c t="s" r="J226" s="7">
+        <v>162</v>
+      </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c r="M226" s="7"/>
@@ -8968,84 +9008,62 @@
         <v>13</v>
       </c>
       <c r="B227" s="7">
-        <v>212</v>
+        <v>645</v>
       </c>
       <c t="s" r="C227" s="7">
         <v>14</v>
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>122</v>
+        <v>17</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>98</v>
+        <v>282</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
-      <c t="s" r="M227" s="7">
-        <v>370</v>
-      </c>
+      <c r="M227" s="7"/>
     </row>
     <row r="228" ht="14.25" customHeight="1">
-      <c t="s" r="A228" s="6">
-        <v>13</v>
-      </c>
-      <c r="B228" s="7">
-        <v>215</v>
-      </c>
-      <c t="s" r="C228" s="7">
-        <v>14</v>
-      </c>
+      <c r="A228" s="6"/>
+      <c r="B228" s="7"/>
+      <c r="C228" s="7"/>
       <c r="D228" s="7"/>
-      <c t="s" r="E228" s="7">
-        <v>369</v>
-      </c>
-      <c r="F228" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G228" s="8">
-        <v>122</v>
-      </c>
-      <c t="s" r="H228" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I228" s="7">
-        <v>31</v>
-      </c>
-      <c t="s" r="J228" s="7">
-        <v>310</v>
-      </c>
+      <c r="E228" s="7"/>
+      <c r="F228" s="7"/>
+      <c r="G228" s="8"/>
+      <c r="H228" s="8"/>
+      <c r="I228" s="7"/>
+      <c r="J228" s="7"/>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
-      <c t="s" r="M228" s="7">
-        <v>371</v>
-      </c>
+      <c r="M228" s="7"/>
     </row>
     <row r="229" ht="14.25" customHeight="1">
       <c t="s" r="A229" s="6">
         <v>13</v>
       </c>
       <c r="B229" s="7">
-        <v>138</v>
+        <v>212</v>
       </c>
       <c t="s" r="C229" s="7">
         <v>14</v>
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -9054,18 +9072,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>29</v>
+        <v>122</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>106</v>
+        <v>258</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -9073,34 +9091,34 @@
         <v>13</v>
       </c>
       <c r="B230" s="7">
-        <v>147</v>
+        <v>215</v>
       </c>
       <c t="s" r="C230" s="7">
         <v>14</v>
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>29</v>
+        <v>122</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -9108,14 +9126,14 @@
         <v>13</v>
       </c>
       <c r="B231" s="7">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c t="s" r="C231" s="7">
         <v>14</v>
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9127,43 +9145,65 @@
         <v>29</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>302</v>
+        <v>131</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>212</v>
+        <v>107</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
-      <c r="M231" s="7"/>
+      <c t="s" r="M231" s="7">
+        <v>376</v>
+      </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
-      <c r="A232" s="6"/>
-      <c r="B232" s="7"/>
-      <c r="C232" s="7"/>
+      <c t="s" r="A232" s="6">
+        <v>13</v>
+      </c>
+      <c r="B232" s="7">
+        <v>147</v>
+      </c>
+      <c t="s" r="C232" s="7">
+        <v>14</v>
+      </c>
       <c r="D232" s="7"/>
-      <c r="E232" s="7"/>
-      <c r="F232" s="7"/>
-      <c r="G232" s="8"/>
-      <c r="H232" s="8"/>
-      <c r="I232" s="7"/>
-      <c r="J232" s="7"/>
+      <c t="s" r="E232" s="7">
+        <v>373</v>
+      </c>
+      <c r="F232" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G232" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H232" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I232" s="7">
+        <v>134</v>
+      </c>
+      <c t="s" r="J232" s="7">
+        <v>289</v>
+      </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
-      <c r="M232" s="7"/>
+      <c t="s" r="M232" s="7">
+        <v>79</v>
+      </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
       <c t="s" r="A233" s="6">
         <v>13</v>
       </c>
       <c r="B233" s="7">
-        <v>270</v>
+        <v>648</v>
       </c>
       <c t="s" r="C233" s="7">
         <v>14</v>
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9172,123 +9212,99 @@
         <v>17</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>118</v>
+        <v>46</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>221</v>
+        <v>254</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>96</v>
+        <v>377</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
-      <c t="s" r="M233" s="7">
-        <v>224</v>
-      </c>
+      <c r="M233" s="7"/>
     </row>
     <row r="234" ht="14.25" customHeight="1">
       <c t="s" r="A234" s="6">
         <v>13</v>
       </c>
       <c r="B234" s="7">
-        <v>271</v>
+        <v>647</v>
       </c>
       <c t="s" r="C234" s="7">
         <v>14</v>
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>118</v>
+        <v>46</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>98</v>
+        <v>304</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
-      <c t="s" r="M234" s="7">
-        <v>376</v>
-      </c>
+      <c r="M234" s="7"/>
     </row>
     <row r="235" ht="15" customHeight="1">
-      <c t="s" r="A235" s="6">
-        <v>13</v>
-      </c>
-      <c r="B235" s="7">
-        <v>1624</v>
-      </c>
-      <c t="s" r="C235" s="7">
-        <v>14</v>
-      </c>
+      <c r="A235" s="6"/>
+      <c r="B235" s="7"/>
+      <c r="C235" s="7"/>
       <c r="D235" s="7"/>
-      <c t="s" r="E235" s="7">
-        <v>374</v>
-      </c>
-      <c r="F235" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G235" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H235" s="8">
-        <v>46</v>
-      </c>
-      <c t="s" r="I235" s="7">
-        <v>377</v>
-      </c>
-      <c t="s" r="J235" s="7">
-        <v>74</v>
-      </c>
+      <c r="E235" s="7"/>
+      <c r="F235" s="7"/>
+      <c r="G235" s="8"/>
+      <c r="H235" s="8"/>
+      <c r="I235" s="7"/>
+      <c r="J235" s="7"/>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
-      <c t="s" r="M235" s="7">
-        <v>378</v>
-      </c>
+      <c r="M235" s="7"/>
     </row>
     <row r="236" ht="14.25" customHeight="1">
       <c t="s" r="A236" s="6">
         <v>13</v>
       </c>
       <c r="B236" s="7">
-        <v>715</v>
+        <v>270</v>
       </c>
       <c t="s" r="C236" s="7">
         <v>14</v>
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>379</v>
+        <v>223</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9296,82 +9312,104 @@
         <v>13</v>
       </c>
       <c r="B237" s="7">
-        <v>714</v>
+        <v>271</v>
       </c>
       <c t="s" r="C237" s="7">
         <v>14</v>
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>197</v>
+        <v>99</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>144</v>
+        <v>380</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
-      <c r="M237" s="7"/>
+      <c t="s" r="M237" s="7">
+        <v>381</v>
+      </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
-      <c r="A238" s="6"/>
-      <c r="B238" s="7"/>
-      <c r="C238" s="7"/>
+      <c t="s" r="A238" s="6">
+        <v>13</v>
+      </c>
+      <c r="B238" s="7">
+        <v>1624</v>
+      </c>
+      <c t="s" r="C238" s="7">
+        <v>14</v>
+      </c>
       <c r="D238" s="7"/>
-      <c r="E238" s="7"/>
-      <c r="F238" s="7"/>
-      <c r="G238" s="8"/>
-      <c r="H238" s="8"/>
-      <c r="I238" s="7"/>
-      <c r="J238" s="7"/>
+      <c t="s" r="E238" s="7">
+        <v>379</v>
+      </c>
+      <c r="F238" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G238" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H238" s="8">
+        <v>46</v>
+      </c>
+      <c t="s" r="I238" s="7">
+        <v>382</v>
+      </c>
+      <c t="s" r="J238" s="7">
+        <v>74</v>
+      </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
-      <c r="M238" s="7"/>
+      <c t="s" r="M238" s="7">
+        <v>383</v>
+      </c>
     </row>
     <row r="239" ht="14.25" customHeight="1">
       <c t="s" r="A239" s="6">
         <v>13</v>
       </c>
       <c r="B239" s="7">
-        <v>823</v>
+        <v>715</v>
       </c>
       <c t="s" r="C239" s="7">
         <v>14</v>
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>138</v>
+        <v>46</v>
       </c>
       <c t="s" r="H239" s="8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>381</v>
+        <v>227</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9379,270 +9417,272 @@
         <v>13</v>
       </c>
       <c r="B240" s="7">
-        <v>327</v>
+        <v>714</v>
       </c>
       <c t="s" r="C240" s="7">
         <v>14</v>
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G240" s="8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>119</v>
+        <v>196</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>192</v>
+        <v>144</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
-      <c t="s" r="A241" s="6">
-        <v>13</v>
-      </c>
-      <c r="B241" s="7">
-        <v>326</v>
-      </c>
-      <c t="s" r="C241" s="7">
-        <v>14</v>
-      </c>
+      <c r="A241" s="6"/>
+      <c r="B241" s="7"/>
+      <c r="C241" s="7"/>
       <c r="D241" s="7"/>
-      <c t="s" r="E241" s="7">
-        <v>380</v>
-      </c>
-      <c r="F241" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G241" s="8">
-        <v>21</v>
-      </c>
-      <c t="s" r="H241" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I241" s="7">
-        <v>237</v>
-      </c>
-      <c t="s" r="J241" s="7">
-        <v>239</v>
-      </c>
+      <c r="E241" s="7"/>
+      <c r="F241" s="7"/>
+      <c r="G241" s="8"/>
+      <c r="H241" s="8"/>
+      <c r="I241" s="7"/>
+      <c r="J241" s="7"/>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c r="M241" s="7"/>
     </row>
     <row r="242" ht="14.25" customHeight="1">
       <c t="s" r="A242" s="6">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B242" s="7">
-        <v>91</v>
+        <v>823</v>
       </c>
       <c t="s" r="C242" s="7">
         <v>14</v>
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>17</v>
+        <v>138</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>384</v>
+        <v>17</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>219</v>
+        <v>387</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>381</v>
+        <v>47</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
-      <c r="M242" s="7"/>
+      <c t="s" r="M242" s="7">
+        <v>388</v>
+      </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
-      <c r="A243" s="6"/>
-      <c r="B243" s="7"/>
-      <c r="C243" s="7"/>
+      <c t="s" r="A243" s="6">
+        <v>13</v>
+      </c>
+      <c r="B243" s="7">
+        <v>327</v>
+      </c>
+      <c t="s" r="C243" s="7">
+        <v>14</v>
+      </c>
       <c r="D243" s="7"/>
-      <c r="E243" s="7"/>
-      <c r="F243" s="7"/>
-      <c r="G243" s="8"/>
-      <c r="H243" s="8"/>
-      <c r="I243" s="7"/>
-      <c r="J243" s="7"/>
+      <c t="s" r="E243" s="7">
+        <v>386</v>
+      </c>
+      <c r="F243" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G243" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H243" s="8">
+        <v>21</v>
+      </c>
+      <c t="s" r="I243" s="7">
+        <v>120</v>
+      </c>
+      <c t="s" r="J243" s="7">
+        <v>191</v>
+      </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
-      <c r="M243" s="7"/>
+      <c t="s" r="M243" s="7">
+        <v>389</v>
+      </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
       <c t="s" r="A244" s="6">
         <v>13</v>
       </c>
       <c r="B244" s="7">
-        <v>503</v>
+        <v>326</v>
       </c>
       <c t="s" r="C244" s="7">
         <v>14</v>
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>96</v>
+        <v>237</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>177</v>
+        <v>239</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
       <c t="s" r="A245" s="6">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="B245" s="7">
-        <v>701</v>
+        <v>91</v>
       </c>
       <c t="s" r="C245" s="7">
         <v>14</v>
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>30</v>
+        <v>391</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>179</v>
+        <v>387</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
-      <c t="s" r="M245" s="7">
-        <v>309</v>
-      </c>
+      <c r="M245" s="7"/>
     </row>
     <row r="246" ht="14.25" customHeight="1">
-      <c t="s" r="A246" s="6">
-        <v>13</v>
-      </c>
-      <c r="B246" s="7">
-        <v>702</v>
-      </c>
-      <c t="s" r="C246" s="7">
-        <v>14</v>
-      </c>
+      <c r="A246" s="6"/>
+      <c r="B246" s="7"/>
+      <c r="C246" s="7"/>
       <c r="D246" s="7"/>
-      <c t="s" r="E246" s="7">
-        <v>385</v>
-      </c>
-      <c r="F246" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G246" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H246" s="8">
-        <v>46</v>
-      </c>
-      <c t="s" r="I246" s="7">
-        <v>299</v>
-      </c>
-      <c t="s" r="J246" s="7">
-        <v>105</v>
-      </c>
+      <c r="E246" s="7"/>
+      <c r="F246" s="7"/>
+      <c r="G246" s="8"/>
+      <c r="H246" s="8"/>
+      <c r="I246" s="7"/>
+      <c r="J246" s="7"/>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
-      <c t="s" r="M246" s="7">
-        <v>105</v>
-      </c>
+      <c r="M246" s="7"/>
     </row>
     <row r="247" ht="14.25" customHeight="1">
-      <c r="A247" s="6"/>
-      <c r="B247" s="7"/>
-      <c r="C247" s="7"/>
+      <c t="s" r="A247" s="6">
+        <v>13</v>
+      </c>
+      <c r="B247" s="7">
+        <v>503</v>
+      </c>
+      <c t="s" r="C247" s="7">
+        <v>14</v>
+      </c>
       <c r="D247" s="7"/>
-      <c r="E247" s="7"/>
-      <c r="F247" s="7"/>
-      <c r="G247" s="8"/>
-      <c r="H247" s="8"/>
-      <c r="I247" s="7"/>
-      <c r="J247" s="7"/>
+      <c t="s" r="E247" s="7">
+        <v>392</v>
+      </c>
+      <c r="F247" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G247" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H247" s="8">
+        <v>46</v>
+      </c>
+      <c t="s" r="I247" s="7">
+        <v>97</v>
+      </c>
+      <c t="s" r="J247" s="7">
+        <v>176</v>
+      </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
-      <c r="M247" s="7"/>
+      <c t="s" r="M247" s="7">
+        <v>393</v>
+      </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
       <c t="s" r="A248" s="6">
         <v>13</v>
       </c>
       <c r="B248" s="7">
-        <v>813</v>
+        <v>701</v>
       </c>
       <c t="s" r="C248" s="7">
         <v>14</v>
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>128</v>
+        <v>30</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>97</v>
+        <v>202</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>388</v>
+        <v>178</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -9650,84 +9690,64 @@
         <v>13</v>
       </c>
       <c r="B249" s="7">
-        <v>970</v>
+        <v>702</v>
       </c>
       <c t="s" r="C249" s="7">
         <v>14</v>
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>128</v>
+        <v>30</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>367</v>
+        <v>299</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>389</v>
+        <v>106</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
-      <c t="s" r="A250" s="6">
-        <v>13</v>
-      </c>
-      <c r="B250" s="7">
-        <v>633</v>
-      </c>
-      <c t="s" r="C250" s="7">
-        <v>14</v>
-      </c>
+      <c r="A250" s="6"/>
+      <c r="B250" s="7"/>
+      <c r="C250" s="7"/>
       <c r="D250" s="7"/>
-      <c t="s" r="E250" s="7">
-        <v>387</v>
-      </c>
-      <c r="F250" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G250" s="8">
-        <v>46</v>
-      </c>
-      <c t="s" r="H250" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I250" s="7">
-        <v>119</v>
-      </c>
-      <c t="s" r="J250" s="7">
-        <v>390</v>
-      </c>
+      <c r="E250" s="7"/>
+      <c r="F250" s="7"/>
+      <c r="G250" s="8"/>
+      <c r="H250" s="8"/>
+      <c r="I250" s="7"/>
+      <c r="J250" s="7"/>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
-      <c t="s" r="M250" s="7">
-        <v>238</v>
-      </c>
+      <c r="M250" s="7"/>
     </row>
     <row r="251" ht="14.25" customHeight="1">
       <c t="s" r="A251" s="6">
         <v>13</v>
       </c>
       <c r="B251" s="7">
-        <v>262</v>
+        <v>813</v>
       </c>
       <c t="s" r="C251" s="7">
         <v>14</v>
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9736,72 +9756,96 @@
         <v>17</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>391</v>
+        <v>128</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>345</v>
+        <v>395</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
-      <c r="M251" s="7"/>
+      <c t="s" r="M251" s="7">
+        <v>308</v>
+      </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
       <c t="s" r="A252" s="6">
         <v>13</v>
       </c>
       <c r="B252" s="7">
-        <v>263</v>
+        <v>970</v>
       </c>
       <c t="s" r="C252" s="7">
         <v>14</v>
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>391</v>
+        <v>128</v>
       </c>
       <c t="s" r="H252" s="8">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>392</v>
+        <v>371</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>393</v>
+        <v>20</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
-      <c r="M252" s="7"/>
+      <c t="s" r="M252" s="7">
+        <v>396</v>
+      </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
-      <c r="A253" s="6"/>
-      <c r="B253" s="7"/>
-      <c r="C253" s="7"/>
+      <c t="s" r="A253" s="6">
+        <v>13</v>
+      </c>
+      <c r="B253" s="7">
+        <v>633</v>
+      </c>
+      <c t="s" r="C253" s="7">
+        <v>14</v>
+      </c>
       <c r="D253" s="7"/>
-      <c r="E253" s="7"/>
-      <c r="F253" s="7"/>
-      <c r="G253" s="8"/>
-      <c r="H253" s="8"/>
-      <c r="I253" s="7"/>
-      <c r="J253" s="7"/>
+      <c t="s" r="E253" s="7">
+        <v>394</v>
+      </c>
+      <c r="F253" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G253" s="8">
+        <v>46</v>
+      </c>
+      <c t="s" r="H253" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I253" s="7">
+        <v>120</v>
+      </c>
+      <c t="s" r="J253" s="7">
+        <v>397</v>
+      </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
-      <c r="M253" s="7"/>
+      <c t="s" r="M253" s="7">
+        <v>238</v>
+      </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
       <c t="s" r="A254" s="6">
         <v>13</v>
       </c>
       <c r="B254" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="C254" s="7">
         <v>14</v>
@@ -9817,26 +9861,24 @@
         <v>17</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>307</v>
+        <v>346</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
-      <c t="s" r="M254" s="7">
-        <v>395</v>
-      </c>
+      <c r="M254" s="7"/>
     </row>
     <row r="255" ht="15" customHeight="1">
       <c t="s" r="A255" s="6">
         <v>13</v>
       </c>
       <c r="B255" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="C255" s="7">
         <v>14</v>
@@ -9849,91 +9891,69 @@
         <v>321</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c t="s" r="H255" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>141</v>
+        <v>399</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
-      <c t="s" r="M255" s="7">
-        <v>31</v>
-      </c>
+      <c r="M255" s="7"/>
     </row>
     <row r="256" ht="14.25" customHeight="1">
-      <c t="s" r="A256" s="6">
-        <v>13</v>
-      </c>
-      <c r="B256" s="7">
-        <v>807</v>
-      </c>
-      <c t="s" r="C256" s="7">
-        <v>14</v>
-      </c>
+      <c r="A256" s="6"/>
+      <c r="B256" s="7"/>
+      <c r="C256" s="7"/>
       <c r="D256" s="7"/>
-      <c t="s" r="E256" s="7">
-        <v>394</v>
-      </c>
-      <c r="F256" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G256" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H256" s="8">
-        <v>190</v>
-      </c>
-      <c t="s" r="I256" s="7">
-        <v>105</v>
-      </c>
-      <c t="s" r="J256" s="7">
-        <v>50</v>
-      </c>
+      <c r="E256" s="7"/>
+      <c r="F256" s="7"/>
+      <c r="G256" s="8"/>
+      <c r="H256" s="8"/>
+      <c r="I256" s="7"/>
+      <c r="J256" s="7"/>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
-      <c t="s" r="M256" s="7">
-        <v>396</v>
-      </c>
+      <c r="M256" s="7"/>
     </row>
     <row r="257" ht="14.25" customHeight="1">
       <c t="s" r="A257" s="6">
         <v>13</v>
       </c>
       <c r="B257" s="7">
-        <v>800</v>
+        <v>260</v>
       </c>
       <c t="s" r="C257" s="7">
         <v>14</v>
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>190</v>
+        <v>17</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>17</v>
+        <v>398</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>134</v>
+        <v>59</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -9941,165 +9961,167 @@
         <v>13</v>
       </c>
       <c r="B258" s="7">
-        <v>648</v>
+        <v>261</v>
       </c>
       <c t="s" r="C258" s="7">
         <v>14</v>
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>17</v>
+        <v>398</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>254</v>
+        <v>141</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
-      <c r="M258" s="7"/>
+      <c t="s" r="M258" s="7">
+        <v>31</v>
+      </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
       <c t="s" r="A259" s="6">
         <v>13</v>
       </c>
       <c r="B259" s="7">
-        <v>647</v>
+        <v>807</v>
       </c>
       <c t="s" r="C259" s="7">
         <v>14</v>
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>17</v>
+        <v>189</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>304</v>
+        <v>106</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>398</v>
+        <v>50</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
-      <c r="M259" s="7"/>
+      <c t="s" r="M259" s="7">
+        <v>402</v>
+      </c>
     </row>
     <row r="260" ht="15" customHeight="1">
-      <c r="A260" s="6"/>
-      <c r="B260" s="7"/>
-      <c r="C260" s="7"/>
+      <c t="s" r="A260" s="6">
+        <v>13</v>
+      </c>
+      <c r="B260" s="7">
+        <v>800</v>
+      </c>
+      <c t="s" r="C260" s="7">
+        <v>14</v>
+      </c>
       <c r="D260" s="7"/>
-      <c r="E260" s="7"/>
-      <c r="F260" s="7"/>
-      <c r="G260" s="8"/>
-      <c r="H260" s="8"/>
-      <c r="I260" s="7"/>
-      <c r="J260" s="7"/>
+      <c t="s" r="E260" s="7">
+        <v>400</v>
+      </c>
+      <c r="F260" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G260" s="8">
+        <v>189</v>
+      </c>
+      <c t="s" r="H260" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I260" s="7">
+        <v>134</v>
+      </c>
+      <c t="s" r="J260" s="7">
+        <v>208</v>
+      </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
-      <c r="M260" s="7"/>
+      <c t="s" r="M260" s="7">
+        <v>77</v>
+      </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
       <c t="s" r="A261" s="6">
         <v>13</v>
       </c>
       <c r="B261" s="7">
-        <v>431</v>
+        <v>154</v>
       </c>
       <c t="s" r="C261" s="7">
         <v>14</v>
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F261" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H261" s="8">
         <v>29</v>
       </c>
-      <c t="s" r="H261" s="8">
-        <v>400</v>
-      </c>
       <c t="s" r="I261" s="7">
-        <v>260</v>
+        <v>302</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>401</v>
+        <v>211</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
-      <c t="s" r="M261" s="7">
-        <v>402</v>
-      </c>
+      <c r="M261" s="7"/>
     </row>
     <row r="262" ht="14.25" customHeight="1">
-      <c t="s" r="A262" s="6">
-        <v>13</v>
-      </c>
-      <c r="B262" s="7">
-        <v>430</v>
-      </c>
-      <c t="s" r="C262" s="7">
-        <v>14</v>
-      </c>
+      <c r="A262" s="6"/>
+      <c r="B262" s="7"/>
+      <c r="C262" s="7"/>
       <c r="D262" s="7"/>
-      <c t="s" r="E262" s="7">
-        <v>399</v>
-      </c>
-      <c r="F262" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G262" s="8">
-        <v>400</v>
-      </c>
-      <c t="s" r="H262" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I262" s="7">
-        <v>307</v>
-      </c>
-      <c t="s" r="J262" s="7">
-        <v>258</v>
-      </c>
+      <c r="E262" s="7"/>
+      <c r="F262" s="7"/>
+      <c r="G262" s="8"/>
+      <c r="H262" s="8"/>
+      <c r="I262" s="7"/>
+      <c r="J262" s="7"/>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
-      <c t="s" r="M262" s="7">
-        <v>403</v>
-      </c>
+      <c r="M262" s="7"/>
     </row>
     <row r="263" ht="14.25" customHeight="1">
       <c t="s" r="A263" s="6">
         <v>13</v>
       </c>
       <c r="B263" s="7">
-        <v>403</v>
+        <v>431</v>
       </c>
       <c t="s" r="C263" s="7">
         <v>14</v>
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="F263" s="7">
         <v>320</v>
@@ -10111,15 +10133,15 @@
         <v>404</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>337</v>
+        <v>405</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>33</v>
+        <v>406</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -10127,14 +10149,14 @@
         <v>13</v>
       </c>
       <c r="B264" s="7">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c t="s" r="C264" s="7">
         <v>14</v>
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="F264" s="7">
         <v>320</v>
@@ -10146,15 +10168,15 @@
         <v>29</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>103</v>
+        <v>307</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>405</v>
+        <v>258</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>396</v>
+        <v>407</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -10162,14 +10184,14 @@
         <v>13</v>
       </c>
       <c r="B265" s="7">
-        <v>7712</v>
+        <v>403</v>
       </c>
       <c t="s" r="C265" s="7">
         <v>14</v>
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="F265" s="7">
         <v>320</v>
@@ -10178,149 +10200,149 @@
         <v>29</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>354</v>
+        <v>236</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>407</v>
+        <v>338</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
-      <c r="M265" s="7"/>
+      <c t="s" r="M265" s="7">
+        <v>33</v>
+      </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
       <c t="s" r="A266" s="6">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B266" s="7">
-        <v>7713</v>
+        <v>404</v>
       </c>
       <c t="s" r="C266" s="7">
         <v>14</v>
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="F266" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>43</v>
+        <v>104</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
-      <c r="M266" s="7"/>
+      <c t="s" r="M266" s="7">
+        <v>402</v>
+      </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
-      <c r="A267" s="6"/>
-      <c r="B267" s="7"/>
-      <c r="C267" s="7"/>
+      <c t="s" r="A267" s="6">
+        <v>13</v>
+      </c>
+      <c r="B267" s="7">
+        <v>7712</v>
+      </c>
+      <c t="s" r="C267" s="7">
+        <v>14</v>
+      </c>
       <c r="D267" s="7"/>
-      <c r="E267" s="7"/>
-      <c r="F267" s="7"/>
-      <c r="G267" s="8"/>
-      <c r="H267" s="8"/>
-      <c r="I267" s="7"/>
-      <c r="J267" s="7"/>
+      <c t="s" r="E267" s="7">
+        <v>403</v>
+      </c>
+      <c r="F267" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G267" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H267" s="8">
+        <v>410</v>
+      </c>
+      <c t="s" r="I267" s="7">
+        <v>358</v>
+      </c>
+      <c t="s" r="J267" s="7">
+        <v>411</v>
+      </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c r="M267" s="7"/>
     </row>
     <row r="268" ht="14.25" customHeight="1">
       <c t="s" r="A268" s="6">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="B268" s="7">
-        <v>123</v>
+        <v>7713</v>
       </c>
       <c t="s" r="C268" s="7">
         <v>14</v>
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="F268" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G268" s="8">
+        <v>410</v>
+      </c>
+      <c t="s" r="H268" s="8">
         <v>29</v>
       </c>
-      <c t="s" r="H268" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I268" s="7">
-        <v>221</v>
+        <v>43</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
-      <c t="s" r="M268" s="7">
-        <v>410</v>
-      </c>
+      <c r="M268" s="7"/>
     </row>
     <row r="269" ht="14.25" customHeight="1">
-      <c t="s" r="A269" s="6">
-        <v>13</v>
-      </c>
-      <c r="B269" s="7">
-        <v>130</v>
-      </c>
-      <c t="s" r="C269" s="7">
-        <v>14</v>
-      </c>
+      <c r="A269" s="6"/>
+      <c r="B269" s="7"/>
+      <c r="C269" s="7"/>
       <c r="D269" s="7"/>
-      <c t="s" r="E269" s="7">
-        <v>409</v>
-      </c>
-      <c r="F269" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G269" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H269" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I269" s="7">
-        <v>141</v>
-      </c>
-      <c t="s" r="J269" s="7">
-        <v>329</v>
-      </c>
+      <c r="E269" s="7"/>
+      <c r="F269" s="7"/>
+      <c r="G269" s="8"/>
+      <c r="H269" s="8"/>
+      <c r="I269" s="7"/>
+      <c r="J269" s="7"/>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
-      <c t="s" r="M269" s="7">
-        <v>411</v>
-      </c>
+      <c r="M269" s="7"/>
     </row>
     <row r="270" ht="15" customHeight="1">
       <c t="s" r="A270" s="6">
         <v>13</v>
       </c>
       <c r="B270" s="7">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c t="s" r="C270" s="7">
         <v>14</v>
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10332,15 +10354,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>116</v>
+        <v>220</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>64</v>
+        <v>405</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10348,14 +10370,14 @@
         <v>13</v>
       </c>
       <c r="B271" s="7">
-        <v>308</v>
+        <v>130</v>
       </c>
       <c t="s" r="C271" s="7">
         <v>14</v>
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10364,18 +10386,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H271" s="8">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>90</v>
+        <v>330</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>37</v>
+        <v>415</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -10383,134 +10405,134 @@
         <v>13</v>
       </c>
       <c r="B272" s="7">
-        <v>307</v>
+        <v>133</v>
       </c>
       <c t="s" r="C272" s="7">
         <v>14</v>
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G272" s="8">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c t="s" r="H272" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>390</v>
+        <v>117</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>413</v>
+        <v>64</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>344</v>
+        <v>416</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
-      <c r="A273" s="6"/>
-      <c r="B273" s="7"/>
-      <c r="C273" s="7"/>
+      <c t="s" r="A273" s="6">
+        <v>13</v>
+      </c>
+      <c r="B273" s="7">
+        <v>308</v>
+      </c>
+      <c t="s" r="C273" s="7">
+        <v>14</v>
+      </c>
       <c r="D273" s="7"/>
-      <c r="E273" s="7"/>
-      <c r="F273" s="7"/>
-      <c r="G273" s="8"/>
-      <c r="H273" s="8"/>
-      <c r="I273" s="7"/>
-      <c r="J273" s="7"/>
+      <c t="s" r="E273" s="7">
+        <v>413</v>
+      </c>
+      <c r="F273" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G273" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H273" s="8">
+        <v>36</v>
+      </c>
+      <c t="s" r="I273" s="7">
+        <v>48</v>
+      </c>
+      <c t="s" r="J273" s="7">
+        <v>90</v>
+      </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
-      <c r="M273" s="7"/>
+      <c t="s" r="M273" s="7">
+        <v>37</v>
+      </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
       <c t="s" r="A274" s="6">
         <v>13</v>
       </c>
       <c r="B274" s="7">
-        <v>122</v>
+        <v>307</v>
       </c>
       <c t="s" r="C274" s="7">
         <v>14</v>
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>222</v>
+        <v>397</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>202</v>
+        <v>417</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>386</v>
+        <v>418</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
-      <c t="s" r="A275" s="6">
-        <v>13</v>
-      </c>
-      <c r="B275" s="7">
-        <v>135</v>
-      </c>
-      <c t="s" r="C275" s="7">
-        <v>14</v>
-      </c>
+      <c r="A275" s="6"/>
+      <c r="B275" s="7"/>
+      <c r="C275" s="7"/>
       <c r="D275" s="7"/>
-      <c t="s" r="E275" s="7">
-        <v>414</v>
-      </c>
-      <c r="F275" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G275" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="H275" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I275" s="7">
-        <v>286</v>
-      </c>
-      <c t="s" r="J275" s="7">
-        <v>33</v>
-      </c>
+      <c r="E275" s="7"/>
+      <c r="F275" s="7"/>
+      <c r="G275" s="8"/>
+      <c r="H275" s="8"/>
+      <c r="I275" s="7"/>
+      <c r="J275" s="7"/>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
-      <c t="s" r="M275" s="7">
-        <v>415</v>
-      </c>
+      <c r="M275" s="7"/>
     </row>
     <row r="276" ht="14.25" customHeight="1">
       <c t="s" r="A276" s="6">
         <v>13</v>
       </c>
       <c r="B276" s="7">
-        <v>842</v>
+        <v>122</v>
       </c>
       <c t="s" r="C276" s="7">
         <v>14</v>
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10519,18 +10541,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>243</v>
+        <v>29</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>64</v>
+        <v>221</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>54</v>
+        <v>201</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
-        <v>416</v>
+        <v>393</v>
       </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
@@ -10538,132 +10560,132 @@
         <v>13</v>
       </c>
       <c r="B277" s="7">
-        <v>843</v>
+        <v>135</v>
       </c>
       <c t="s" r="C277" s="7">
         <v>14</v>
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>243</v>
+        <v>29</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>230</v>
+        <v>286</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>270</v>
+        <v>33</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
-      <c r="M277" s="7"/>
+      <c t="s" r="M277" s="7">
+        <v>420</v>
+      </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
-      <c r="A278" s="6"/>
-      <c r="B278" s="7"/>
-      <c r="C278" s="7"/>
+      <c t="s" r="A278" s="6">
+        <v>13</v>
+      </c>
+      <c r="B278" s="7">
+        <v>842</v>
+      </c>
+      <c t="s" r="C278" s="7">
+        <v>14</v>
+      </c>
       <c r="D278" s="7"/>
-      <c r="E278" s="7"/>
-      <c r="F278" s="7"/>
-      <c r="G278" s="8"/>
-      <c r="H278" s="8"/>
-      <c r="I278" s="7"/>
-      <c r="J278" s="7"/>
+      <c t="s" r="E278" s="7">
+        <v>419</v>
+      </c>
+      <c r="F278" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G278" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H278" s="8">
+        <v>243</v>
+      </c>
+      <c t="s" r="I278" s="7">
+        <v>64</v>
+      </c>
+      <c t="s" r="J278" s="7">
+        <v>54</v>
+      </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
-      <c r="M278" s="7"/>
+      <c t="s" r="M278" s="7">
+        <v>421</v>
+      </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
       <c t="s" r="A279" s="6">
         <v>13</v>
       </c>
       <c r="B279" s="7">
-        <v>447</v>
+        <v>843</v>
       </c>
       <c t="s" r="C279" s="7">
         <v>14</v>
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F279" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>29</v>
+        <v>243</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>167</v>
+        <v>229</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>329</v>
+        <v>270</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
-      <c t="s" r="M279" s="7">
-        <v>418</v>
-      </c>
+      <c r="M279" s="7"/>
     </row>
     <row r="280" ht="15" customHeight="1">
-      <c t="s" r="A280" s="6">
-        <v>13</v>
-      </c>
-      <c r="B280" s="7">
-        <v>440</v>
-      </c>
-      <c t="s" r="C280" s="7">
-        <v>14</v>
-      </c>
+      <c r="A280" s="6"/>
+      <c r="B280" s="7"/>
+      <c r="C280" s="7"/>
       <c r="D280" s="7"/>
-      <c t="s" r="E280" s="7">
-        <v>417</v>
-      </c>
-      <c r="F280" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G280" s="8">
-        <v>21</v>
-      </c>
-      <c t="s" r="H280" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I280" s="7">
-        <v>419</v>
-      </c>
-      <c t="s" r="J280" s="7">
-        <v>64</v>
-      </c>
+      <c r="E280" s="7"/>
+      <c r="F280" s="7"/>
+      <c r="G280" s="8"/>
+      <c r="H280" s="8"/>
+      <c r="I280" s="7"/>
+      <c r="J280" s="7"/>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
-      <c t="s" r="M280" s="7">
-        <v>420</v>
-      </c>
+      <c r="M280" s="7"/>
     </row>
     <row r="281" ht="14.25" customHeight="1">
       <c t="s" r="A281" s="6">
         <v>13</v>
       </c>
       <c r="B281" s="7">
-        <v>903</v>
+        <v>447</v>
       </c>
       <c t="s" r="C281" s="7">
         <v>14</v>
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10672,18 +10694,18 @@
         <v>29</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>26</v>
+        <v>330</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -10691,47 +10713,49 @@
         <v>13</v>
       </c>
       <c r="B282" s="7">
-        <v>904</v>
+        <v>440</v>
       </c>
       <c t="s" r="C282" s="7">
         <v>14</v>
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>190</v>
+        <v>21</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>302</v>
+        <v>424</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>422</v>
+        <v>64</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
-      <c r="M282" s="7"/>
+      <c t="s" r="M282" s="7">
+        <v>425</v>
+      </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
       <c t="s" r="A283" s="6">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B283" s="7">
-        <v>1980</v>
+        <v>903</v>
       </c>
       <c t="s" r="C283" s="7">
         <v>14</v>
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10740,136 +10764,134 @@
         <v>29</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>423</v>
+        <v>189</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>424</v>
+        <v>134</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
-      <c r="M283" s="7"/>
+      <c t="s" r="M283" s="7">
+        <v>426</v>
+      </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
-      <c r="A284" s="6"/>
-      <c r="B284" s="7"/>
-      <c r="C284" s="7"/>
+      <c t="s" r="A284" s="6">
+        <v>13</v>
+      </c>
+      <c r="B284" s="7">
+        <v>904</v>
+      </c>
+      <c t="s" r="C284" s="7">
+        <v>14</v>
+      </c>
       <c r="D284" s="7"/>
-      <c r="E284" s="7"/>
-      <c r="F284" s="7"/>
-      <c r="G284" s="8"/>
-      <c r="H284" s="8"/>
-      <c r="I284" s="7"/>
-      <c r="J284" s="7"/>
+      <c t="s" r="E284" s="7">
+        <v>422</v>
+      </c>
+      <c r="F284" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G284" s="8">
+        <v>189</v>
+      </c>
+      <c t="s" r="H284" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I284" s="7">
+        <v>302</v>
+      </c>
+      <c t="s" r="J284" s="7">
+        <v>427</v>
+      </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c r="M284" s="7"/>
     </row>
     <row r="285" ht="15" customHeight="1">
       <c t="s" r="A285" s="6">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="B285" s="7">
-        <v>126</v>
+        <v>1980</v>
       </c>
       <c t="s" r="C285" s="7">
         <v>14</v>
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="F285" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>29</v>
+        <v>428</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>96</v>
+        <v>429</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>203</v>
+        <v>18</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
-      <c t="s" r="M285" s="7">
-        <v>426</v>
-      </c>
+      <c r="M285" s="7"/>
     </row>
     <row r="286" ht="14.25" customHeight="1">
-      <c t="s" r="A286" s="6">
-        <v>13</v>
-      </c>
-      <c r="B286" s="7">
-        <v>1491</v>
-      </c>
-      <c t="s" r="C286" s="7">
-        <v>14</v>
-      </c>
+      <c r="A286" s="6"/>
+      <c r="B286" s="7"/>
+      <c r="C286" s="7"/>
       <c r="D286" s="7"/>
-      <c t="s" r="E286" s="7">
-        <v>425</v>
-      </c>
-      <c r="F286" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G286" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="H286" s="8">
-        <v>94</v>
-      </c>
-      <c t="s" r="I286" s="7">
-        <v>427</v>
-      </c>
-      <c t="s" r="J286" s="7">
-        <v>337</v>
-      </c>
+      <c r="E286" s="7"/>
+      <c r="F286" s="7"/>
+      <c r="G286" s="8"/>
+      <c r="H286" s="8"/>
+      <c r="I286" s="7"/>
+      <c r="J286" s="7"/>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
-      <c t="s" r="M286" s="7">
-        <v>337</v>
-      </c>
+      <c r="M286" s="7"/>
     </row>
     <row r="287" ht="14.25" customHeight="1">
       <c t="s" r="A287" s="6">
         <v>13</v>
       </c>
       <c r="B287" s="7">
-        <v>1492</v>
+        <v>126</v>
       </c>
       <c t="s" r="C287" s="7">
         <v>14</v>
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>287</v>
+        <v>202</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -10877,14 +10899,14 @@
         <v>13</v>
       </c>
       <c r="B288" s="7">
-        <v>511</v>
+        <v>1491</v>
       </c>
       <c t="s" r="C288" s="7">
         <v>14</v>
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10893,18 +10915,18 @@
         <v>29</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>87</v>
+        <v>432</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>237</v>
+        <v>338</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>429</v>
+        <v>338</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -10912,47 +10934,49 @@
         <v>13</v>
       </c>
       <c r="B289" s="7">
-        <v>512</v>
+        <v>1492</v>
       </c>
       <c t="s" r="C289" s="7">
         <v>14</v>
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c t="s" r="H289" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>158</v>
+        <v>104</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>144</v>
+        <v>287</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
-      <c r="M289" s="7"/>
+      <c t="s" r="M289" s="7">
+        <v>433</v>
+      </c>
     </row>
     <row r="290" ht="15" customHeight="1">
       <c t="s" r="A290" s="6">
         <v>13</v>
       </c>
       <c r="B290" s="7">
-        <v>1127</v>
+        <v>511</v>
       </c>
       <c t="s" r="C290" s="7">
         <v>14</v>
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10961,46 +10985,48 @@
         <v>29</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>430</v>
+        <v>237</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
-      <c r="M290" s="7"/>
+      <c t="s" r="M290" s="7">
+        <v>434</v>
+      </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
       <c t="s" r="A291" s="6">
         <v>13</v>
       </c>
       <c r="B291" s="7">
-        <v>1128</v>
+        <v>512</v>
       </c>
       <c t="s" r="C291" s="7">
         <v>14</v>
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c t="s" r="H291" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>431</v>
+        <v>158</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>432</v>
+        <v>144</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -11033,7 +11059,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -11042,18 +11068,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -11068,19 +11094,19 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>19</v>
@@ -11088,7 +11114,7 @@
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -11103,7 +11129,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -11112,18 +11138,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c t="s" r="I295" s="7">
         <v>76</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c t="s" r="M295" s="7">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
@@ -11138,13 +11164,13 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>17</v>
@@ -11153,7 +11179,7 @@
         <v>254</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>159</v>
+        <v>91</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -11186,7 +11212,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -11198,15 +11224,15 @@
         <v>46</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -11221,7 +11247,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -11241,7 +11267,7 @@
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
       <c t="s" r="M299" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1">
@@ -11256,7 +11282,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -11271,11 +11297,13 @@
         <v>289</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
-      <c r="M300" s="7"/>
+      <c t="s" r="M300" s="7">
+        <v>440</v>
+      </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
       <c t="s" r="A301" s="6">
@@ -11289,7 +11317,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -11298,13 +11326,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -11322,22 +11350,22 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -11370,7 +11398,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -11385,12 +11413,12 @@
         <v>299</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11405,7 +11433,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -11420,12 +11448,12 @@
         <v>76</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11440,7 +11468,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -11449,13 +11477,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="I306" s="7">
         <v>239</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -11473,22 +11501,22 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>430</v>
+        <v>352</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -11521,7 +11549,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11533,7 +11561,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>32</v>
@@ -11556,7 +11584,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11568,7 +11596,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>76</v>
@@ -11576,7 +11604,7 @@
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11591,7 +11619,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11600,18 +11628,18 @@
         <v>29</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c t="s" r="I311" s="7">
         <v>90</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11626,13 +11654,13 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>29</v>
@@ -11659,7 +11687,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11707,7 +11735,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
@@ -11719,15 +11747,15 @@
         <v>291</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -11742,7 +11770,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -11757,12 +11785,12 @@
         <v>32</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -11777,7 +11805,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -11789,7 +11817,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>77</v>
@@ -11797,7 +11825,7 @@
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>452</v>
+        <v>109</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -11812,7 +11840,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -11827,11 +11855,15 @@
         <v>121</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>218</v>
-      </c>
-      <c r="K318" s="7"/>
+        <v>217</v>
+      </c>
+      <c t="s" r="K318" s="7">
+        <v>229</v>
+      </c>
       <c r="L318" s="7"/>
-      <c r="M318" s="7"/>
+      <c t="s" r="M318" s="7">
+        <v>315</v>
+      </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
       <c r="A319" s="6"/>
@@ -11860,7 +11892,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11869,18 +11901,18 @@
         <v>46</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c t="s" r="I320" s="7">
         <v>48</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -11895,19 +11927,19 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c t="s" r="J321" s="7">
         <v>158</v>
@@ -11915,7 +11947,7 @@
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -11930,7 +11962,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11942,10 +11974,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>159</v>
+        <v>91</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11978,7 +12010,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -11987,10 +12019,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c t="s" r="J324" s="7">
         <v>90</v>
@@ -11998,7 +12030,7 @@
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -12013,27 +12045,27 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -12048,7 +12080,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
@@ -12057,13 +12089,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c t="s" r="I326" s="7">
         <v>254</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -12081,22 +12113,22 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c t="s" r="H327" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -12129,7 +12161,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -12138,10 +12170,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>62</v>
@@ -12164,27 +12196,27 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c t="s" r="H330" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -12199,7 +12231,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -12211,7 +12243,7 @@
         <v>122</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>64</v>
@@ -12219,7 +12251,7 @@
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -12234,7 +12266,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -12249,12 +12281,12 @@
         <v>143</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12269,7 +12301,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -12278,7 +12310,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c t="s" r="I333" s="7">
         <v>313</v>
@@ -12302,13 +12334,13 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>17</v>
@@ -12317,7 +12349,7 @@
         <v>305</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -12350,7 +12382,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -12359,18 +12391,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
       <c t="s" r="M336" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
@@ -12385,27 +12417,27 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c t="s" r="H337" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -12420,7 +12452,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -12429,7 +12461,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c t="s" r="I338" s="7">
         <v>249</v>
@@ -12440,7 +12472,7 @@
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12455,19 +12487,19 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c t="s" r="H339" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c t="s" r="J339" s="7">
         <v>32</v>
@@ -12475,7 +12507,7 @@
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -12490,7 +12522,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12499,18 +12531,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c t="s" r="I340" s="7">
         <v>76</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12525,19 +12557,19 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>158</v>
@@ -12545,7 +12577,7 @@
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -12575,7 +12607,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -12584,18 +12616,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -12610,19 +12642,19 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c t="s" r="J344" s="7">
         <v>289</v>
@@ -12630,7 +12662,7 @@
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -12645,22 +12677,22 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12678,22 +12710,22 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12726,7 +12758,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -12735,18 +12767,18 @@
         <v>29</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -12761,13 +12793,13 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>122</v>
@@ -12776,12 +12808,12 @@
         <v>249</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -12796,7 +12828,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -12805,10 +12837,10 @@
         <v>122</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c t="s" r="J350" s="7">
         <v>131</v>
@@ -12816,7 +12848,7 @@
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -12831,22 +12863,22 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c t="s" r="H351" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12866,7 +12898,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -12875,7 +12907,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c t="s" r="I352" s="7">
         <v>37</v>
@@ -12885,7 +12917,9 @@
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
-      <c r="M352" s="7"/>
+      <c t="s" r="M352" s="7">
+        <v>485</v>
+      </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
       <c t="s" r="A353" s="6">
@@ -12899,13 +12933,13 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c t="s" r="H353" s="8">
         <v>29</v>
@@ -12932,7 +12966,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12941,13 +12975,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c t="s" r="I354" s="7">
         <v>266</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12965,22 +12999,22 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -13013,7 +13047,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -13025,15 +13059,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -13048,7 +13082,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -13060,7 +13094,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="J358" s="7">
         <v>31</v>
@@ -13083,7 +13117,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -13095,15 +13129,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -13118,7 +13152,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -13133,12 +13167,12 @@
         <v>19</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13153,7 +13187,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -13165,7 +13199,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c t="s" r="J361" s="7">
         <v>70</v>
@@ -13201,7 +13235,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13213,15 +13247,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -13236,7 +13270,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -13248,15 +13282,15 @@
         <v>46</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -13271,7 +13305,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -13280,13 +13314,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -13306,27 +13340,27 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -13341,7 +13375,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -13350,13 +13384,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c t="s" r="I367" s="7">
         <v>144</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -13374,13 +13408,13 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>46</v>
@@ -13422,7 +13456,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13442,7 +13476,7 @@
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13457,7 +13491,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -13469,7 +13503,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c t="s" r="J371" s="7">
         <v>33</v>
@@ -13477,7 +13511,7 @@
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -13492,7 +13526,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -13507,7 +13541,7 @@
         <v>64</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13527,7 +13561,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -13547,7 +13581,7 @@
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -13562,7 +13596,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -13610,7 +13644,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -13619,10 +13653,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c t="s" r="J376" s="7">
         <v>263</v>
@@ -13630,7 +13664,7 @@
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -13645,22 +13679,22 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13680,7 +13714,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13689,7 +13723,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c t="s" r="I378" s="7">
         <v>34</v>
@@ -13700,7 +13734,7 @@
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -13715,13 +13749,13 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>17</v>
@@ -13730,7 +13764,7 @@
         <v>265</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>430</v>
+        <v>352</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13763,7 +13797,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13783,7 +13817,7 @@
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -13798,7 +13832,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13813,12 +13847,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
       <c t="s" r="M382" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
@@ -13833,7 +13867,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13845,10 +13879,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13868,7 +13902,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13880,7 +13914,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>56</v>
@@ -13901,7 +13935,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13913,10 +13947,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13949,7 +13983,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -13958,10 +13992,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>83</v>
@@ -13969,7 +14003,7 @@
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -13984,27 +14018,27 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -14019,7 +14053,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -14031,15 +14065,15 @@
         <v>36</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -14054,7 +14088,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -14066,7 +14100,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>310</v>
@@ -14089,7 +14123,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -14098,17 +14132,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c t="s" r="J391" s="7">
         <v>302</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
-      <c r="M391" s="7"/>
+      <c t="s" r="M391" s="7">
+        <v>79</v>
+      </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
       <c t="s" r="A392" s="6">
@@ -14122,19 +14158,19 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c t="s" r="J392" s="7">
         <v>270</v>
@@ -14155,7 +14191,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -14170,7 +14206,7 @@
         <v>255</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -14203,7 +14239,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -14215,15 +14251,15 @@
         <v>75</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -14238,7 +14274,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -14250,15 +14286,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -14273,7 +14309,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -14293,7 +14329,7 @@
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -14308,7 +14344,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -14341,7 +14377,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -14356,7 +14392,7 @@
         <v>255</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -14389,7 +14425,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -14424,7 +14460,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -14439,12 +14475,12 @@
         <v>300</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
       <c t="s" r="M402" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
@@ -14459,7 +14495,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -14471,7 +14507,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>41</v>
@@ -14492,7 +14528,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -14504,7 +14540,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>277</v>
@@ -14540,7 +14576,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -14549,18 +14585,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -14575,27 +14611,27 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c t="s" r="I407" s="7">
         <v>276</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -14610,27 +14646,27 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G408" s="8">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -14645,13 +14681,13 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>17</v>
@@ -14693,7 +14729,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="F411" s="7">
         <v>320</v>
@@ -14702,7 +14738,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c t="s" r="I411" s="7">
         <v>47</v>
@@ -14728,13 +14764,13 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="F412" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>17</v>
@@ -14748,7 +14784,7 @@
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -14763,7 +14799,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
@@ -14772,10 +14808,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c t="s" r="J413" s="7">
         <v>26</v>
@@ -14796,13 +14832,13 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="F414" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>17</v>
@@ -14844,7 +14880,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
@@ -14856,15 +14892,15 @@
         <v>46</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -14879,7 +14915,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
@@ -14888,13 +14924,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14914,13 +14950,13 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>46</v>
@@ -14929,7 +14965,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14962,7 +14998,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F420" s="7">
         <v>330</v>
@@ -14971,20 +15007,20 @@
         <v>46</v>
       </c>
       <c t="s" r="H420" s="8">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c t="s" r="I420" s="7">
         <v>44</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c t="s" r="K420" s="7">
         <v>18</v>
       </c>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -14999,25 +15035,25 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G421" s="8">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c t="s" r="H421" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c t="s" r="K421" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
@@ -15051,7 +15087,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F423" s="7">
         <v>330</v>
@@ -15071,7 +15107,7 @@
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
@@ -15086,7 +15122,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F424" s="7">
         <v>330</v>
@@ -15101,7 +15137,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -15121,7 +15157,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F425" s="7">
         <v>330</v>
@@ -15133,14 +15169,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
-      <c r="M425" s="7"/>
+      <c t="s" r="M425" s="7">
+        <v>528</v>
+      </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
       <c r="A426" s="6"/>
@@ -15169,19 +15207,19 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="F427" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G427" s="8">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c t="s" r="H427" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c t="s" r="J427" s="7">
         <v>51</v>
@@ -15189,7 +15227,7 @@
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
       <c t="s" r="M427" s="7">
-        <v>527</v>
+        <v>531</v>
       </c>
     </row>
     <row r="428" ht="14.25" customHeight="1">
@@ -15204,7 +15242,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="F428" s="7">
         <v>330</v>
@@ -15213,13 +15251,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H428" s="8">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -15252,27 +15290,27 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G430" s="8">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c t="s" r="H430" s="8">
         <v>82</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
       <c t="s" r="M430" s="7">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
@@ -15302,7 +15340,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="F432" s="7">
         <v>330</v>
@@ -15311,18 +15349,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H432" s="8">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>430</v>
+        <v>352</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c t="s" r="M432" s="7">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
@@ -15337,22 +15375,22 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="F433" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G433" s="8">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c t="s" r="H433" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -15360,7 +15398,7 @@
     </row>
     <row r="434" ht="15.75" customHeight="1">
       <c t="s" r="A434" s="9">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B434" s="9"/>
       <c r="C434" s="9"/>
@@ -15380,7 +15418,7 @@
     <row r="435" ht="66" customHeight="1"/>
     <row r="436" ht="16.5" customHeight="1">
       <c t="s" r="A436" s="10">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B436" s="10"/>
       <c r="C436" s="10"/>
@@ -15393,7 +15431,7 @@
       <c r="J436" s="10"/>
       <c r="K436" s="10"/>
       <c t="s" r="L436" s="11">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="M436" s="11"/>
       <c r="N436" s="11"/>

--- a/Data/FlightPlan/FPL_09SEP26.xlsx
+++ b/Data/FlightPlan/FPL_09SEP26.xlsx
@@ -362,6 +362,9 @@
     <t>21:05</t>
   </si>
   <si>
+    <t>22:13</t>
+  </si>
+  <si>
     <t>VN-A522</t>
   </si>
   <si>
@@ -599,6 +602,9 @@
     <t>21:50</t>
   </si>
   <si>
+    <t>22:17</t>
+  </si>
+  <si>
     <t>22:45</t>
   </si>
   <si>
@@ -1010,6 +1016,78 @@
     <t>20:37</t>
   </si>
   <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>10:16</t>
+  </si>
+  <si>
+    <t>14:16</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>17:24</t>
+  </si>
+  <si>
+    <t>20:53</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>16:36</t>
+  </si>
+  <si>
+    <t>18:57</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>12:54</t>
+  </si>
+  <si>
+    <t>14:58</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>16:54</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>10:42</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>12:41</t>
+  </si>
+  <si>
+    <t>15:27</t>
+  </si>
+  <si>
     <t>CAN</t>
   </si>
   <si>
@@ -1019,78 +1097,6 @@
     <t>03:05</t>
   </si>
   <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>10:16</t>
-  </si>
-  <si>
-    <t>14:16</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>17:24</t>
-  </si>
-  <si>
-    <t>20:53</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>16:36</t>
-  </si>
-  <si>
-    <t>18:57</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>12:54</t>
-  </si>
-  <si>
-    <t>14:58</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>16:54</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>10:42</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>12:41</t>
-  </si>
-  <si>
-    <t>15:27</t>
-  </si>
-  <si>
     <t>VN-A636</t>
   </si>
   <si>
@@ -1196,7 +1202,7 @@
     <t>18:54</t>
   </si>
   <si>
-    <t>21:06</t>
+    <t>21:22</t>
   </si>
   <si>
     <t>VN-A643</t>
@@ -1214,6 +1220,9 @@
     <t>21:20</t>
   </si>
   <si>
+    <t>21:17</t>
+  </si>
+  <si>
     <t>23:30</t>
   </si>
   <si>
@@ -1280,6 +1289,9 @@
     <t>19:45</t>
   </si>
   <si>
+    <t>21:54</t>
+  </si>
+  <si>
     <t>VN-A649</t>
   </si>
   <si>
@@ -1439,6 +1451,9 @@
     <t>19:16</t>
   </si>
   <si>
+    <t>21:32</t>
+  </si>
+  <si>
     <t>VN-A663</t>
   </si>
   <si>
@@ -1643,9 +1658,6 @@
     <t>11:02</t>
   </si>
   <si>
-    <t>21:28</t>
-  </si>
-  <si>
     <t>VN-A693</t>
   </si>
   <si>
@@ -1682,6 +1694,9 @@
     <t>18:42</t>
   </si>
   <si>
+    <t>21:27</t>
+  </si>
+  <si>
     <t>VN-A811</t>
   </si>
   <si>
@@ -1715,6 +1730,9 @@
     <t>17:16</t>
   </si>
   <si>
+    <t>08:03</t>
+  </si>
+  <si>
     <t>VN-A816</t>
   </si>
   <si>
@@ -1736,7 +1754,7 @@
     <t>Total Record(s): 351</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 09, 2026 19:59</t>
+    <t xml:space="preserve">Generated on  Sep 09, 2026 20:23</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3411,7 +3429,9 @@
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
+      <c t="s" r="M42" s="7">
+        <v>117</v>
+      </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="6"/>
@@ -3440,7 +3460,7 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
@@ -3449,20 +3469,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H44" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J44" s="7">
         <v>46</v>
       </c>
       <c t="s" r="K44" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L44" s="7"/>
       <c t="s" r="M44" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
@@ -3477,25 +3497,25 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G45" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="H45" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J45" s="7">
         <v>18</v>
       </c>
       <c t="s" r="K45" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L45" s="7"/>
       <c t="s" r="M45" s="7">
@@ -3514,7 +3534,7 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
@@ -3526,7 +3546,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="J46" s="7">
         <v>34</v>
@@ -3534,7 +3554,7 @@
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
       <c t="s" r="M46" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
@@ -3549,7 +3569,7 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
@@ -3558,7 +3578,7 @@
         <v>21</v>
       </c>
       <c t="s" r="H47" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I47" s="7">
         <v>19</v>
@@ -3569,7 +3589,7 @@
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
       <c t="s" r="M47" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
@@ -3584,13 +3604,13 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G48" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H48" s="8">
         <v>21</v>
@@ -3619,7 +3639,7 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
@@ -3631,7 +3651,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="J49" s="7">
         <v>70</v>
@@ -3639,7 +3659,7 @@
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
       <c t="s" r="M49" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
@@ -3654,7 +3674,7 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3663,13 +3683,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H50" s="8">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3687,22 +3707,22 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G51" s="8">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="H51" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -3735,7 +3755,7 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
@@ -3744,18 +3764,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H53" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I53" s="7">
         <v>105</v>
       </c>
       <c t="s" r="J53" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
       <c t="s" r="M53" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
@@ -3770,27 +3790,27 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G54" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H54" s="8">
         <v>21</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c t="s" r="M54" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
@@ -3805,7 +3825,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3814,18 +3834,18 @@
         <v>21</v>
       </c>
       <c t="s" r="H55" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
       <c t="s" r="M55" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
@@ -3840,19 +3860,19 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G56" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H56" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="J56" s="7">
         <v>84</v>
@@ -3860,7 +3880,7 @@
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
       <c t="s" r="M56" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
@@ -3875,7 +3895,7 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3884,13 +3904,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H57" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="I57" s="7">
         <v>73</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -3923,7 +3943,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -3935,7 +3955,7 @@
         <v>64</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J59" s="7">
         <v>19</v>
@@ -3943,7 +3963,7 @@
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
       <c t="s" r="M59" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
@@ -3958,7 +3978,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3970,15 +3990,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
       <c t="s" r="M60" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
@@ -3993,7 +4013,7 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
@@ -4002,13 +4022,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H61" s="8">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
@@ -4026,19 +4046,19 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G62" s="8">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="H62" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="J62" s="7">
         <v>103</v>
@@ -4074,7 +4094,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -4086,15 +4106,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
       <c t="s" r="M64" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
@@ -4109,7 +4129,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -4144,7 +4164,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -4159,12 +4179,12 @@
         <v>108</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
       <c t="s" r="M66" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
@@ -4179,7 +4199,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -4194,12 +4214,12 @@
         <v>92</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
       <c t="s" r="M67" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
@@ -4214,7 +4234,7 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
@@ -4223,10 +4243,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H68" s="8">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J68" s="7">
         <v>96</v>
@@ -4234,7 +4254,7 @@
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
       <c t="s" r="M68" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
@@ -4249,22 +4269,22 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G69" s="8">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="H69" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -4297,7 +4317,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -4309,10 +4329,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -4345,7 +4365,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -4354,18 +4374,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H73" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
       <c t="s" r="M73" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
@@ -4380,13 +4400,13 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G74" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H74" s="8">
         <v>17</v>
@@ -4395,12 +4415,12 @@
         <v>80</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
       <c t="s" r="M74" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
@@ -4415,7 +4435,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -4424,18 +4444,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H75" s="8">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
       <c t="s" r="M75" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
@@ -4450,19 +4470,19 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G76" s="8">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c t="s" r="H76" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c t="s" r="J76" s="7">
         <v>101</v>
@@ -4498,7 +4518,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4513,12 +4533,12 @@
         <v>46</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
       <c t="s" r="M78" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
@@ -4533,7 +4553,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -4548,12 +4568,12 @@
         <v>77</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
       <c t="s" r="M79" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
@@ -4568,7 +4588,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4580,15 +4600,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c t="s" r="M80" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -4603,7 +4623,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4615,7 +4635,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="J81" s="7">
         <v>53</v>
@@ -4623,7 +4643,7 @@
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
       <c t="s" r="M81" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -4638,7 +4658,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4650,15 +4670,15 @@
         <v>31</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
       <c t="s" r="M82" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
@@ -4673,7 +4693,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4685,14 +4705,16 @@
         <v>30</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
-      <c r="M83" s="7"/>
+      <c t="s" r="M83" s="7">
+        <v>197</v>
+      </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
       <c t="s" r="A84" s="6">
@@ -4706,7 +4728,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4718,10 +4740,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4754,7 +4776,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4763,10 +4785,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J86" s="7">
         <v>19</v>
@@ -4774,7 +4796,7 @@
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
       <c t="s" r="M86" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
@@ -4789,27 +4811,27 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c t="s" r="H87" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
       <c t="s" r="M87" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="88" ht="14.25" customHeight="1">
@@ -4824,7 +4846,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4836,15 +4858,15 @@
         <v>87</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
       <c t="s" r="M88" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
@@ -4859,7 +4881,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4874,7 +4896,7 @@
         <v>84</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4907,7 +4929,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4916,13 +4938,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4942,27 +4964,27 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="H92" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
       <c t="s" r="M92" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
@@ -4977,7 +4999,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4986,10 +5008,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="J93" s="7">
         <v>104</v>
@@ -5025,7 +5047,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -5037,15 +5059,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -5060,7 +5082,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -5072,15 +5094,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -5095,7 +5117,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -5110,12 +5132,12 @@
         <v>20</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -5130,7 +5152,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -5142,10 +5164,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -5165,7 +5187,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -5180,14 +5202,14 @@
         <v>26</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="K99" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L99" s="7"/>
       <c t="s" r="M99" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
@@ -5202,7 +5224,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -5214,17 +5236,17 @@
         <v>30</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="K100" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L100" s="7"/>
       <c t="s" r="M100" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
@@ -5254,7 +5276,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -5263,10 +5285,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c t="s" r="J102" s="7">
         <v>49</v>
@@ -5289,27 +5311,27 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H103" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
       <c t="s" r="M103" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
@@ -5324,7 +5346,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5333,18 +5355,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H104" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I104" s="7">
         <v>41</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c t="s" r="M104" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
@@ -5359,22 +5381,22 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G105" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H105" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -5392,7 +5414,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5404,7 +5426,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="J106" s="7">
         <v>98</v>
@@ -5440,7 +5462,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5452,15 +5474,15 @@
         <v>37</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
       <c t="s" r="M108" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -5475,7 +5497,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5487,10 +5509,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -5510,7 +5532,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5522,7 +5544,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="J110" s="7">
         <v>108</v>
@@ -5530,7 +5552,7 @@
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
       <c t="s" r="M110" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -5545,7 +5567,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5557,7 +5579,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="J111" s="7">
         <v>34</v>
@@ -5565,7 +5587,7 @@
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5580,7 +5602,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5592,15 +5614,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5615,7 +5637,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5627,15 +5649,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
       <c t="s" r="M113" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
@@ -5650,7 +5672,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5659,13 +5681,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5683,22 +5705,22 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="H115" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5731,7 +5753,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5740,18 +5762,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
       <c t="s" r="M117" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -5766,27 +5788,27 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G118" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H118" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
       <c t="s" r="M118" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
@@ -5801,7 +5823,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5813,7 +5835,7 @@
         <v>76</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="J119" s="7">
         <v>104</v>
@@ -5849,13 +5871,13 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="H121" s="8">
         <v>30</v>
@@ -5864,7 +5886,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5884,7 +5906,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5893,7 +5915,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H122" s="8">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c t="s" r="I122" s="7">
         <v>22</v>
@@ -5904,7 +5926,7 @@
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
       <c t="s" r="M122" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -5919,27 +5941,27 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c t="s" r="H123" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
@@ -5954,7 +5976,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5966,10 +5988,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -6002,7 +6024,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -6014,15 +6036,15 @@
         <v>107</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -6037,7 +6059,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -6049,15 +6071,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
       <c t="s" r="M127" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
@@ -6072,7 +6094,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -6084,7 +6106,7 @@
         <v>87</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="J128" s="7">
         <v>19</v>
@@ -6092,7 +6114,7 @@
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
       <c t="s" r="M128" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
@@ -6107,7 +6129,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -6116,18 +6138,18 @@
         <v>87</v>
       </c>
       <c t="s" r="H129" s="8">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="I129" s="7">
         <v>50</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -6142,27 +6164,27 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G130" s="8">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="H130" s="8">
         <v>87</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
       <c t="s" r="M130" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
@@ -6177,7 +6199,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -6186,13 +6208,13 @@
         <v>87</v>
       </c>
       <c t="s" r="H131" s="8">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -6225,7 +6247,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -6237,15 +6259,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
@@ -6260,7 +6282,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -6272,15 +6294,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -6295,7 +6317,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -6315,7 +6337,7 @@
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
       <c t="s" r="M135" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -6330,7 +6352,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6342,15 +6364,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
       <c t="s" r="M136" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
@@ -6380,19 +6402,19 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c t="s" r="H138" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="J138" s="7">
         <v>22</v>
@@ -6400,7 +6422,7 @@
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
       <c t="s" r="M138" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
@@ -6415,7 +6437,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6427,7 +6449,7 @@
         <v>87</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c t="s" r="J139" s="7">
         <v>55</v>
@@ -6450,7 +6472,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -6465,12 +6487,12 @@
         <v>56</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
       <c t="s" r="M140" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
@@ -6485,7 +6507,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6497,10 +6519,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -6518,7 +6540,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6530,10 +6552,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -6566,7 +6588,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6586,7 +6608,7 @@
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c t="s" r="M144" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
@@ -6601,7 +6623,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6610,18 +6632,18 @@
         <v>87</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6636,13 +6658,13 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H146" s="8">
         <v>87</v>
@@ -6671,7 +6693,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6683,10 +6705,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6719,7 +6741,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6731,15 +6753,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
       <c t="s" r="M149" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
@@ -6754,7 +6776,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6763,10 +6785,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J150" s="7">
         <v>114</v>
@@ -6774,7 +6796,7 @@
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
       <c t="s" r="M150" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
@@ -6789,19 +6811,19 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J151" s="7">
         <v>85</v>
@@ -6809,7 +6831,7 @@
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c t="s" r="M151" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
@@ -6824,7 +6846,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6836,10 +6858,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6872,7 +6894,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6881,18 +6903,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -6907,19 +6929,19 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>56</v>
@@ -6927,7 +6949,7 @@
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -6942,7 +6964,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6951,13 +6973,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="I156" s="7">
         <v>61</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6990,7 +7012,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6999,10 +7021,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J158" s="7">
         <v>67</v>
@@ -7010,7 +7032,7 @@
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -7025,19 +7047,19 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="J159" s="7">
         <v>112</v>
@@ -7045,7 +7067,7 @@
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
       <c t="s" r="M159" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
@@ -7060,7 +7082,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -7069,18 +7091,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -7095,22 +7117,22 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -7143,7 +7165,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -7158,12 +7180,12 @@
         <v>65</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c t="s" r="M163" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -7178,7 +7200,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7190,10 +7212,10 @@
         <v>87</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -7213,7 +7235,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -7225,7 +7247,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c t="s" r="J165" s="7">
         <v>38</v>
@@ -7233,7 +7255,7 @@
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -7248,7 +7270,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -7260,15 +7282,15 @@
         <v>48</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -7283,7 +7305,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -7295,10 +7317,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -7316,7 +7338,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -7325,10 +7347,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c t="s" r="J168" s="7">
         <v>103</v>
@@ -7364,29 +7386,29 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="H170" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="K170" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7401,7 +7423,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7413,7 +7435,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c t="s" r="J171" s="7">
         <v>67</v>
@@ -7421,7 +7443,7 @@
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -7436,7 +7458,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7448,15 +7470,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
@@ -7471,7 +7493,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7480,18 +7502,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
       <c t="s" r="M173" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
@@ -7506,123 +7528,127 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
-      <c t="s" r="A175" s="6">
-        <v>13</v>
-      </c>
-      <c r="B175" s="7">
-        <v>7526</v>
-      </c>
-      <c t="s" r="C175" s="7">
-        <v>14</v>
-      </c>
+      <c r="A175" s="6"/>
+      <c r="B175" s="7"/>
+      <c r="C175" s="7"/>
       <c r="D175" s="7"/>
-      <c t="s" r="E175" s="7">
-        <v>322</v>
-      </c>
-      <c r="F175" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G175" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H175" s="8">
-        <v>333</v>
-      </c>
-      <c t="s" r="I175" s="7">
-        <v>334</v>
-      </c>
-      <c t="s" r="J175" s="7">
-        <v>27</v>
-      </c>
+      <c r="E175" s="7"/>
+      <c r="F175" s="7"/>
+      <c r="G175" s="8"/>
+      <c r="H175" s="8"/>
+      <c r="I175" s="7"/>
+      <c r="J175" s="7"/>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c r="M175" s="7"/>
     </row>
     <row r="176" ht="14.25" customHeight="1">
       <c t="s" r="A176" s="6">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="B176" s="7">
-        <v>7527</v>
+        <v>120</v>
       </c>
       <c t="s" r="C176" s="7">
         <v>14</v>
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>333</v>
+        <v>17</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>244</v>
+        <v>336</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>335</v>
+        <v>103</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
-      <c r="M176" s="7"/>
+      <c t="s" r="M176" s="7">
+        <v>337</v>
+      </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
-      <c r="A177" s="6"/>
-      <c r="B177" s="7"/>
-      <c r="C177" s="7"/>
+      <c t="s" r="A177" s="6">
+        <v>13</v>
+      </c>
+      <c r="B177" s="7">
+        <v>127</v>
+      </c>
+      <c t="s" r="C177" s="7">
+        <v>14</v>
+      </c>
       <c r="D177" s="7"/>
-      <c r="E177" s="7"/>
-      <c r="F177" s="7"/>
-      <c r="G177" s="8"/>
-      <c r="H177" s="8"/>
-      <c r="I177" s="7"/>
-      <c r="J177" s="7"/>
+      <c t="s" r="E177" s="7">
+        <v>335</v>
+      </c>
+      <c r="F177" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G177" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H177" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I177" s="7">
+        <v>325</v>
+      </c>
+      <c t="s" r="J177" s="7">
+        <v>32</v>
+      </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
-      <c r="M177" s="7"/>
+      <c t="s" r="M177" s="7">
+        <v>338</v>
+      </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
       <c t="s" r="A178" s="6">
         <v>13</v>
       </c>
       <c r="B178" s="7">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c t="s" r="C178" s="7">
         <v>14</v>
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7634,15 +7660,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>337</v>
+        <v>162</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>103</v>
+        <v>241</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -7650,14 +7676,14 @@
         <v>13</v>
       </c>
       <c r="B179" s="7">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c t="s" r="C179" s="7">
         <v>14</v>
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7669,15 +7695,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -7685,14 +7711,14 @@
         <v>13</v>
       </c>
       <c r="B180" s="7">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c t="s" r="C180" s="7">
         <v>14</v>
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7704,15 +7730,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>161</v>
+        <v>41</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>239</v>
+        <v>281</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7720,14 +7746,14 @@
         <v>13</v>
       </c>
       <c r="B181" s="7">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c t="s" r="C181" s="7">
         <v>14</v>
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7739,148 +7765,148 @@
         <v>17</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>341</v>
+        <v>225</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>226</v>
+        <v>96</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
-      <c t="s" r="M181" s="7">
-        <v>342</v>
-      </c>
+      <c r="M181" s="7"/>
     </row>
     <row r="182" ht="14.25" customHeight="1">
-      <c t="s" r="A182" s="6">
-        <v>13</v>
-      </c>
-      <c r="B182" s="7">
-        <v>150</v>
-      </c>
-      <c t="s" r="C182" s="7">
-        <v>14</v>
-      </c>
+      <c r="A182" s="6"/>
+      <c r="B182" s="7"/>
+      <c r="C182" s="7"/>
       <c r="D182" s="7"/>
-      <c t="s" r="E182" s="7">
-        <v>336</v>
-      </c>
-      <c r="F182" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G182" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H182" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I182" s="7">
-        <v>41</v>
-      </c>
-      <c t="s" r="J182" s="7">
-        <v>279</v>
-      </c>
+      <c r="E182" s="7"/>
+      <c r="F182" s="7"/>
+      <c r="G182" s="8"/>
+      <c r="H182" s="8"/>
+      <c r="I182" s="7"/>
+      <c r="J182" s="7"/>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
-      <c t="s" r="M182" s="7">
-        <v>343</v>
-      </c>
+      <c r="M182" s="7"/>
     </row>
     <row r="183" ht="14.25" customHeight="1">
       <c t="s" r="A183" s="6">
         <v>13</v>
       </c>
       <c r="B183" s="7">
-        <v>161</v>
+        <v>961</v>
       </c>
       <c t="s" r="C183" s="7">
         <v>14</v>
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H183" s="8">
         <v>30</v>
       </c>
-      <c t="s" r="H183" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I183" s="7">
-        <v>223</v>
+        <v>189</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>96</v>
+        <v>176</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
-      <c r="M183" s="7"/>
+      <c t="s" r="M183" s="7">
+        <v>140</v>
+      </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
-      <c r="A184" s="6"/>
-      <c r="B184" s="7"/>
-      <c r="C184" s="7"/>
+      <c t="s" r="A184" s="6">
+        <v>13</v>
+      </c>
+      <c r="B184" s="7">
+        <v>423</v>
+      </c>
+      <c t="s" r="C184" s="7">
+        <v>14</v>
+      </c>
       <c r="D184" s="7"/>
-      <c r="E184" s="7"/>
-      <c r="F184" s="7"/>
-      <c r="G184" s="8"/>
-      <c r="H184" s="8"/>
-      <c r="I184" s="7"/>
-      <c r="J184" s="7"/>
+      <c t="s" r="E184" s="7">
+        <v>343</v>
+      </c>
+      <c r="F184" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G184" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="H184" s="8">
+        <v>119</v>
+      </c>
+      <c t="s" r="I184" s="7">
+        <v>92</v>
+      </c>
+      <c t="s" r="J184" s="7">
+        <v>55</v>
+      </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
-      <c r="M184" s="7"/>
+      <c t="s" r="M184" s="7">
+        <v>344</v>
+      </c>
     </row>
     <row r="185" ht="15" customHeight="1">
       <c t="s" r="A185" s="6">
         <v>13</v>
       </c>
       <c r="B185" s="7">
-        <v>961</v>
+        <v>424</v>
       </c>
       <c t="s" r="C185" s="7">
         <v>14</v>
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G185" s="8">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c t="s" r="H185" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>188</v>
+        <v>39</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>175</v>
+        <v>320</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>139</v>
+        <v>345</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
       <c t="s" r="A186" s="6">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="B186" s="7">
-        <v>423</v>
+        <v>958</v>
       </c>
       <c t="s" r="C186" s="7">
         <v>14</v>
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7889,116 +7915,116 @@
         <v>30</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>118</v>
+        <v>346</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>55</v>
+        <v>147</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
-      <c t="s" r="M186" s="7">
-        <v>345</v>
-      </c>
+      <c r="M186" s="7"/>
     </row>
     <row r="187" ht="14.25" customHeight="1">
-      <c t="s" r="A187" s="6">
-        <v>13</v>
-      </c>
-      <c r="B187" s="7">
-        <v>424</v>
-      </c>
-      <c t="s" r="C187" s="7">
-        <v>14</v>
-      </c>
+      <c r="A187" s="6"/>
+      <c r="B187" s="7"/>
+      <c r="C187" s="7"/>
       <c r="D187" s="7"/>
-      <c t="s" r="E187" s="7">
-        <v>344</v>
-      </c>
-      <c r="F187" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G187" s="8">
-        <v>118</v>
-      </c>
-      <c t="s" r="H187" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="I187" s="7">
-        <v>39</v>
-      </c>
-      <c t="s" r="J187" s="7">
-        <v>318</v>
-      </c>
+      <c r="E187" s="7"/>
+      <c r="F187" s="7"/>
+      <c r="G187" s="8"/>
+      <c r="H187" s="8"/>
+      <c r="I187" s="7"/>
+      <c r="J187" s="7"/>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
-      <c t="s" r="M187" s="7">
-        <v>346</v>
-      </c>
+      <c r="M187" s="7"/>
     </row>
     <row r="188" ht="14.25" customHeight="1">
       <c t="s" r="A188" s="6">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="B188" s="7">
-        <v>958</v>
+        <v>720</v>
       </c>
       <c t="s" r="C188" s="7">
         <v>14</v>
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>347</v>
+        <v>125</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>97</v>
+        <v>18</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>146</v>
+        <v>348</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
-      <c r="M188" s="7"/>
+      <c t="s" r="M188" s="7">
+        <v>348</v>
+      </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
-      <c r="A189" s="6"/>
-      <c r="B189" s="7"/>
-      <c r="C189" s="7"/>
+      <c t="s" r="A189" s="6">
+        <v>13</v>
+      </c>
+      <c r="B189" s="7">
+        <v>721</v>
+      </c>
+      <c t="s" r="C189" s="7">
+        <v>14</v>
+      </c>
       <c r="D189" s="7"/>
-      <c r="E189" s="7"/>
-      <c r="F189" s="7"/>
-      <c r="G189" s="8"/>
-      <c r="H189" s="8"/>
-      <c r="I189" s="7"/>
-      <c r="J189" s="7"/>
+      <c t="s" r="E189" s="7">
+        <v>347</v>
+      </c>
+      <c r="F189" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G189" s="8">
+        <v>125</v>
+      </c>
+      <c t="s" r="H189" s="8">
+        <v>48</v>
+      </c>
+      <c t="s" r="I189" s="7">
+        <v>123</v>
+      </c>
+      <c t="s" r="J189" s="7">
+        <v>349</v>
+      </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
-      <c r="M189" s="7"/>
+      <c t="s" r="M189" s="7">
+        <v>350</v>
+      </c>
     </row>
     <row r="190" ht="15" customHeight="1">
       <c t="s" r="A190" s="6">
         <v>13</v>
       </c>
       <c r="B190" s="7">
-        <v>720</v>
+        <v>703</v>
       </c>
       <c t="s" r="C190" s="7">
         <v>14</v>
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -8007,18 +8033,18 @@
         <v>48</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>349</v>
+        <v>126</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -8026,134 +8052,134 @@
         <v>13</v>
       </c>
       <c r="B191" s="7">
-        <v>721</v>
+        <v>704</v>
       </c>
       <c t="s" r="C191" s="7">
         <v>14</v>
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>124</v>
+        <v>31</v>
       </c>
       <c t="s" r="H191" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>122</v>
+        <v>352</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>350</v>
+        <v>228</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
-      <c t="s" r="A192" s="6">
-        <v>13</v>
-      </c>
-      <c r="B192" s="7">
-        <v>703</v>
-      </c>
-      <c t="s" r="C192" s="7">
-        <v>14</v>
-      </c>
+      <c r="A192" s="6"/>
+      <c r="B192" s="7"/>
+      <c r="C192" s="7"/>
       <c r="D192" s="7"/>
-      <c t="s" r="E192" s="7">
-        <v>348</v>
-      </c>
-      <c r="F192" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G192" s="8">
-        <v>48</v>
-      </c>
-      <c t="s" r="H192" s="8">
-        <v>31</v>
-      </c>
-      <c t="s" r="I192" s="7">
-        <v>91</v>
-      </c>
-      <c t="s" r="J192" s="7">
-        <v>125</v>
-      </c>
+      <c r="E192" s="7"/>
+      <c r="F192" s="7"/>
+      <c r="G192" s="8"/>
+      <c r="H192" s="8"/>
+      <c r="I192" s="7"/>
+      <c r="J192" s="7"/>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
-      <c t="s" r="M192" s="7">
-        <v>352</v>
-      </c>
+      <c r="M192" s="7"/>
     </row>
     <row r="193" ht="14.25" customHeight="1">
       <c t="s" r="A193" s="6">
         <v>13</v>
       </c>
       <c r="B193" s="7">
-        <v>704</v>
+        <v>505</v>
       </c>
       <c t="s" r="C193" s="7">
         <v>14</v>
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>353</v>
+        <v>214</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="194" ht="14.25" customHeight="1">
+      <c t="s" r="A194" s="6">
+        <v>13</v>
+      </c>
+      <c r="B194" s="7">
+        <v>506</v>
+      </c>
+      <c t="s" r="C194" s="7">
+        <v>14</v>
+      </c>
+      <c r="D194" s="7"/>
+      <c t="s" r="E194" s="7">
         <v>354</v>
       </c>
-    </row>
-    <row r="194" ht="14.25" customHeight="1">
-      <c r="A194" s="6"/>
-      <c r="B194" s="7"/>
-      <c r="C194" s="7"/>
-      <c r="D194" s="7"/>
-      <c r="E194" s="7"/>
-      <c r="F194" s="7"/>
-      <c r="G194" s="8"/>
-      <c r="H194" s="8"/>
-      <c r="I194" s="7"/>
-      <c r="J194" s="7"/>
+      <c r="F194" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G194" s="8">
+        <v>48</v>
+      </c>
+      <c t="s" r="H194" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I194" s="7">
+        <v>279</v>
+      </c>
+      <c t="s" r="J194" s="7">
+        <v>356</v>
+      </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
-      <c r="M194" s="7"/>
+      <c t="s" r="M194" s="7">
+        <v>357</v>
+      </c>
     </row>
     <row r="195" ht="15" customHeight="1">
       <c t="s" r="A195" s="6">
         <v>13</v>
       </c>
       <c r="B195" s="7">
-        <v>505</v>
+        <v>453</v>
       </c>
       <c t="s" r="C195" s="7">
         <v>14</v>
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -8162,18 +8188,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>212</v>
+        <v>19</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>248</v>
+        <v>92</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -8181,34 +8207,34 @@
         <v>13</v>
       </c>
       <c r="B196" s="7">
-        <v>506</v>
+        <v>456</v>
       </c>
       <c t="s" r="C196" s="7">
         <v>14</v>
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>277</v>
+        <v>95</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>357</v>
+        <v>26</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>358</v>
+        <v>57</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -8216,14 +8242,14 @@
         <v>13</v>
       </c>
       <c r="B197" s="7">
-        <v>453</v>
+        <v>7526</v>
       </c>
       <c t="s" r="C197" s="7">
         <v>14</v>
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -8232,54 +8258,50 @@
         <v>30</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>21</v>
+        <v>359</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>19</v>
+        <v>360</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
-      <c t="s" r="M197" s="7">
-        <v>359</v>
-      </c>
+      <c r="M197" s="7"/>
     </row>
     <row r="198" ht="14.25" customHeight="1">
       <c t="s" r="A198" s="6">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="B198" s="7">
-        <v>456</v>
+        <v>7527</v>
       </c>
       <c t="s" r="C198" s="7">
         <v>14</v>
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>21</v>
+        <v>359</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>95</v>
+        <v>246</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>26</v>
+        <v>361</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
-      <c t="s" r="M198" s="7">
-        <v>57</v>
-      </c>
+      <c r="M198" s="7"/>
     </row>
     <row r="199" ht="14.25" customHeight="1">
       <c r="A199" s="6"/>
@@ -8308,27 +8330,27 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -8343,7 +8365,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8352,18 +8374,18 @@
         <v>48</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I201" s="7">
         <v>50</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -8378,19 +8400,19 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H202" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>116</v>
@@ -8398,7 +8420,7 @@
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8428,7 +8450,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8440,15 +8462,15 @@
         <v>87</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -8463,7 +8485,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8475,15 +8497,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8498,7 +8520,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8513,12 +8535,12 @@
         <v>70</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
       <c t="s" r="M206" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
@@ -8533,7 +8555,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8545,10 +8567,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -8581,29 +8603,29 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>87</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="K209" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8618,7 +8640,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8627,7 +8649,7 @@
         <v>87</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c t="s" r="I210" s="7">
         <v>80</v>
@@ -8638,7 +8660,7 @@
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8653,27 +8675,27 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c t="s" r="H211" s="8">
         <v>87</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8688,7 +8710,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8703,7 +8725,7 @@
         <v>60</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8736,7 +8758,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8745,18 +8767,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -8771,27 +8793,27 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="H215" s="8">
         <v>100</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -8806,7 +8828,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8815,18 +8837,18 @@
         <v>100</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -8841,19 +8863,19 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J217" s="7">
         <v>19</v>
@@ -8861,7 +8883,7 @@
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8876,7 +8898,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8885,10 +8907,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c t="s" r="J218" s="7">
         <v>38</v>
@@ -8896,7 +8918,7 @@
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -8911,19 +8933,19 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J219" s="7">
         <v>114</v>
@@ -8931,7 +8953,7 @@
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -8961,7 +8983,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8976,12 +8998,12 @@
         <v>101</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -8996,7 +9018,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -9008,15 +9030,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -9031,7 +9053,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -9046,12 +9068,12 @@
         <v>34</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -9066,7 +9088,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -9081,12 +9103,12 @@
         <v>35</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -9101,7 +9123,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -9116,12 +9138,12 @@
         <v>68</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -9136,7 +9158,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -9151,12 +9173,12 @@
         <v>70</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -9171,7 +9193,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -9186,7 +9208,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -9219,7 +9241,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -9228,18 +9250,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="I229" s="7">
         <v>104</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -9254,13 +9276,13 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>17</v>
@@ -9269,12 +9291,12 @@
         <v>32</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -9289,7 +9311,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9301,7 +9323,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J231" s="7">
         <v>112</v>
@@ -9309,7 +9331,7 @@
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -9324,7 +9346,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9336,10 +9358,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -9359,7 +9381,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9371,14 +9393,16 @@
         <v>48</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
-      <c r="M233" s="7"/>
+      <c t="s" r="M233" s="7">
+        <v>403</v>
+      </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
       <c t="s" r="A234" s="6">
@@ -9392,7 +9416,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9404,10 +9428,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -9440,7 +9464,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9449,10 +9473,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>102</v>
@@ -9460,7 +9484,7 @@
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9475,13 +9499,13 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>17</v>
@@ -9490,12 +9514,12 @@
         <v>104</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
       <c t="s" r="M237" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
@@ -9510,7 +9534,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9522,7 +9546,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c t="s" r="J238" s="7">
         <v>78</v>
@@ -9530,7 +9554,7 @@
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
       <c t="s" r="M238" s="7">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="239" ht="14.25" customHeight="1">
@@ -9545,7 +9569,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9557,7 +9581,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>38</v>
@@ -9565,7 +9589,7 @@
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9580,7 +9604,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9592,15 +9616,15 @@
         <v>48</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -9630,19 +9654,19 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c t="s" r="J242" s="7">
         <v>49</v>
@@ -9650,7 +9674,7 @@
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9665,7 +9689,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9677,15 +9701,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -9700,7 +9724,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9712,15 +9736,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -9750,7 +9774,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9765,12 +9789,12 @@
         <v>102</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
@@ -9785,7 +9809,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9797,15 +9821,15 @@
         <v>31</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -9820,7 +9844,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9832,7 +9856,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c t="s" r="J248" s="7">
         <v>111</v>
@@ -9870,7 +9894,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9879,18 +9903,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I250" s="7">
         <v>103</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c t="s" r="M250" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
@@ -9905,19 +9929,19 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H251" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c t="s" r="J251" s="7">
         <v>20</v>
@@ -9925,7 +9949,7 @@
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -9940,7 +9964,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9952,15 +9976,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
       <c t="s" r="M252" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
@@ -9975,7 +9999,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9984,18 +10008,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c t="s" r="I253" s="7">
         <v>41</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -10010,26 +10034,28 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
-      <c r="M254" s="7"/>
+      <c t="s" r="M254" s="7">
+        <v>426</v>
+      </c>
     </row>
     <row r="255" ht="15" customHeight="1">
       <c r="A255" s="6"/>
@@ -10058,27 +10084,27 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
+        <v>427</v>
+      </c>
+      <c r="F256" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G256" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H256" s="8">
         <v>423</v>
-      </c>
-      <c r="F256" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G256" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H256" s="8">
-        <v>420</v>
       </c>
       <c t="s" r="I256" s="7">
         <v>62</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -10093,22 +10119,22 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
+        <v>427</v>
+      </c>
+      <c r="F257" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G257" s="8">
         <v>423</v>
       </c>
-      <c r="F257" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G257" s="8">
+      <c t="s" r="H257" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I257" s="7">
+        <v>149</v>
+      </c>
+      <c t="s" r="J257" s="7">
         <v>420</v>
-      </c>
-      <c t="s" r="H257" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I257" s="7">
-        <v>148</v>
-      </c>
-      <c t="s" r="J257" s="7">
-        <v>417</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -10128,7 +10154,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -10137,7 +10163,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c t="s" r="I258" s="7">
         <v>111</v>
@@ -10148,7 +10174,7 @@
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -10163,22 +10189,22 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c t="s" r="H259" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -10198,7 +10224,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -10210,15 +10236,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -10248,7 +10274,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F262" s="7">
         <v>320</v>
@@ -10257,18 +10283,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c t="s" r="M262" s="7">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
@@ -10283,27 +10309,27 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F263" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -10318,7 +10344,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F264" s="7">
         <v>320</v>
@@ -10327,13 +10353,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -10353,13 +10379,13 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F265" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>30</v>
@@ -10368,12 +10394,12 @@
         <v>109</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10388,7 +10414,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F266" s="7">
         <v>320</v>
@@ -10397,13 +10423,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -10421,13 +10447,13 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>30</v>
@@ -10436,7 +10462,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -10469,7 +10495,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -10481,15 +10507,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10504,7 +10530,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10516,15 +10542,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10539,7 +10565,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10551,7 +10577,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>67</v>
@@ -10559,7 +10585,7 @@
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -10574,7 +10600,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10609,7 +10635,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10621,15 +10647,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10659,7 +10685,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10671,15 +10697,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -10694,7 +10720,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10706,7 +10732,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>34</v>
@@ -10714,7 +10740,7 @@
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
@@ -10729,7 +10755,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10738,7 +10764,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c t="s" r="I277" s="7">
         <v>67</v>
@@ -10749,7 +10775,7 @@
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
       <c t="s" r="M277" s="7">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
@@ -10764,27 +10790,27 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -10799,7 +10825,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -10808,13 +10834,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10847,7 +10873,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10859,15 +10885,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -10882,7 +10908,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10894,7 +10920,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c t="s" r="J282" s="7">
         <v>67</v>
@@ -10902,7 +10928,7 @@
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -10917,7 +10943,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10926,10 +10952,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J283" s="7">
         <v>26</v>
@@ -10937,7 +10963,7 @@
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -10952,27 +10978,27 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -10987,7 +11013,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10996,10 +11022,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>18</v>
@@ -11035,7 +11061,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -11050,12 +11076,12 @@
         <v>102</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -11070,7 +11096,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -11082,15 +11108,15 @@
         <v>100</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -11105,7 +11131,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -11120,12 +11146,12 @@
         <v>109</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -11140,7 +11166,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -11155,12 +11181,12 @@
         <v>92</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -11175,7 +11201,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -11187,15 +11213,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -11225,7 +11251,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -11234,18 +11260,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -11260,19 +11286,19 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>19</v>
@@ -11280,7 +11306,7 @@
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -11295,7 +11321,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -11304,18 +11330,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c t="s" r="I295" s="7">
         <v>80</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c t="s" r="M295" s="7">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
@@ -11330,19 +11356,19 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="J296" s="7">
         <v>96</v>
@@ -11350,7 +11376,7 @@
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -11380,7 +11406,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -11392,10 +11418,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -11415,7 +11441,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -11424,18 +11450,18 @@
         <v>48</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="I299" s="7">
         <v>20</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
       <c t="s" r="M299" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1">
@@ -11450,27 +11476,27 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -11485,7 +11511,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -11494,20 +11520,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c t="s" r="K301" s="7">
         <v>71</v>
       </c>
       <c r="L301" s="7"/>
       <c t="s" r="M301" s="7">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="302" ht="14.25" customHeight="1">
@@ -11522,29 +11548,29 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c t="s" r="K302" s="7">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="303" ht="14.25" customHeight="1">
@@ -11574,7 +11600,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -11586,15 +11612,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11609,7 +11635,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -11624,12 +11650,12 @@
         <v>80</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11644,7 +11670,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -11656,15 +11682,15 @@
         <v>100</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11679,7 +11705,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -11691,14 +11717,16 @@
         <v>30</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
-      <c r="M307" s="7"/>
+      <c t="s" r="M307" s="7">
+        <v>480</v>
+      </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
       <c r="A308" s="6"/>
@@ -11727,7 +11755,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11739,7 +11767,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>33</v>
@@ -11762,7 +11790,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11782,7 +11810,7 @@
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11797,7 +11825,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11806,18 +11834,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c t="s" r="I311" s="7">
         <v>95</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11832,13 +11860,13 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>30</v>
@@ -11852,7 +11880,7 @@
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -11867,7 +11895,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11879,7 +11907,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>73</v>
@@ -11915,7 +11943,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
@@ -11924,18 +11952,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -11950,13 +11978,13 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>30</v>
@@ -11965,12 +11993,12 @@
         <v>33</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -11985,7 +12013,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
@@ -11997,7 +12025,7 @@
         <v>87</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>81</v>
@@ -12020,7 +12048,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -12032,17 +12060,17 @@
         <v>30</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="K318" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -12072,7 +12100,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -12081,18 +12109,18 @@
         <v>48</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c t="s" r="I320" s="7">
         <v>50</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -12107,27 +12135,27 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -12142,7 +12170,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -12154,7 +12182,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c t="s" r="J322" s="7">
         <v>96</v>
@@ -12190,7 +12218,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -12202,7 +12230,7 @@
         <v>107</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c t="s" r="J324" s="7">
         <v>95</v>
@@ -12210,7 +12238,7 @@
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -12225,7 +12253,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -12237,10 +12265,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -12260,7 +12288,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
@@ -12269,17 +12297,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
-      <c r="M326" s="7"/>
+      <c t="s" r="M326" s="7">
+        <v>323</v>
+      </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
       <c t="s" r="A327" s="6">
@@ -12293,22 +12323,22 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c t="s" r="H327" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -12341,7 +12371,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -12350,10 +12380,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>65</v>
@@ -12376,27 +12406,27 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c t="s" r="H330" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -12411,7 +12441,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -12420,10 +12450,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>67</v>
@@ -12431,7 +12461,7 @@
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -12446,27 +12476,27 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12481,7 +12511,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -12490,10 +12520,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="J333" s="7">
         <v>61</v>
@@ -12501,7 +12531,7 @@
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12516,22 +12546,22 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -12564,7 +12594,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -12573,13 +12603,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -12599,13 +12629,13 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c t="s" r="H337" s="8">
         <v>17</v>
@@ -12619,7 +12649,7 @@
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -12634,7 +12664,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -12643,18 +12673,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12669,19 +12699,19 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c t="s" r="H339" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J339" s="7">
         <v>33</v>
@@ -12689,7 +12719,7 @@
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -12704,7 +12734,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12713,18 +12743,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c t="s" r="I340" s="7">
         <v>80</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12739,27 +12769,27 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -12789,7 +12819,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -12798,18 +12828,18 @@
         <v>25</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -12824,27 +12854,27 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -12859,27 +12889,27 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I345" s="7">
         <v>114</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -12894,22 +12924,22 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12942,7 +12972,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -12951,18 +12981,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -12977,27 +13007,27 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -13012,27 +13042,27 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -13047,22 +13077,22 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c t="s" r="H351" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -13082,7 +13112,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -13091,7 +13121,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c t="s" r="I352" s="7">
         <v>38</v>
@@ -13102,7 +13132,7 @@
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -13117,27 +13147,27 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c t="s" r="H353" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -13152,7 +13182,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -13161,13 +13191,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -13185,22 +13215,22 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -13233,7 +13263,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -13253,7 +13283,7 @@
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>521</v>
+        <v>526</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -13268,7 +13298,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -13303,7 +13333,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -13315,15 +13345,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -13338,7 +13368,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -13353,12 +13383,12 @@
         <v>19</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>523</v>
+        <v>528</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13373,7 +13403,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -13385,7 +13415,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c t="s" r="J361" s="7">
         <v>74</v>
@@ -13421,7 +13451,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13433,15 +13463,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>526</v>
+        <v>531</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -13456,7 +13486,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -13471,7 +13501,7 @@
         <v>102</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -13491,7 +13521,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -13500,18 +13530,18 @@
         <v>48</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c t="s" r="M365" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
@@ -13526,27 +13556,27 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -13561,7 +13591,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -13570,18 +13600,18 @@
         <v>48</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -13596,22 +13626,22 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -13644,7 +13674,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -13656,15 +13686,15 @@
         <v>37</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>530</v>
+        <v>535</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13679,7 +13709,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -13691,7 +13721,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J371" s="7">
         <v>34</v>
@@ -13699,7 +13729,7 @@
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>531</v>
+        <v>536</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -13714,7 +13744,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -13723,13 +13753,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c t="s" r="I372" s="7">
         <v>67</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13749,13 +13779,13 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>30</v>
@@ -13764,12 +13794,12 @@
         <v>56</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>532</v>
+        <v>537</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -13784,7 +13814,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -13796,10 +13826,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13832,7 +13862,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -13841,18 +13871,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -13867,27 +13897,27 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -13902,7 +13932,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13911,7 +13941,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c t="s" r="I378" s="7">
         <v>35</v>
@@ -13922,7 +13952,7 @@
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>538</v>
+        <v>543</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -13937,27 +13967,27 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>539</v>
+        <v>544</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -13987,7 +14017,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -14002,7 +14032,7 @@
         <v>74</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -14022,7 +14052,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -14031,13 +14061,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="I382" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -14057,22 +14087,22 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="H383" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -14092,7 +14122,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -14104,7 +14134,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>59</v>
@@ -14112,7 +14142,7 @@
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -14127,7 +14157,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -14139,10 +14169,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -14175,7 +14205,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -14184,10 +14214,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>88</v>
@@ -14195,7 +14225,7 @@
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>542</v>
+        <v>547</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -14210,27 +14240,27 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -14245,7 +14275,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -14257,15 +14287,15 @@
         <v>37</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>543</v>
+        <v>548</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -14280,7 +14310,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -14295,7 +14325,7 @@
         <v>108</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -14315,7 +14345,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -14324,18 +14354,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -14350,27 +14380,27 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>544</v>
+        <v>480</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -14385,7 +14415,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -14397,10 +14427,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -14433,7 +14463,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -14448,12 +14478,12 @@
         <v>102</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -14468,7 +14498,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -14480,15 +14510,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>548</v>
+        <v>552</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -14503,7 +14533,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -14518,12 +14548,12 @@
         <v>38</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>549</v>
+        <v>553</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -14538,7 +14568,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -14550,10 +14580,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -14571,7 +14601,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -14580,13 +14610,13 @@
         <v>21</v>
       </c>
       <c t="s" r="H399" s="8">
+        <v>272</v>
+      </c>
+      <c t="s" r="I399" s="7">
         <v>270</v>
       </c>
-      <c t="s" r="I399" s="7">
-        <v>268</v>
-      </c>
       <c t="s" r="J399" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -14619,7 +14649,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -14631,7 +14661,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>34</v>
@@ -14654,7 +14684,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -14666,7 +14696,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c t="s" r="J402" s="7">
         <v>113</v>
@@ -14689,7 +14719,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -14701,7 +14731,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>42</v>
@@ -14709,7 +14739,7 @@
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c t="s" r="M403" s="7">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
@@ -14724,7 +14754,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -14736,10 +14766,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -14772,7 +14802,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -14781,18 +14811,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I406" s="7">
         <v>105</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -14807,27 +14837,27 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>554</v>
+        <v>558</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -14842,27 +14872,27 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G408" s="8">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -14877,13 +14907,13 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>17</v>
@@ -14892,12 +14922,12 @@
         <v>81</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -14927,7 +14957,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F411" s="7">
         <v>320</v>
@@ -14936,7 +14966,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c t="s" r="I411" s="7">
         <v>49</v>
@@ -14947,7 +14977,7 @@
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -14962,13 +14992,13 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F412" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>17</v>
@@ -14982,7 +15012,7 @@
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -14997,7 +15027,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
@@ -15006,10 +15036,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c t="s" r="J413" s="7">
         <v>26</v>
@@ -15017,7 +15047,7 @@
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>556</v>
+        <v>560</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -15032,26 +15062,28 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="F414" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J414" s="7">
         <v>70</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
-      <c r="M414" s="7"/>
+      <c t="s" r="M414" s="7">
+        <v>561</v>
+      </c>
     </row>
     <row r="415" ht="15" customHeight="1">
       <c r="A415" s="6"/>
@@ -15080,7 +15112,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
@@ -15092,15 +15124,15 @@
         <v>48</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>558</v>
+        <v>563</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -15115,7 +15147,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
@@ -15124,10 +15156,10 @@
         <v>48</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c t="s" r="J417" s="7">
         <v>116</v>
@@ -15150,13 +15182,13 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>48</v>
@@ -15198,7 +15230,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="F420" s="7">
         <v>330</v>
@@ -15207,20 +15239,20 @@
         <v>48</v>
       </c>
       <c t="s" r="H420" s="8">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c t="s" r="I420" s="7">
         <v>46</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c t="s" r="K420" s="7">
         <v>18</v>
       </c>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -15235,25 +15267,25 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G421" s="8">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c t="s" r="H421" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c t="s" r="K421" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
@@ -15287,7 +15319,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F423" s="7">
         <v>330</v>
@@ -15299,7 +15331,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="J423" s="7">
         <v>34</v>
@@ -15307,7 +15339,7 @@
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
@@ -15322,7 +15354,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F424" s="7">
         <v>330</v>
@@ -15337,7 +15369,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
@@ -15357,7 +15389,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F425" s="7">
         <v>330</v>
@@ -15369,15 +15401,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
       <c t="s" r="M425" s="7">
-        <v>564</v>
+        <v>569</v>
       </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
@@ -15407,19 +15439,19 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="F427" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G427" s="8">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c t="s" r="H427" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c t="s" r="J427" s="7">
         <v>53</v>
@@ -15427,7 +15459,7 @@
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
       <c t="s" r="M427" s="7">
-        <v>567</v>
+        <v>572</v>
       </c>
     </row>
     <row r="428" ht="14.25" customHeight="1">
@@ -15442,7 +15474,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="F428" s="7">
         <v>330</v>
@@ -15451,17 +15483,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H428" s="8">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
-      <c r="M428" s="7"/>
+      <c t="s" r="M428" s="7">
+        <v>573</v>
+      </c>
     </row>
     <row r="429" ht="14.25" customHeight="1">
       <c r="A429" s="6"/>
@@ -15490,27 +15524,27 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="F430" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G430" s="8">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c t="s" r="H430" s="8">
         <v>87</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
       <c t="s" r="M430" s="7">
-        <v>570</v>
+        <v>576</v>
       </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
@@ -15540,7 +15574,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="F432" s="7">
         <v>330</v>
@@ -15549,18 +15583,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H432" s="8">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c t="s" r="M432" s="7">
-        <v>573</v>
+        <v>579</v>
       </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
@@ -15575,22 +15609,22 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="F433" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G433" s="8">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c t="s" r="H433" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -15598,7 +15632,7 @@
     </row>
     <row r="434" ht="15.75" customHeight="1">
       <c t="s" r="A434" s="9">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="B434" s="9"/>
       <c r="C434" s="9"/>
@@ -15618,7 +15652,7 @@
     <row r="435" ht="66" customHeight="1"/>
     <row r="436" ht="16.5" customHeight="1">
       <c t="s" r="A436" s="10">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="B436" s="10"/>
       <c r="C436" s="10"/>
@@ -15631,7 +15665,7 @@
       <c r="J436" s="10"/>
       <c r="K436" s="10"/>
       <c t="s" r="L436" s="11">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="M436" s="11"/>
       <c r="N436" s="11"/>
